--- a/templates/ERC000044/metadata_template_ERC000044.xlsx
+++ b/templates/ERC000044/metadata_template_ERC000044.xlsx
@@ -20,13 +20,13 @@
     <definedName name="clinicalsetting">'cv_sample'!$I$1:$I$2</definedName>
     <definedName name="countryoftravel">'cv_sample'!$J$1:$J$273</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Q$1:$Q$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
     <definedName name="travelrelation">'cv_sample'!$H$1:$H$3</definedName>
   </definedNames>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="625">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1738,7 +1744,7 @@
     <t>subject exposure duration</t>
   </si>
   <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>Arctic Ocean</t>
@@ -1759,7 +1765,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1771,10 +1777,19 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
   </si>
   <si>
     <t>North Sea</t>
@@ -2421,10 +2436,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2465,10 +2480,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2512,7 +2527,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2529,7 +2544,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2546,7 +2561,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2563,7 +2578,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2580,7 +2595,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2597,7 +2612,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2614,7 +2629,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2631,7 +2646,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2648,7 +2663,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2662,7 +2677,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2676,7 +2691,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2690,7 +2705,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2704,7 +2719,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2718,7 +2733,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2732,7 +2747,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2746,7 +2761,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2760,7 +2775,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2770,8 +2785,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2782,7 +2800,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2793,7 +2811,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2804,7 +2822,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2815,7 +2833,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2826,7 +2844,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2837,7 +2855,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2848,7 +2866,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2859,7 +2877,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2870,7 +2888,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2881,7 +2899,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2892,7 +2910,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2903,7 +2921,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2914,7 +2932,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2922,7 +2940,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2930,7 +2948,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2938,7 +2956,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2946,7 +2964,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2954,7 +2972,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2962,7 +2980,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2970,7 +2988,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2978,7 +2996,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2986,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2994,236 +3012,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3245,27 +3268,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3285,122 +3308,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3424,138 +3447,138 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -3582,1716 +3605,1716 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:Q289"/>
+  <dimension ref="H1:Q294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:17">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="8:17">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q2" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="8:17">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q3" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="8:17">
       <c r="J4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="8:17">
       <c r="J5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="8:17">
       <c r="J6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="8:17">
       <c r="J7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="8:17">
       <c r="J8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="8:17">
       <c r="J9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="8:17">
       <c r="J10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="8:17">
       <c r="J11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="8:17">
       <c r="J12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="8:17">
       <c r="J13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="8:17">
       <c r="J14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="8:17">
       <c r="J15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O15" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="8:17">
       <c r="J16" t="s">
+        <v>302</v>
+      </c>
+      <c r="O16" t="s">
         <v>300</v>
-      </c>
-      <c r="O16" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="17" spans="10:15">
       <c r="J17" t="s">
+        <v>303</v>
+      </c>
+      <c r="O17" t="s">
         <v>301</v>
-      </c>
-      <c r="O17" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="18" spans="10:15">
       <c r="J18" t="s">
+        <v>304</v>
+      </c>
+      <c r="O18" t="s">
         <v>302</v>
-      </c>
-      <c r="O18" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="19" spans="10:15">
       <c r="J19" t="s">
+        <v>305</v>
+      </c>
+      <c r="O19" t="s">
         <v>303</v>
-      </c>
-      <c r="O19" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="20" spans="10:15">
       <c r="J20" t="s">
+        <v>306</v>
+      </c>
+      <c r="O20" t="s">
         <v>304</v>
-      </c>
-      <c r="O20" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="21" spans="10:15">
       <c r="J21" t="s">
+        <v>307</v>
+      </c>
+      <c r="O21" t="s">
         <v>305</v>
-      </c>
-      <c r="O21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="22" spans="10:15">
       <c r="J22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O22" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="10:15">
       <c r="J23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="10:15">
       <c r="J24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="10:15">
       <c r="J25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="10:15">
       <c r="J26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O26" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="10:15">
       <c r="J27" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="10:15">
       <c r="J28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="10:15">
       <c r="J29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="10:15">
       <c r="J30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O30" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="10:15">
       <c r="J31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="10:15">
       <c r="J32" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O32" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="10:15">
       <c r="J33" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O33" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="34" spans="10:15">
       <c r="J34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="10:15">
       <c r="J35" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="10:15">
       <c r="J36" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="10:15">
       <c r="J37" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="10:15">
       <c r="J38" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="10:15">
       <c r="J39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="10:15">
       <c r="J40" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="10:15">
       <c r="J41" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="10:15">
       <c r="J42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O42" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="10:15">
       <c r="J43" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="10:15">
       <c r="J44" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O44" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="10:15">
       <c r="J45" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="10:15">
       <c r="J46" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="10:15">
       <c r="J47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="10:15">
       <c r="J48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O48" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="10:15">
       <c r="J49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O49" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="10:15">
       <c r="J50" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="10:15">
       <c r="J51" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O51" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="10:15">
       <c r="J52" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O52" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="10:15">
       <c r="J53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O53" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="10:15">
       <c r="J54" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O54" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="10:15">
       <c r="J55" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O55" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="10:15">
       <c r="J56" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O56" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="10:15">
       <c r="J57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O57" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="10:15">
       <c r="J58" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O58" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="10:15">
       <c r="J59" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O59" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="10:15">
       <c r="J60" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O60" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="10:15">
       <c r="J61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="10:15">
       <c r="J62" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O62" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="10:15">
       <c r="J63" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O63" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" spans="10:15">
       <c r="J64" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O64" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="10:15">
       <c r="J65" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O65" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="66" spans="10:15">
       <c r="J66" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O66" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="10:15">
       <c r="J67" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O67" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="10:15">
       <c r="J68" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O68" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="10:15">
       <c r="J69" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="10:15">
       <c r="J70" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="10:15">
       <c r="J71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O71" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="10:15">
       <c r="J72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O72" t="s">
-        <v>574</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="10:15">
       <c r="J73" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O73" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" spans="10:15">
       <c r="J74" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="75" spans="10:15">
       <c r="J75" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O75" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="10:15">
       <c r="J76" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O76" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="10:15">
       <c r="J77" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O77" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="10:15">
       <c r="J78" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O78" t="s">
-        <v>357</v>
+        <v>576</v>
       </c>
     </row>
     <row r="79" spans="10:15">
       <c r="J79" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O79" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="10:15">
       <c r="J80" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O80" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="10:15">
       <c r="J81" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O81" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" spans="10:15">
       <c r="J82" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O82" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="10:15">
       <c r="J83" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O83" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="10:15">
       <c r="J84" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O84" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="10:15">
       <c r="J85" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O85" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="10:15">
       <c r="J86" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O86" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="10:15">
       <c r="J87" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O87" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="10:15">
       <c r="J88" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O88" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="10:15">
       <c r="J89" t="s">
+        <v>375</v>
+      </c>
+      <c r="O89" t="s">
         <v>373</v>
-      </c>
-      <c r="O89" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="90" spans="10:15">
       <c r="J90" t="s">
+        <v>376</v>
+      </c>
+      <c r="O90" t="s">
         <v>374</v>
-      </c>
-      <c r="O90" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="91" spans="10:15">
       <c r="J91" t="s">
+        <v>377</v>
+      </c>
+      <c r="O91" t="s">
         <v>375</v>
-      </c>
-      <c r="O91" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="92" spans="10:15">
       <c r="J92" t="s">
+        <v>378</v>
+      </c>
+      <c r="O92" t="s">
         <v>376</v>
-      </c>
-      <c r="O92" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="93" spans="10:15">
       <c r="J93" t="s">
+        <v>379</v>
+      </c>
+      <c r="O93" t="s">
         <v>377</v>
-      </c>
-      <c r="O93" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="94" spans="10:15">
       <c r="J94" t="s">
+        <v>380</v>
+      </c>
+      <c r="O94" t="s">
         <v>378</v>
-      </c>
-      <c r="O94" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="95" spans="10:15">
       <c r="J95" t="s">
+        <v>381</v>
+      </c>
+      <c r="O95" t="s">
         <v>379</v>
-      </c>
-      <c r="O95" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="96" spans="10:15">
       <c r="J96" t="s">
+        <v>382</v>
+      </c>
+      <c r="O96" t="s">
         <v>380</v>
-      </c>
-      <c r="O96" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="97" spans="10:15">
       <c r="J97" t="s">
+        <v>383</v>
+      </c>
+      <c r="O97" t="s">
         <v>381</v>
-      </c>
-      <c r="O97" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="98" spans="10:15">
       <c r="J98" t="s">
+        <v>384</v>
+      </c>
+      <c r="O98" t="s">
         <v>382</v>
-      </c>
-      <c r="O98" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="99" spans="10:15">
       <c r="J99" t="s">
+        <v>385</v>
+      </c>
+      <c r="O99" t="s">
         <v>383</v>
-      </c>
-      <c r="O99" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="100" spans="10:15">
       <c r="J100" t="s">
+        <v>386</v>
+      </c>
+      <c r="O100" t="s">
         <v>384</v>
-      </c>
-      <c r="O100" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="101" spans="10:15">
       <c r="J101" t="s">
+        <v>387</v>
+      </c>
+      <c r="O101" t="s">
         <v>385</v>
-      </c>
-      <c r="O101" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="102" spans="10:15">
       <c r="J102" t="s">
+        <v>388</v>
+      </c>
+      <c r="O102" t="s">
         <v>386</v>
-      </c>
-      <c r="O102" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="103" spans="10:15">
       <c r="J103" t="s">
+        <v>389</v>
+      </c>
+      <c r="O103" t="s">
         <v>387</v>
-      </c>
-      <c r="O103" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="104" spans="10:15">
       <c r="J104" t="s">
+        <v>390</v>
+      </c>
+      <c r="O104" t="s">
         <v>388</v>
-      </c>
-      <c r="O104" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="105" spans="10:15">
       <c r="J105" t="s">
+        <v>391</v>
+      </c>
+      <c r="O105" t="s">
         <v>389</v>
-      </c>
-      <c r="O105" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="106" spans="10:15">
       <c r="J106" t="s">
+        <v>392</v>
+      </c>
+      <c r="O106" t="s">
         <v>390</v>
-      </c>
-      <c r="O106" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="107" spans="10:15">
       <c r="J107" t="s">
+        <v>393</v>
+      </c>
+      <c r="O107" t="s">
         <v>391</v>
-      </c>
-      <c r="O107" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="108" spans="10:15">
       <c r="J108" t="s">
+        <v>394</v>
+      </c>
+      <c r="O108" t="s">
         <v>392</v>
-      </c>
-      <c r="O108" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="109" spans="10:15">
       <c r="J109" t="s">
+        <v>395</v>
+      </c>
+      <c r="O109" t="s">
         <v>393</v>
-      </c>
-      <c r="O109" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="110" spans="10:15">
       <c r="J110" t="s">
+        <v>396</v>
+      </c>
+      <c r="O110" t="s">
         <v>394</v>
-      </c>
-      <c r="O110" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="111" spans="10:15">
       <c r="J111" t="s">
+        <v>397</v>
+      </c>
+      <c r="O111" t="s">
         <v>395</v>
-      </c>
-      <c r="O111" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="112" spans="10:15">
       <c r="J112" t="s">
+        <v>398</v>
+      </c>
+      <c r="O112" t="s">
         <v>396</v>
-      </c>
-      <c r="O112" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="113" spans="10:15">
       <c r="J113" t="s">
+        <v>399</v>
+      </c>
+      <c r="O113" t="s">
         <v>397</v>
-      </c>
-      <c r="O113" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="114" spans="10:15">
       <c r="J114" t="s">
+        <v>400</v>
+      </c>
+      <c r="O114" t="s">
         <v>398</v>
-      </c>
-      <c r="O114" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="115" spans="10:15">
       <c r="J115" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O115" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="116" spans="10:15">
       <c r="J116" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O116" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="10:15">
       <c r="J117" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O117" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="10:15">
       <c r="J118" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O118" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="10:15">
       <c r="J119" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O119" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="10:15">
       <c r="J120" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O120" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="10:15">
       <c r="J121" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O121" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="10:15">
       <c r="J122" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O122" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="10:15">
       <c r="J123" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O123" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="10:15">
       <c r="J124" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O124" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="10:15">
       <c r="J125" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O125" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="10:15">
       <c r="J126" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O126" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="127" spans="10:15">
       <c r="J127" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O127" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128" spans="10:15">
       <c r="J128" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O128" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" spans="10:15">
       <c r="J129" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O129" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="130" spans="10:15">
       <c r="J130" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O130" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131" spans="10:15">
       <c r="J131" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O131" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="10:15">
       <c r="J132" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O132" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="133" spans="10:15">
       <c r="J133" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O133" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="134" spans="10:15">
       <c r="J134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O134" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="10:15">
       <c r="J135" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O135" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="10:15">
       <c r="J136" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O136" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="10:15">
       <c r="J137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O137" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="10:15">
       <c r="J138" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O138" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="10:15">
       <c r="J139" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O139" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="10:15">
       <c r="J140" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O140" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="141" spans="10:15">
       <c r="J141" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O141" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="142" spans="10:15">
       <c r="J142" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O142" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="10:15">
       <c r="J143" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O143" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="10:15">
       <c r="J144" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O144" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="10:15">
       <c r="J145" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O145" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="146" spans="10:15">
       <c r="J146" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O146" t="s">
-        <v>427</v>
+        <v>580</v>
       </c>
     </row>
     <row r="147" spans="10:15">
       <c r="J147" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O147" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="148" spans="10:15">
       <c r="J148" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O148" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="149" spans="10:15">
       <c r="J149" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O149" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="150" spans="10:15">
       <c r="J150" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O150" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="151" spans="10:15">
       <c r="J151" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O151" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="152" spans="10:15">
       <c r="J152" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O152" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="10:15">
       <c r="J153" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O153" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="10:15">
       <c r="J154" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O154" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="155" spans="10:15">
       <c r="J155" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O155" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="156" spans="10:15">
       <c r="J156" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O156" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="157" spans="10:15">
       <c r="J157" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O157" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="158" spans="10:15">
       <c r="J158" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O158" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="159" spans="10:15">
       <c r="J159" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O159" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="160" spans="10:15">
       <c r="J160" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O160" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="161" spans="10:15">
       <c r="J161" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O161" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="162" spans="10:15">
       <c r="J162" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O162" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="10:15">
       <c r="J163" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O163" t="s">
-        <v>443</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="10:15">
       <c r="J164" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O164" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="10:15">
       <c r="J165" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O165" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="10:15">
       <c r="J166" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O166" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="167" spans="10:15">
       <c r="J167" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O167" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="10:15">
       <c r="J168" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="169" spans="10:15">
       <c r="J169" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="10:15">
       <c r="J170" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O170" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="171" spans="10:15">
       <c r="J171" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O171" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="172" spans="10:15">
       <c r="J172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O172" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="173" spans="10:15">
       <c r="J173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O173" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="174" spans="10:15">
       <c r="J174" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O174" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="10:15">
       <c r="J175" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O175" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="176" spans="10:15">
       <c r="J176" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O176" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="177" spans="10:15">
       <c r="J177" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O177" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="10:15">
       <c r="J178" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O178" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="10:15">
       <c r="J179" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O179" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="180" spans="10:15">
       <c r="J180" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O180" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="10:15">
       <c r="J181" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O181" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="10:15">
       <c r="J182" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O182" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="10:15">
       <c r="J183" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O183" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="184" spans="10:15">
       <c r="J184" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O184" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="185" spans="10:15">
       <c r="J185" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O185" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="10:15">
       <c r="J186" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O186" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="187" spans="10:15">
       <c r="J187" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O187" t="s">
-        <v>466</v>
+        <v>585</v>
       </c>
     </row>
     <row r="188" spans="10:15">
       <c r="J188" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O188" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="189" spans="10:15">
       <c r="J189" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O189" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="190" spans="10:15">
       <c r="J190" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O190" t="s">
-        <v>581</v>
+        <v>470</v>
       </c>
     </row>
     <row r="191" spans="10:15">
       <c r="J191" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O191" t="s">
-        <v>469</v>
+        <v>586</v>
       </c>
     </row>
     <row r="192" spans="10:15">
       <c r="J192" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O192" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="193" spans="10:15">
       <c r="J193" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O193" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194" spans="10:15">
       <c r="J194" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O194" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="195" spans="10:15">
       <c r="J195" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O195" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="196" spans="10:15">
       <c r="J196" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O196" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="197" spans="10:15">
       <c r="J197" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O197" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="198" spans="10:15">
       <c r="J198" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O198" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="199" spans="10:15">
       <c r="J199" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O199" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="200" spans="10:15">
       <c r="J200" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O200" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="201" spans="10:15">
       <c r="J201" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O201" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="202" spans="10:15">
       <c r="J202" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O202" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203" spans="10:15">
       <c r="J203" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O203" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="204" spans="10:15">
       <c r="J204" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O204" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="10:15">
       <c r="J205" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="10:15">
       <c r="J206" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="10:15">
       <c r="J207" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O207" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="208" spans="10:15">
       <c r="J208" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O208" t="s">
-        <v>582</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="10:15">
       <c r="J209" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O209" t="s">
-        <v>486</v>
+        <v>587</v>
       </c>
     </row>
     <row r="210" spans="10:15">
       <c r="J210" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O210" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211" spans="10:15">
       <c r="J211" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O211" t="s">
         <v>489</v>
@@ -5299,7 +5322,7 @@
     </row>
     <row r="212" spans="10:15">
       <c r="J212" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O212" t="s">
         <v>490</v>
@@ -5307,7 +5330,7 @@
     </row>
     <row r="213" spans="10:15">
       <c r="J213" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O213" t="s">
         <v>491</v>
@@ -5315,23 +5338,23 @@
     </row>
     <row r="214" spans="10:15">
       <c r="J214" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O214" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="215" spans="10:15">
       <c r="J215" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O215" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="216" spans="10:15">
       <c r="J216" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O216" t="s">
         <v>495</v>
@@ -5339,7 +5362,7 @@
     </row>
     <row r="217" spans="10:15">
       <c r="J217" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O217" t="s">
         <v>496</v>
@@ -5347,7 +5370,7 @@
     </row>
     <row r="218" spans="10:15">
       <c r="J218" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O218" t="s">
         <v>497</v>
@@ -5355,7 +5378,7 @@
     </row>
     <row r="219" spans="10:15">
       <c r="J219" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O219" t="s">
         <v>498</v>
@@ -5363,55 +5386,55 @@
     </row>
     <row r="220" spans="10:15">
       <c r="J220" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O220" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="221" spans="10:15">
       <c r="J221" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O221" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="222" spans="10:15">
       <c r="J222" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O222" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="10:15">
       <c r="J223" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O223" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="10:15">
       <c r="J224" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O224" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="225" spans="10:15">
       <c r="J225" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O225" t="s">
-        <v>583</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="10:15">
       <c r="J226" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O226" t="s">
         <v>505</v>
@@ -5419,7 +5442,7 @@
     </row>
     <row r="227" spans="10:15">
       <c r="J227" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O227" t="s">
         <v>506</v>
@@ -5427,410 +5450,410 @@
     </row>
     <row r="228" spans="10:15">
       <c r="J228" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O228" t="s">
-        <v>507</v>
+        <v>588</v>
       </c>
     </row>
     <row r="229" spans="10:15">
       <c r="J229" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O229" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="230" spans="10:15">
       <c r="J230" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O230" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="231" spans="10:15">
       <c r="J231" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O231" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="232" spans="10:15">
       <c r="J232" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O232" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="233" spans="10:15">
       <c r="J233" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O233" t="s">
-        <v>584</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="10:15">
       <c r="J234" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O234" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="10:15">
       <c r="J235" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="236" spans="10:15">
       <c r="J236" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O236" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="237" spans="10:15">
       <c r="J237" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O237" t="s">
-        <v>517</v>
+        <v>589</v>
       </c>
     </row>
     <row r="238" spans="10:15">
       <c r="J238" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O238" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="239" spans="10:15">
       <c r="J239" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O239" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="240" spans="10:15">
       <c r="J240" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O240" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="241" spans="10:15">
       <c r="J241" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O241" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="242" spans="10:15">
       <c r="J242" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O242" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="243" spans="10:15">
       <c r="J243" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O243" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="244" spans="10:15">
       <c r="J244" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O244" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="245" spans="10:15">
       <c r="J245" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O245" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="10:15">
       <c r="J246" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O246" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="247" spans="10:15">
       <c r="J247" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O247" t="s">
-        <v>585</v>
+        <v>525</v>
       </c>
     </row>
     <row r="248" spans="10:15">
       <c r="J248" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O248" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="249" spans="10:15">
       <c r="J249" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O249" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250" spans="10:15">
       <c r="J250" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O250" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="251" spans="10:15">
       <c r="J251" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O251" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
     </row>
     <row r="252" spans="10:15">
       <c r="J252" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O252" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="253" spans="10:15">
       <c r="J253" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O253" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="254" spans="10:15">
       <c r="J254" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O254" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="255" spans="10:15">
       <c r="J255" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O255" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="256" spans="10:15">
       <c r="J256" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O256" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="257" spans="10:15">
       <c r="J257" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O257" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="258" spans="10:15">
       <c r="J258" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O258" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="259" spans="10:15">
       <c r="J259" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O259" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="260" spans="10:15">
       <c r="J260" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O260" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="261" spans="10:15">
       <c r="J261" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O261" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262" spans="10:15">
       <c r="J262" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O262" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="263" spans="10:15">
       <c r="J263" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O263" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="10:15">
       <c r="J264" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="O264" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" spans="10:15">
       <c r="J265" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O265" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="266" spans="10:15">
       <c r="J266" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O266" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="267" spans="10:15">
       <c r="J267" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O267" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="268" spans="10:15">
       <c r="J268" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O268" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="269" spans="10:15">
       <c r="J269" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O269" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="270" spans="10:15">
       <c r="J270" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O270" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="271" spans="10:15">
       <c r="J271" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O271" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="272" spans="10:15">
       <c r="J272" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O272" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="273" spans="10:15">
       <c r="J273" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O273" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="274" spans="10:15">
       <c r="O274" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="275" spans="10:15">
       <c r="O275" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="276" spans="10:15">
       <c r="O276" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="277" spans="10:15">
       <c r="O277" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
     </row>
     <row r="278" spans="10:15">
       <c r="O278" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
     </row>
     <row r="279" spans="10:15">
       <c r="O279" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
     </row>
     <row r="280" spans="10:15">
       <c r="O280" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="281" spans="10:15">
       <c r="O281" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
     </row>
     <row r="282" spans="10:15">
@@ -5871,6 +5894,31 @@
     <row r="289" spans="15:15">
       <c r="O289" t="s">
         <v>598</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000044/metadata_template_ERC000044.xlsx
+++ b/templates/ERC000044/metadata_template_ERC000044.xlsx
@@ -17,25 +17,25 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="clinicalsetting">'cv_sample'!$G$1:$G$2</definedName>
-    <definedName name="countryoftravel">'cv_sample'!$H$1:$H$273</definedName>
+    <definedName name="clinicalsetting">'cv_sample'!$H$1:$H$2</definedName>
+    <definedName name="countryoftravel">'cv_sample'!$I$1:$I$273</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$M$1:$M$289</definedName>
-    <definedName name="hostdiseaseoutcome">'cv_sample'!$O$1:$O$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$294</definedName>
+    <definedName name="hostdiseaseoutcome">'cv_sample'!$P$1:$P$3</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="travelrelation">'cv_sample'!$F$1:$F$3</definedName>
+    <definedName name="travelrelation">'cv_sample'!$G$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="623">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -841,6 +847,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1747,7 +1759,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1759,10 +1771,19 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
   </si>
   <si>
     <t>North Sea</t>
@@ -2409,10 +2430,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2453,10 +2474,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2483,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2500,7 +2521,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2517,7 +2538,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2534,7 +2555,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2551,7 +2572,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2568,7 +2589,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2585,7 +2606,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2602,7 +2623,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2619,7 +2640,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2636,7 +2657,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2650,7 +2671,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2664,7 +2685,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2678,7 +2699,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2692,7 +2713,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2706,7 +2727,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2720,7 +2741,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2734,7 +2755,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2748,7 +2769,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2758,8 +2779,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2770,7 +2794,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2781,7 +2805,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2792,7 +2816,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2803,7 +2827,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2814,7 +2838,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2825,7 +2849,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2836,7 +2860,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2847,7 +2871,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2858,7 +2882,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2869,7 +2893,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2880,7 +2904,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2891,7 +2915,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2902,7 +2926,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2910,7 +2934,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2918,7 +2942,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2926,7 +2950,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2934,7 +2958,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2942,7 +2966,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2950,7 +2974,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2958,7 +2982,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2966,7 +2990,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2974,7 +2998,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2982,236 +3006,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3233,27 +3262,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3273,122 +3302,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3398,13 +3427,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3412,143 +3441,149 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>279</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>554</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="150" customHeight="1">
+        <v>619</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>280</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>555</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>travelrelation</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>clinicalsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>countryoftravel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
       <formula1>hostdiseaseoutcome</formula1>
     </dataValidation>
   </dataValidations>
@@ -3558,2295 +3593,2320 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:O289"/>
+  <dimension ref="G1:P294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:15">
-      <c r="F1" t="s">
-        <v>272</v>
-      </c>
+    <row r="1" spans="7:16">
       <c r="G1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
         <v>281</v>
       </c>
-      <c r="M1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="2" spans="6:15">
-      <c r="F2" t="s">
-        <v>273</v>
-      </c>
+      <c r="I1" t="s">
+        <v>285</v>
+      </c>
+      <c r="N1" t="s">
+        <v>285</v>
+      </c>
+      <c r="P1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="2" spans="7:16">
       <c r="G2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
         <v>282</v>
       </c>
-      <c r="M2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>286</v>
+      </c>
+      <c r="P2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3" spans="7:16">
+      <c r="G3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" t="s">
+        <v>287</v>
+      </c>
+      <c r="N3" t="s">
+        <v>287</v>
+      </c>
+      <c r="P3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="4" spans="7:16">
+      <c r="I4" t="s">
+        <v>288</v>
+      </c>
+      <c r="N4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="7:16">
+      <c r="I5" t="s">
+        <v>289</v>
+      </c>
+      <c r="N5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="7:16">
+      <c r="I6" t="s">
+        <v>290</v>
+      </c>
+      <c r="N6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="7:16">
+      <c r="I7" t="s">
+        <v>291</v>
+      </c>
+      <c r="N7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="7:16">
+      <c r="I8" t="s">
+        <v>292</v>
+      </c>
+      <c r="N8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="7:16">
+      <c r="I9" t="s">
+        <v>293</v>
+      </c>
+      <c r="N9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="7:16">
+      <c r="I10" t="s">
+        <v>294</v>
+      </c>
+      <c r="N10" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="11" spans="7:16">
+      <c r="I11" t="s">
+        <v>295</v>
+      </c>
+      <c r="N11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="7:16">
+      <c r="I12" t="s">
+        <v>296</v>
+      </c>
+      <c r="N12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="7:16">
+      <c r="I13" t="s">
+        <v>297</v>
+      </c>
+      <c r="N13" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="7:16">
+      <c r="I14" t="s">
+        <v>298</v>
+      </c>
+      <c r="N14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="7:16">
+      <c r="I15" t="s">
+        <v>299</v>
+      </c>
+      <c r="N15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" spans="7:16">
+      <c r="I16" t="s">
+        <v>300</v>
+      </c>
+      <c r="N16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="9:14">
+      <c r="I17" t="s">
+        <v>301</v>
+      </c>
+      <c r="N17" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="9:14">
+      <c r="I18" t="s">
+        <v>302</v>
+      </c>
+      <c r="N18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="9:14">
+      <c r="I19" t="s">
+        <v>303</v>
+      </c>
+      <c r="N19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="9:14">
+      <c r="I20" t="s">
+        <v>304</v>
+      </c>
+      <c r="N20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" spans="9:14">
+      <c r="I21" t="s">
+        <v>305</v>
+      </c>
+      <c r="N21" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="9:14">
+      <c r="I22" t="s">
+        <v>306</v>
+      </c>
+      <c r="N22" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="23" spans="9:14">
+      <c r="I23" t="s">
+        <v>307</v>
+      </c>
+      <c r="N23" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="9:14">
+      <c r="I24" t="s">
+        <v>308</v>
+      </c>
+      <c r="N24" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="25" spans="9:14">
+      <c r="I25" t="s">
+        <v>309</v>
+      </c>
+      <c r="N25" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="26" spans="9:14">
+      <c r="I26" t="s">
+        <v>310</v>
+      </c>
+      <c r="N26" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="27" spans="9:14">
+      <c r="I27" t="s">
+        <v>311</v>
+      </c>
+      <c r="N27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="9:14">
+      <c r="I28" t="s">
+        <v>312</v>
+      </c>
+      <c r="N28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="9:14">
+      <c r="I29" t="s">
+        <v>313</v>
+      </c>
+      <c r="N29" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" spans="9:14">
+      <c r="I30" t="s">
+        <v>314</v>
+      </c>
+      <c r="N30" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" spans="9:14">
+      <c r="I31" t="s">
+        <v>315</v>
+      </c>
+      <c r="N31" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" spans="9:14">
+      <c r="I32" t="s">
+        <v>316</v>
+      </c>
+      <c r="N32" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="33" spans="9:14">
+      <c r="I33" t="s">
+        <v>317</v>
+      </c>
+      <c r="N33" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="34" spans="9:14">
+      <c r="I34" t="s">
+        <v>318</v>
+      </c>
+      <c r="N34" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="9:14">
+      <c r="I35" t="s">
+        <v>319</v>
+      </c>
+      <c r="N35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="9:14">
+      <c r="I36" t="s">
+        <v>320</v>
+      </c>
+      <c r="N36" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="9:14">
+      <c r="I37" t="s">
+        <v>321</v>
+      </c>
+      <c r="N37" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="9:14">
+      <c r="I38" t="s">
+        <v>322</v>
+      </c>
+      <c r="N38" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="39" spans="9:14">
+      <c r="I39" t="s">
+        <v>323</v>
+      </c>
+      <c r="N39" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="9:14">
+      <c r="I40" t="s">
+        <v>324</v>
+      </c>
+      <c r="N40" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="41" spans="9:14">
+      <c r="I41" t="s">
+        <v>325</v>
+      </c>
+      <c r="N41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="42" spans="9:14">
+      <c r="I42" t="s">
+        <v>326</v>
+      </c>
+      <c r="N42" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="9:14">
+      <c r="I43" t="s">
+        <v>327</v>
+      </c>
+      <c r="N43" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="9:14">
+      <c r="I44" t="s">
+        <v>328</v>
+      </c>
+      <c r="N44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="9:14">
+      <c r="I45" t="s">
+        <v>329</v>
+      </c>
+      <c r="N45" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="46" spans="9:14">
+      <c r="I46" t="s">
+        <v>330</v>
+      </c>
+      <c r="N46" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="9:14">
+      <c r="I47" t="s">
+        <v>331</v>
+      </c>
+      <c r="N47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48" spans="9:14">
+      <c r="I48" t="s">
+        <v>332</v>
+      </c>
+      <c r="N48" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="9:14">
+      <c r="I49" t="s">
+        <v>333</v>
+      </c>
+      <c r="N49" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="9:14">
+      <c r="I50" t="s">
+        <v>334</v>
+      </c>
+      <c r="N50" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51" spans="9:14">
+      <c r="I51" t="s">
+        <v>335</v>
+      </c>
+      <c r="N51" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="9:14">
+      <c r="I52" t="s">
+        <v>336</v>
+      </c>
+      <c r="N52" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="53" spans="9:14">
+      <c r="I53" t="s">
+        <v>337</v>
+      </c>
+      <c r="N53" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="9:14">
+      <c r="I54" t="s">
+        <v>338</v>
+      </c>
+      <c r="N54" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="55" spans="9:14">
+      <c r="I55" t="s">
+        <v>339</v>
+      </c>
+      <c r="N55" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="56" spans="9:14">
+      <c r="I56" t="s">
+        <v>340</v>
+      </c>
+      <c r="N56" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="57" spans="9:14">
+      <c r="I57" t="s">
+        <v>341</v>
+      </c>
+      <c r="N57" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="9:14">
+      <c r="I58" t="s">
+        <v>342</v>
+      </c>
+      <c r="N58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="9:14">
+      <c r="I59" t="s">
+        <v>343</v>
+      </c>
+      <c r="N59" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="9:14">
+      <c r="I60" t="s">
+        <v>344</v>
+      </c>
+      <c r="N60" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="61" spans="9:14">
+      <c r="I61" t="s">
+        <v>345</v>
+      </c>
+      <c r="N61" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="62" spans="9:14">
+      <c r="I62" t="s">
+        <v>346</v>
+      </c>
+      <c r="N62" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="63" spans="9:14">
+      <c r="I63" t="s">
+        <v>347</v>
+      </c>
+      <c r="N63" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="64" spans="9:14">
+      <c r="I64" t="s">
+        <v>348</v>
+      </c>
+      <c r="N64" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="65" spans="9:14">
+      <c r="I65" t="s">
+        <v>349</v>
+      </c>
+      <c r="N65" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="66" spans="9:14">
+      <c r="I66" t="s">
+        <v>350</v>
+      </c>
+      <c r="N66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="9:14">
+      <c r="I67" t="s">
+        <v>351</v>
+      </c>
+      <c r="N67" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="68" spans="9:14">
+      <c r="I68" t="s">
+        <v>352</v>
+      </c>
+      <c r="N68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="9:14">
+      <c r="I69" t="s">
+        <v>353</v>
+      </c>
+      <c r="N69" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="70" spans="9:14">
+      <c r="I70" t="s">
+        <v>354</v>
+      </c>
+      <c r="N70" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" spans="9:14">
+      <c r="I71" t="s">
+        <v>355</v>
+      </c>
+      <c r="N71" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="9:14">
+      <c r="I72" t="s">
+        <v>356</v>
+      </c>
+      <c r="N72" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="73" spans="9:14">
+      <c r="I73" t="s">
+        <v>357</v>
+      </c>
+      <c r="N73" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="74" spans="9:14">
+      <c r="I74" t="s">
+        <v>358</v>
+      </c>
+      <c r="N74" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="75" spans="9:14">
+      <c r="I75" t="s">
+        <v>359</v>
+      </c>
+      <c r="N75" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="76" spans="9:14">
+      <c r="I76" t="s">
+        <v>360</v>
+      </c>
+      <c r="N76" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77" spans="9:14">
+      <c r="I77" t="s">
+        <v>361</v>
+      </c>
+      <c r="N77" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="78" spans="9:14">
+      <c r="I78" t="s">
+        <v>362</v>
+      </c>
+      <c r="N78" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="79" spans="9:14">
+      <c r="I79" t="s">
+        <v>363</v>
+      </c>
+      <c r="N79" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="9:14">
+      <c r="I80" t="s">
+        <v>364</v>
+      </c>
+      <c r="N80" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81" spans="9:14">
+      <c r="I81" t="s">
+        <v>365</v>
+      </c>
+      <c r="N81" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="82" spans="9:14">
+      <c r="I82" t="s">
+        <v>366</v>
+      </c>
+      <c r="N82" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="83" spans="9:14">
+      <c r="I83" t="s">
+        <v>367</v>
+      </c>
+      <c r="N83" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="84" spans="9:14">
+      <c r="I84" t="s">
+        <v>368</v>
+      </c>
+      <c r="N84" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="85" spans="9:14">
+      <c r="I85" t="s">
+        <v>369</v>
+      </c>
+      <c r="N85" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="86" spans="9:14">
+      <c r="I86" t="s">
+        <v>370</v>
+      </c>
+      <c r="N86" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="87" spans="9:14">
+      <c r="I87" t="s">
+        <v>371</v>
+      </c>
+      <c r="N87" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="88" spans="9:14">
+      <c r="I88" t="s">
+        <v>372</v>
+      </c>
+      <c r="N88" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="89" spans="9:14">
+      <c r="I89" t="s">
+        <v>373</v>
+      </c>
+      <c r="N89" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="90" spans="9:14">
+      <c r="I90" t="s">
+        <v>374</v>
+      </c>
+      <c r="N90" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="91" spans="9:14">
+      <c r="I91" t="s">
+        <v>375</v>
+      </c>
+      <c r="N91" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="92" spans="9:14">
+      <c r="I92" t="s">
+        <v>376</v>
+      </c>
+      <c r="N92" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="9:14">
+      <c r="I93" t="s">
+        <v>377</v>
+      </c>
+      <c r="N93" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="94" spans="9:14">
+      <c r="I94" t="s">
+        <v>378</v>
+      </c>
+      <c r="N94" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="95" spans="9:14">
+      <c r="I95" t="s">
+        <v>379</v>
+      </c>
+      <c r="N95" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="96" spans="9:14">
+      <c r="I96" t="s">
+        <v>380</v>
+      </c>
+      <c r="N96" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="97" spans="9:14">
+      <c r="I97" t="s">
+        <v>381</v>
+      </c>
+      <c r="N97" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="98" spans="9:14">
+      <c r="I98" t="s">
+        <v>382</v>
+      </c>
+      <c r="N98" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="99" spans="9:14">
+      <c r="I99" t="s">
+        <v>383</v>
+      </c>
+      <c r="N99" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="100" spans="9:14">
+      <c r="I100" t="s">
+        <v>384</v>
+      </c>
+      <c r="N100" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="101" spans="9:14">
+      <c r="I101" t="s">
+        <v>385</v>
+      </c>
+      <c r="N101" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="102" spans="9:14">
+      <c r="I102" t="s">
+        <v>386</v>
+      </c>
+      <c r="N102" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="103" spans="9:14">
+      <c r="I103" t="s">
+        <v>387</v>
+      </c>
+      <c r="N103" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="104" spans="9:14">
+      <c r="I104" t="s">
+        <v>388</v>
+      </c>
+      <c r="N104" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="105" spans="9:14">
+      <c r="I105" t="s">
+        <v>389</v>
+      </c>
+      <c r="N105" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="106" spans="9:14">
+      <c r="I106" t="s">
+        <v>390</v>
+      </c>
+      <c r="N106" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="107" spans="9:14">
+      <c r="I107" t="s">
+        <v>391</v>
+      </c>
+      <c r="N107" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="108" spans="9:14">
+      <c r="I108" t="s">
+        <v>392</v>
+      </c>
+      <c r="N108" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="109" spans="9:14">
+      <c r="I109" t="s">
+        <v>393</v>
+      </c>
+      <c r="N109" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="110" spans="9:14">
+      <c r="I110" t="s">
+        <v>394</v>
+      </c>
+      <c r="N110" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="111" spans="9:14">
+      <c r="I111" t="s">
+        <v>395</v>
+      </c>
+      <c r="N111" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="112" spans="9:14">
+      <c r="I112" t="s">
+        <v>396</v>
+      </c>
+      <c r="N112" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="113" spans="9:14">
+      <c r="I113" t="s">
+        <v>397</v>
+      </c>
+      <c r="N113" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="114" spans="9:14">
+      <c r="I114" t="s">
+        <v>398</v>
+      </c>
+      <c r="N114" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="115" spans="9:14">
+      <c r="I115" t="s">
+        <v>399</v>
+      </c>
+      <c r="N115" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="116" spans="9:14">
+      <c r="I116" t="s">
+        <v>400</v>
+      </c>
+      <c r="N116" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="117" spans="9:14">
+      <c r="I117" t="s">
+        <v>401</v>
+      </c>
+      <c r="N117" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="118" spans="9:14">
+      <c r="I118" t="s">
+        <v>402</v>
+      </c>
+      <c r="N118" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="119" spans="9:14">
+      <c r="I119" t="s">
+        <v>403</v>
+      </c>
+      <c r="N119" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="120" spans="9:14">
+      <c r="I120" t="s">
+        <v>404</v>
+      </c>
+      <c r="N120" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="121" spans="9:14">
+      <c r="I121" t="s">
+        <v>405</v>
+      </c>
+      <c r="N121" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="122" spans="9:14">
+      <c r="I122" t="s">
+        <v>406</v>
+      </c>
+      <c r="N122" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="123" spans="9:14">
+      <c r="I123" t="s">
+        <v>407</v>
+      </c>
+      <c r="N123" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="124" spans="9:14">
+      <c r="I124" t="s">
+        <v>408</v>
+      </c>
+      <c r="N124" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="125" spans="9:14">
+      <c r="I125" t="s">
+        <v>409</v>
+      </c>
+      <c r="N125" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="126" spans="9:14">
+      <c r="I126" t="s">
+        <v>410</v>
+      </c>
+      <c r="N126" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="127" spans="9:14">
+      <c r="I127" t="s">
+        <v>411</v>
+      </c>
+      <c r="N127" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="128" spans="9:14">
+      <c r="I128" t="s">
+        <v>412</v>
+      </c>
+      <c r="N128" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="129" spans="9:14">
+      <c r="I129" t="s">
+        <v>413</v>
+      </c>
+      <c r="N129" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="130" spans="9:14">
+      <c r="I130" t="s">
+        <v>414</v>
+      </c>
+      <c r="N130" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="131" spans="9:14">
+      <c r="I131" t="s">
+        <v>415</v>
+      </c>
+      <c r="N131" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="132" spans="9:14">
+      <c r="I132" t="s">
+        <v>416</v>
+      </c>
+      <c r="N132" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="133" spans="9:14">
+      <c r="I133" t="s">
+        <v>417</v>
+      </c>
+      <c r="N133" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="134" spans="9:14">
+      <c r="I134" t="s">
+        <v>418</v>
+      </c>
+      <c r="N134" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="135" spans="9:14">
+      <c r="I135" t="s">
+        <v>419</v>
+      </c>
+      <c r="N135" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="136" spans="9:14">
+      <c r="I136" t="s">
+        <v>420</v>
+      </c>
+      <c r="N136" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="137" spans="9:14">
+      <c r="I137" t="s">
+        <v>421</v>
+      </c>
+      <c r="N137" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="138" spans="9:14">
+      <c r="I138" t="s">
+        <v>422</v>
+      </c>
+      <c r="N138" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="139" spans="9:14">
+      <c r="I139" t="s">
+        <v>423</v>
+      </c>
+      <c r="N139" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="140" spans="9:14">
+      <c r="I140" t="s">
+        <v>424</v>
+      </c>
+      <c r="N140" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="141" spans="9:14">
+      <c r="I141" t="s">
+        <v>425</v>
+      </c>
+      <c r="N141" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="142" spans="9:14">
+      <c r="I142" t="s">
+        <v>426</v>
+      </c>
+      <c r="N142" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="143" spans="9:14">
+      <c r="I143" t="s">
+        <v>427</v>
+      </c>
+      <c r="N143" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="144" spans="9:14">
+      <c r="I144" t="s">
+        <v>428</v>
+      </c>
+      <c r="N144" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="145" spans="9:14">
+      <c r="I145" t="s">
+        <v>429</v>
+      </c>
+      <c r="N145" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="146" spans="9:14">
+      <c r="I146" t="s">
+        <v>430</v>
+      </c>
+      <c r="N146" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="147" spans="9:14">
+      <c r="I147" t="s">
+        <v>431</v>
+      </c>
+      <c r="N147" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="148" spans="9:14">
+      <c r="I148" t="s">
+        <v>432</v>
+      </c>
+      <c r="N148" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="149" spans="9:14">
+      <c r="I149" t="s">
+        <v>433</v>
+      </c>
+      <c r="N149" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="150" spans="9:14">
+      <c r="I150" t="s">
+        <v>434</v>
+      </c>
+      <c r="N150" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="151" spans="9:14">
+      <c r="I151" t="s">
+        <v>435</v>
+      </c>
+      <c r="N151" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="152" spans="9:14">
+      <c r="I152" t="s">
+        <v>436</v>
+      </c>
+      <c r="N152" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="153" spans="9:14">
+      <c r="I153" t="s">
+        <v>437</v>
+      </c>
+      <c r="N153" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="154" spans="9:14">
+      <c r="I154" t="s">
+        <v>438</v>
+      </c>
+      <c r="N154" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="155" spans="9:14">
+      <c r="I155" t="s">
+        <v>439</v>
+      </c>
+      <c r="N155" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="156" spans="9:14">
+      <c r="I156" t="s">
+        <v>440</v>
+      </c>
+      <c r="N156" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="157" spans="9:14">
+      <c r="I157" t="s">
+        <v>441</v>
+      </c>
+      <c r="N157" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="158" spans="9:14">
+      <c r="I158" t="s">
+        <v>442</v>
+      </c>
+      <c r="N158" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="159" spans="9:14">
+      <c r="I159" t="s">
+        <v>443</v>
+      </c>
+      <c r="N159" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="160" spans="9:14">
+      <c r="I160" t="s">
+        <v>444</v>
+      </c>
+      <c r="N160" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="161" spans="9:14">
+      <c r="I161" t="s">
+        <v>445</v>
+      </c>
+      <c r="N161" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="162" spans="9:14">
+      <c r="I162" t="s">
+        <v>446</v>
+      </c>
+      <c r="N162" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="163" spans="9:14">
+      <c r="I163" t="s">
+        <v>447</v>
+      </c>
+      <c r="N163" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="164" spans="9:14">
+      <c r="I164" t="s">
+        <v>448</v>
+      </c>
+      <c r="N164" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="165" spans="9:14">
+      <c r="I165" t="s">
+        <v>449</v>
+      </c>
+      <c r="N165" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="166" spans="9:14">
+      <c r="I166" t="s">
+        <v>450</v>
+      </c>
+      <c r="N166" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="167" spans="9:14">
+      <c r="I167" t="s">
+        <v>451</v>
+      </c>
+      <c r="N167" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="168" spans="9:14">
+      <c r="I168" t="s">
+        <v>452</v>
+      </c>
+      <c r="N168" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="169" spans="9:14">
+      <c r="I169" t="s">
+        <v>453</v>
+      </c>
+      <c r="N169" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="170" spans="9:14">
+      <c r="I170" t="s">
+        <v>454</v>
+      </c>
+      <c r="N170" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="171" spans="9:14">
+      <c r="I171" t="s">
+        <v>455</v>
+      </c>
+      <c r="N171" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="172" spans="9:14">
+      <c r="I172" t="s">
+        <v>456</v>
+      </c>
+      <c r="N172" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="173" spans="9:14">
+      <c r="I173" t="s">
+        <v>457</v>
+      </c>
+      <c r="N173" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="174" spans="9:14">
+      <c r="I174" t="s">
+        <v>458</v>
+      </c>
+      <c r="N174" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="175" spans="9:14">
+      <c r="I175" t="s">
+        <v>459</v>
+      </c>
+      <c r="N175" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="176" spans="9:14">
+      <c r="I176" t="s">
+        <v>460</v>
+      </c>
+      <c r="N176" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="177" spans="9:14">
+      <c r="I177" t="s">
+        <v>461</v>
+      </c>
+      <c r="N177" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="178" spans="9:14">
+      <c r="I178" t="s">
+        <v>462</v>
+      </c>
+      <c r="N178" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="179" spans="9:14">
+      <c r="I179" t="s">
+        <v>463</v>
+      </c>
+      <c r="N179" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="180" spans="9:14">
+      <c r="I180" t="s">
+        <v>464</v>
+      </c>
+      <c r="N180" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="181" spans="9:14">
+      <c r="I181" t="s">
+        <v>465</v>
+      </c>
+      <c r="N181" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="182" spans="9:14">
+      <c r="I182" t="s">
+        <v>466</v>
+      </c>
+      <c r="N182" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="183" spans="9:14">
+      <c r="I183" t="s">
+        <v>467</v>
+      </c>
+      <c r="N183" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="184" spans="9:14">
+      <c r="I184" t="s">
+        <v>468</v>
+      </c>
+      <c r="N184" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="185" spans="9:14">
+      <c r="I185" t="s">
+        <v>469</v>
+      </c>
+      <c r="N185" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="186" spans="9:14">
+      <c r="I186" t="s">
+        <v>470</v>
+      </c>
+      <c r="N186" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="187" spans="9:14">
+      <c r="I187" t="s">
+        <v>471</v>
+      </c>
+      <c r="N187" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="188" spans="9:14">
+      <c r="I188" t="s">
+        <v>472</v>
+      </c>
+      <c r="N188" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="189" spans="9:14">
+      <c r="I189" t="s">
+        <v>473</v>
+      </c>
+      <c r="N189" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="190" spans="9:14">
+      <c r="I190" t="s">
+        <v>474</v>
+      </c>
+      <c r="N190" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="191" spans="9:14">
+      <c r="I191" t="s">
+        <v>475</v>
+      </c>
+      <c r="N191" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="192" spans="9:14">
+      <c r="I192" t="s">
+        <v>476</v>
+      </c>
+      <c r="N192" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="193" spans="9:14">
+      <c r="I193" t="s">
+        <v>477</v>
+      </c>
+      <c r="N193" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="194" spans="9:14">
+      <c r="I194" t="s">
+        <v>478</v>
+      </c>
+      <c r="N194" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="195" spans="9:14">
+      <c r="I195" t="s">
+        <v>479</v>
+      </c>
+      <c r="N195" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="196" spans="9:14">
+      <c r="I196" t="s">
+        <v>480</v>
+      </c>
+      <c r="N196" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="197" spans="9:14">
+      <c r="I197" t="s">
+        <v>481</v>
+      </c>
+      <c r="N197" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="198" spans="9:14">
+      <c r="I198" t="s">
+        <v>482</v>
+      </c>
+      <c r="N198" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="199" spans="9:14">
+      <c r="I199" t="s">
+        <v>483</v>
+      </c>
+      <c r="N199" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="200" spans="9:14">
+      <c r="I200" t="s">
+        <v>484</v>
+      </c>
+      <c r="N200" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="201" spans="9:14">
+      <c r="I201" t="s">
+        <v>485</v>
+      </c>
+      <c r="N201" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="202" spans="9:14">
+      <c r="I202" t="s">
+        <v>486</v>
+      </c>
+      <c r="N202" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="203" spans="9:14">
+      <c r="I203" t="s">
+        <v>487</v>
+      </c>
+      <c r="N203" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="204" spans="9:14">
+      <c r="I204" t="s">
+        <v>488</v>
+      </c>
+      <c r="N204" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="205" spans="9:14">
+      <c r="I205" t="s">
+        <v>489</v>
+      </c>
+      <c r="N205" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="206" spans="9:14">
+      <c r="I206" t="s">
+        <v>490</v>
+      </c>
+      <c r="N206" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="207" spans="9:14">
+      <c r="I207" t="s">
+        <v>491</v>
+      </c>
+      <c r="N207" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="208" spans="9:14">
+      <c r="I208" t="s">
+        <v>492</v>
+      </c>
+      <c r="N208" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="209" spans="9:14">
+      <c r="I209" t="s">
+        <v>493</v>
+      </c>
+      <c r="N209" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="210" spans="9:14">
+      <c r="I210" t="s">
+        <v>494</v>
+      </c>
+      <c r="N210" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="211" spans="9:14">
+      <c r="I211" t="s">
+        <v>495</v>
+      </c>
+      <c r="N211" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="212" spans="9:14">
+      <c r="I212" t="s">
+        <v>496</v>
+      </c>
+      <c r="N212" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="213" spans="9:14">
+      <c r="I213" t="s">
+        <v>497</v>
+      </c>
+      <c r="N213" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="214" spans="9:14">
+      <c r="I214" t="s">
+        <v>498</v>
+      </c>
+      <c r="N214" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="215" spans="9:14">
+      <c r="I215" t="s">
+        <v>499</v>
+      </c>
+      <c r="N215" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="216" spans="9:14">
+      <c r="I216" t="s">
+        <v>500</v>
+      </c>
+      <c r="N216" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="217" spans="9:14">
+      <c r="I217" t="s">
+        <v>501</v>
+      </c>
+      <c r="N217" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="218" spans="9:14">
+      <c r="I218" t="s">
+        <v>502</v>
+      </c>
+      <c r="N218" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="219" spans="9:14">
+      <c r="I219" t="s">
+        <v>503</v>
+      </c>
+      <c r="N219" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="220" spans="9:14">
+      <c r="I220" t="s">
+        <v>504</v>
+      </c>
+      <c r="N220" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="221" spans="9:14">
+      <c r="I221" t="s">
+        <v>505</v>
+      </c>
+      <c r="N221" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="222" spans="9:14">
+      <c r="I222" t="s">
+        <v>506</v>
+      </c>
+      <c r="N222" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="223" spans="9:14">
+      <c r="I223" t="s">
+        <v>507</v>
+      </c>
+      <c r="N223" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="224" spans="9:14">
+      <c r="I224" t="s">
+        <v>508</v>
+      </c>
+      <c r="N224" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="225" spans="9:14">
+      <c r="I225" t="s">
+        <v>509</v>
+      </c>
+      <c r="N225" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="226" spans="9:14">
+      <c r="I226" t="s">
+        <v>510</v>
+      </c>
+      <c r="N226" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="227" spans="9:14">
+      <c r="I227" t="s">
+        <v>511</v>
+      </c>
+      <c r="N227" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="228" spans="9:14">
+      <c r="I228" t="s">
+        <v>512</v>
+      </c>
+      <c r="N228" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="229" spans="9:14">
+      <c r="I229" t="s">
+        <v>513</v>
+      </c>
+      <c r="N229" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="230" spans="9:14">
+      <c r="I230" t="s">
+        <v>514</v>
+      </c>
+      <c r="N230" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="231" spans="9:14">
+      <c r="I231" t="s">
+        <v>515</v>
+      </c>
+      <c r="N231" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="232" spans="9:14">
+      <c r="I232" t="s">
+        <v>516</v>
+      </c>
+      <c r="N232" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="233" spans="9:14">
+      <c r="I233" t="s">
+        <v>517</v>
+      </c>
+      <c r="N233" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="234" spans="9:14">
+      <c r="I234" t="s">
+        <v>518</v>
+      </c>
+      <c r="N234" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="235" spans="9:14">
+      <c r="I235" t="s">
+        <v>519</v>
+      </c>
+      <c r="N235" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="236" spans="9:14">
+      <c r="I236" t="s">
+        <v>520</v>
+      </c>
+      <c r="N236" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="237" spans="9:14">
+      <c r="I237" t="s">
+        <v>521</v>
+      </c>
+      <c r="N237" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="238" spans="9:14">
+      <c r="I238" t="s">
+        <v>522</v>
+      </c>
+      <c r="N238" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="239" spans="9:14">
+      <c r="I239" t="s">
+        <v>523</v>
+      </c>
+      <c r="N239" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="240" spans="9:14">
+      <c r="I240" t="s">
+        <v>524</v>
+      </c>
+      <c r="N240" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="241" spans="9:14">
+      <c r="I241" t="s">
+        <v>525</v>
+      </c>
+      <c r="N241" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="242" spans="9:14">
+      <c r="I242" t="s">
+        <v>526</v>
+      </c>
+      <c r="N242" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="243" spans="9:14">
+      <c r="I243" t="s">
+        <v>527</v>
+      </c>
+      <c r="N243" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="244" spans="9:14">
+      <c r="I244" t="s">
+        <v>528</v>
+      </c>
+      <c r="N244" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="245" spans="9:14">
+      <c r="I245" t="s">
+        <v>529</v>
+      </c>
+      <c r="N245" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="246" spans="9:14">
+      <c r="I246" t="s">
+        <v>530</v>
+      </c>
+      <c r="N246" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="247" spans="9:14">
+      <c r="I247" t="s">
+        <v>531</v>
+      </c>
+      <c r="N247" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="248" spans="9:14">
+      <c r="I248" t="s">
+        <v>532</v>
+      </c>
+      <c r="N248" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="249" spans="9:14">
+      <c r="I249" t="s">
+        <v>533</v>
+      </c>
+      <c r="N249" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="250" spans="9:14">
+      <c r="I250" t="s">
+        <v>534</v>
+      </c>
+      <c r="N250" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="251" spans="9:14">
+      <c r="I251" t="s">
+        <v>535</v>
+      </c>
+      <c r="N251" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="252" spans="9:14">
+      <c r="I252" t="s">
+        <v>536</v>
+      </c>
+      <c r="N252" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="253" spans="9:14">
+      <c r="I253" t="s">
+        <v>537</v>
+      </c>
+      <c r="N253" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="254" spans="9:14">
+      <c r="I254" t="s">
+        <v>538</v>
+      </c>
+      <c r="N254" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="255" spans="9:14">
+      <c r="I255" t="s">
+        <v>539</v>
+      </c>
+      <c r="N255" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="256" spans="9:14">
+      <c r="I256" t="s">
+        <v>540</v>
+      </c>
+      <c r="N256" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="257" spans="9:14">
+      <c r="I257" t="s">
+        <v>541</v>
+      </c>
+      <c r="N257" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="258" spans="9:14">
+      <c r="I258" t="s">
+        <v>542</v>
+      </c>
+      <c r="N258" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="259" spans="9:14">
+      <c r="I259" t="s">
+        <v>543</v>
+      </c>
+      <c r="N259" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="260" spans="9:14">
+      <c r="I260" t="s">
+        <v>544</v>
+      </c>
+      <c r="N260" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="261" spans="9:14">
+      <c r="I261" t="s">
+        <v>545</v>
+      </c>
+      <c r="N261" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="262" spans="9:14">
+      <c r="I262" t="s">
+        <v>546</v>
+      </c>
+      <c r="N262" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="263" spans="9:14">
+      <c r="I263" t="s">
+        <v>547</v>
+      </c>
+      <c r="N263" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="264" spans="9:14">
+      <c r="I264" t="s">
+        <v>548</v>
+      </c>
+      <c r="N264" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="265" spans="9:14">
+      <c r="I265" t="s">
+        <v>549</v>
+      </c>
+      <c r="N265" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="266" spans="9:14">
+      <c r="I266" t="s">
+        <v>550</v>
+      </c>
+      <c r="N266" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="267" spans="9:14">
+      <c r="I267" t="s">
+        <v>551</v>
+      </c>
+      <c r="N267" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="268" spans="9:14">
+      <c r="I268" t="s">
+        <v>552</v>
+      </c>
+      <c r="N268" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="269" spans="9:14">
+      <c r="I269" t="s">
+        <v>553</v>
+      </c>
+      <c r="N269" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="270" spans="9:14">
+      <c r="I270" t="s">
+        <v>554</v>
+      </c>
+      <c r="N270" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="271" spans="9:14">
+      <c r="I271" t="s">
+        <v>555</v>
+      </c>
+      <c r="N271" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="272" spans="9:14">
+      <c r="I272" t="s">
+        <v>556</v>
+      </c>
+      <c r="N272" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="273" spans="9:14">
+      <c r="I273" t="s">
+        <v>557</v>
+      </c>
+      <c r="N273" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="274" spans="9:14">
+      <c r="N274" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="275" spans="9:14">
+      <c r="N275" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="276" spans="9:14">
+      <c r="N276" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="277" spans="9:14">
+      <c r="N277" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="278" spans="9:14">
+      <c r="N278" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="279" spans="9:14">
+      <c r="N279" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="280" spans="9:14">
+      <c r="N280" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="281" spans="9:14">
+      <c r="N281" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="282" spans="9:14">
+      <c r="N282" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="283" spans="9:14">
+      <c r="N283" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="284" spans="9:14">
+      <c r="N284" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="285" spans="9:14">
+      <c r="N285" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="286" spans="9:14">
+      <c r="N286" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="287" spans="9:14">
+      <c r="N287" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="288" spans="9:14">
+      <c r="N288" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="289" spans="14:14">
+      <c r="N289" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="290" spans="14:14">
+      <c r="N290" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="291" spans="14:14">
+      <c r="N291" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="292" spans="14:14">
+      <c r="N292" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="293" spans="14:14">
+      <c r="N293" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="6:15">
-      <c r="F3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" t="s">
-        <v>283</v>
-      </c>
-      <c r="M3" t="s">
-        <v>283</v>
-      </c>
-      <c r="O3" t="s">
+    <row r="294" spans="14:14">
+      <c r="N294" t="s">
         <v>601</v>
-      </c>
-    </row>
-    <row r="4" spans="6:15">
-      <c r="H4" t="s">
-        <v>284</v>
-      </c>
-      <c r="M4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="5" spans="6:15">
-      <c r="H5" t="s">
-        <v>285</v>
-      </c>
-      <c r="M5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="6" spans="6:15">
-      <c r="H6" t="s">
-        <v>286</v>
-      </c>
-      <c r="M6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="7" spans="6:15">
-      <c r="H7" t="s">
-        <v>287</v>
-      </c>
-      <c r="M7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="6:15">
-      <c r="H8" t="s">
-        <v>288</v>
-      </c>
-      <c r="M8" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="6:15">
-      <c r="H9" t="s">
-        <v>289</v>
-      </c>
-      <c r="M9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="10" spans="6:15">
-      <c r="H10" t="s">
-        <v>290</v>
-      </c>
-      <c r="M10" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="11" spans="6:15">
-      <c r="H11" t="s">
-        <v>291</v>
-      </c>
-      <c r="M11" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="6:15">
-      <c r="H12" t="s">
-        <v>292</v>
-      </c>
-      <c r="M12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="6:15">
-      <c r="H13" t="s">
-        <v>293</v>
-      </c>
-      <c r="M13" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="6:15">
-      <c r="H14" t="s">
-        <v>294</v>
-      </c>
-      <c r="M14" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="6:15">
-      <c r="H15" t="s">
-        <v>295</v>
-      </c>
-      <c r="M15" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="16" spans="6:15">
-      <c r="H16" t="s">
-        <v>296</v>
-      </c>
-      <c r="M16" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="17" spans="8:13">
-      <c r="H17" t="s">
-        <v>297</v>
-      </c>
-      <c r="M17" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="18" spans="8:13">
-      <c r="H18" t="s">
-        <v>298</v>
-      </c>
-      <c r="M18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="19" spans="8:13">
-      <c r="H19" t="s">
-        <v>299</v>
-      </c>
-      <c r="M19" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" spans="8:13">
-      <c r="H20" t="s">
-        <v>300</v>
-      </c>
-      <c r="M20" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" spans="8:13">
-      <c r="H21" t="s">
-        <v>301</v>
-      </c>
-      <c r="M21" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="22" spans="8:13">
-      <c r="H22" t="s">
-        <v>302</v>
-      </c>
-      <c r="M22" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="23" spans="8:13">
-      <c r="H23" t="s">
-        <v>303</v>
-      </c>
-      <c r="M23" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" spans="8:13">
-      <c r="H24" t="s">
-        <v>304</v>
-      </c>
-      <c r="M24" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" spans="8:13">
-      <c r="H25" t="s">
-        <v>305</v>
-      </c>
-      <c r="M25" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" spans="8:13">
-      <c r="H26" t="s">
-        <v>306</v>
-      </c>
-      <c r="M26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="27" spans="8:13">
-      <c r="H27" t="s">
-        <v>307</v>
-      </c>
-      <c r="M27" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="28" spans="8:13">
-      <c r="H28" t="s">
-        <v>308</v>
-      </c>
-      <c r="M28" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="29" spans="8:13">
-      <c r="H29" t="s">
-        <v>309</v>
-      </c>
-      <c r="M29" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="30" spans="8:13">
-      <c r="H30" t="s">
-        <v>310</v>
-      </c>
-      <c r="M30" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="31" spans="8:13">
-      <c r="H31" t="s">
-        <v>311</v>
-      </c>
-      <c r="M31" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="32" spans="8:13">
-      <c r="H32" t="s">
-        <v>312</v>
-      </c>
-      <c r="M32" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="33" spans="8:13">
-      <c r="H33" t="s">
-        <v>313</v>
-      </c>
-      <c r="M33" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="34" spans="8:13">
-      <c r="H34" t="s">
-        <v>314</v>
-      </c>
-      <c r="M34" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="35" spans="8:13">
-      <c r="H35" t="s">
-        <v>315</v>
-      </c>
-      <c r="M35" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="36" spans="8:13">
-      <c r="H36" t="s">
-        <v>316</v>
-      </c>
-      <c r="M36" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="37" spans="8:13">
-      <c r="H37" t="s">
-        <v>317</v>
-      </c>
-      <c r="M37" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="38" spans="8:13">
-      <c r="H38" t="s">
-        <v>318</v>
-      </c>
-      <c r="M38" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="39" spans="8:13">
-      <c r="H39" t="s">
-        <v>319</v>
-      </c>
-      <c r="M39" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="40" spans="8:13">
-      <c r="H40" t="s">
-        <v>320</v>
-      </c>
-      <c r="M40" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" spans="8:13">
-      <c r="H41" t="s">
-        <v>321</v>
-      </c>
-      <c r="M41" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="42" spans="8:13">
-      <c r="H42" t="s">
-        <v>322</v>
-      </c>
-      <c r="M42" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="43" spans="8:13">
-      <c r="H43" t="s">
-        <v>323</v>
-      </c>
-      <c r="M43" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="44" spans="8:13">
-      <c r="H44" t="s">
-        <v>324</v>
-      </c>
-      <c r="M44" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="45" spans="8:13">
-      <c r="H45" t="s">
-        <v>325</v>
-      </c>
-      <c r="M45" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="46" spans="8:13">
-      <c r="H46" t="s">
-        <v>326</v>
-      </c>
-      <c r="M46" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="47" spans="8:13">
-      <c r="H47" t="s">
-        <v>327</v>
-      </c>
-      <c r="M47" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="48" spans="8:13">
-      <c r="H48" t="s">
-        <v>328</v>
-      </c>
-      <c r="M48" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="49" spans="8:13">
-      <c r="H49" t="s">
-        <v>329</v>
-      </c>
-      <c r="M49" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="50" spans="8:13">
-      <c r="H50" t="s">
-        <v>330</v>
-      </c>
-      <c r="M50" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="51" spans="8:13">
-      <c r="H51" t="s">
-        <v>331</v>
-      </c>
-      <c r="M51" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="52" spans="8:13">
-      <c r="H52" t="s">
-        <v>332</v>
-      </c>
-      <c r="M52" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="53" spans="8:13">
-      <c r="H53" t="s">
-        <v>333</v>
-      </c>
-      <c r="M53" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="54" spans="8:13">
-      <c r="H54" t="s">
-        <v>334</v>
-      </c>
-      <c r="M54" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="55" spans="8:13">
-      <c r="H55" t="s">
-        <v>335</v>
-      </c>
-      <c r="M55" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="56" spans="8:13">
-      <c r="H56" t="s">
-        <v>336</v>
-      </c>
-      <c r="M56" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="57" spans="8:13">
-      <c r="H57" t="s">
-        <v>337</v>
-      </c>
-      <c r="M57" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="58" spans="8:13">
-      <c r="H58" t="s">
-        <v>338</v>
-      </c>
-      <c r="M58" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="59" spans="8:13">
-      <c r="H59" t="s">
-        <v>339</v>
-      </c>
-      <c r="M59" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="60" spans="8:13">
-      <c r="H60" t="s">
-        <v>340</v>
-      </c>
-      <c r="M60" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="61" spans="8:13">
-      <c r="H61" t="s">
-        <v>341</v>
-      </c>
-      <c r="M61" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="62" spans="8:13">
-      <c r="H62" t="s">
-        <v>342</v>
-      </c>
-      <c r="M62" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="63" spans="8:13">
-      <c r="H63" t="s">
-        <v>343</v>
-      </c>
-      <c r="M63" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="64" spans="8:13">
-      <c r="H64" t="s">
-        <v>344</v>
-      </c>
-      <c r="M64" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="65" spans="8:13">
-      <c r="H65" t="s">
-        <v>345</v>
-      </c>
-      <c r="M65" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="66" spans="8:13">
-      <c r="H66" t="s">
-        <v>346</v>
-      </c>
-      <c r="M66" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="67" spans="8:13">
-      <c r="H67" t="s">
-        <v>347</v>
-      </c>
-      <c r="M67" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="68" spans="8:13">
-      <c r="H68" t="s">
-        <v>348</v>
-      </c>
-      <c r="M68" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="69" spans="8:13">
-      <c r="H69" t="s">
-        <v>349</v>
-      </c>
-      <c r="M69" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="70" spans="8:13">
-      <c r="H70" t="s">
-        <v>350</v>
-      </c>
-      <c r="M70" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="71" spans="8:13">
-      <c r="H71" t="s">
-        <v>351</v>
-      </c>
-      <c r="M71" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="72" spans="8:13">
-      <c r="H72" t="s">
-        <v>352</v>
-      </c>
-      <c r="M72" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="73" spans="8:13">
-      <c r="H73" t="s">
-        <v>353</v>
-      </c>
-      <c r="M73" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="74" spans="8:13">
-      <c r="H74" t="s">
-        <v>354</v>
-      </c>
-      <c r="M74" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="75" spans="8:13">
-      <c r="H75" t="s">
-        <v>355</v>
-      </c>
-      <c r="M75" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="76" spans="8:13">
-      <c r="H76" t="s">
-        <v>356</v>
-      </c>
-      <c r="M76" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="77" spans="8:13">
-      <c r="H77" t="s">
-        <v>357</v>
-      </c>
-      <c r="M77" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="78" spans="8:13">
-      <c r="H78" t="s">
-        <v>358</v>
-      </c>
-      <c r="M78" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="8:13">
-      <c r="H79" t="s">
-        <v>359</v>
-      </c>
-      <c r="M79" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="80" spans="8:13">
-      <c r="H80" t="s">
-        <v>360</v>
-      </c>
-      <c r="M80" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="81" spans="8:13">
-      <c r="H81" t="s">
-        <v>361</v>
-      </c>
-      <c r="M81" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="82" spans="8:13">
-      <c r="H82" t="s">
-        <v>362</v>
-      </c>
-      <c r="M82" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="83" spans="8:13">
-      <c r="H83" t="s">
-        <v>363</v>
-      </c>
-      <c r="M83" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="84" spans="8:13">
-      <c r="H84" t="s">
-        <v>364</v>
-      </c>
-      <c r="M84" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="85" spans="8:13">
-      <c r="H85" t="s">
-        <v>365</v>
-      </c>
-      <c r="M85" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="86" spans="8:13">
-      <c r="H86" t="s">
-        <v>366</v>
-      </c>
-      <c r="M86" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="87" spans="8:13">
-      <c r="H87" t="s">
-        <v>367</v>
-      </c>
-      <c r="M87" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="88" spans="8:13">
-      <c r="H88" t="s">
-        <v>368</v>
-      </c>
-      <c r="M88" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="89" spans="8:13">
-      <c r="H89" t="s">
-        <v>369</v>
-      </c>
-      <c r="M89" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="90" spans="8:13">
-      <c r="H90" t="s">
-        <v>370</v>
-      </c>
-      <c r="M90" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="91" spans="8:13">
-      <c r="H91" t="s">
-        <v>371</v>
-      </c>
-      <c r="M91" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="92" spans="8:13">
-      <c r="H92" t="s">
-        <v>372</v>
-      </c>
-      <c r="M92" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="93" spans="8:13">
-      <c r="H93" t="s">
-        <v>373</v>
-      </c>
-      <c r="M93" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="94" spans="8:13">
-      <c r="H94" t="s">
-        <v>374</v>
-      </c>
-      <c r="M94" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="95" spans="8:13">
-      <c r="H95" t="s">
-        <v>375</v>
-      </c>
-      <c r="M95" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="96" spans="8:13">
-      <c r="H96" t="s">
-        <v>376</v>
-      </c>
-      <c r="M96" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="97" spans="8:13">
-      <c r="H97" t="s">
-        <v>377</v>
-      </c>
-      <c r="M97" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="98" spans="8:13">
-      <c r="H98" t="s">
-        <v>378</v>
-      </c>
-      <c r="M98" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="99" spans="8:13">
-      <c r="H99" t="s">
-        <v>379</v>
-      </c>
-      <c r="M99" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="100" spans="8:13">
-      <c r="H100" t="s">
-        <v>380</v>
-      </c>
-      <c r="M100" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="101" spans="8:13">
-      <c r="H101" t="s">
-        <v>381</v>
-      </c>
-      <c r="M101" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="102" spans="8:13">
-      <c r="H102" t="s">
-        <v>382</v>
-      </c>
-      <c r="M102" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="103" spans="8:13">
-      <c r="H103" t="s">
-        <v>383</v>
-      </c>
-      <c r="M103" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="104" spans="8:13">
-      <c r="H104" t="s">
-        <v>384</v>
-      </c>
-      <c r="M104" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="105" spans="8:13">
-      <c r="H105" t="s">
-        <v>385</v>
-      </c>
-      <c r="M105" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="106" spans="8:13">
-      <c r="H106" t="s">
-        <v>386</v>
-      </c>
-      <c r="M106" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="107" spans="8:13">
-      <c r="H107" t="s">
-        <v>387</v>
-      </c>
-      <c r="M107" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="108" spans="8:13">
-      <c r="H108" t="s">
-        <v>388</v>
-      </c>
-      <c r="M108" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="109" spans="8:13">
-      <c r="H109" t="s">
-        <v>389</v>
-      </c>
-      <c r="M109" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="110" spans="8:13">
-      <c r="H110" t="s">
-        <v>390</v>
-      </c>
-      <c r="M110" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="111" spans="8:13">
-      <c r="H111" t="s">
-        <v>391</v>
-      </c>
-      <c r="M111" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="112" spans="8:13">
-      <c r="H112" t="s">
-        <v>392</v>
-      </c>
-      <c r="M112" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="113" spans="8:13">
-      <c r="H113" t="s">
-        <v>393</v>
-      </c>
-      <c r="M113" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="114" spans="8:13">
-      <c r="H114" t="s">
-        <v>394</v>
-      </c>
-      <c r="M114" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="115" spans="8:13">
-      <c r="H115" t="s">
-        <v>395</v>
-      </c>
-      <c r="M115" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="116" spans="8:13">
-      <c r="H116" t="s">
-        <v>396</v>
-      </c>
-      <c r="M116" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="117" spans="8:13">
-      <c r="H117" t="s">
-        <v>397</v>
-      </c>
-      <c r="M117" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="118" spans="8:13">
-      <c r="H118" t="s">
-        <v>398</v>
-      </c>
-      <c r="M118" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="119" spans="8:13">
-      <c r="H119" t="s">
-        <v>399</v>
-      </c>
-      <c r="M119" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="120" spans="8:13">
-      <c r="H120" t="s">
-        <v>400</v>
-      </c>
-      <c r="M120" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="121" spans="8:13">
-      <c r="H121" t="s">
-        <v>401</v>
-      </c>
-      <c r="M121" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="122" spans="8:13">
-      <c r="H122" t="s">
-        <v>402</v>
-      </c>
-      <c r="M122" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="123" spans="8:13">
-      <c r="H123" t="s">
-        <v>403</v>
-      </c>
-      <c r="M123" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="124" spans="8:13">
-      <c r="H124" t="s">
-        <v>404</v>
-      </c>
-      <c r="M124" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="125" spans="8:13">
-      <c r="H125" t="s">
-        <v>405</v>
-      </c>
-      <c r="M125" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="126" spans="8:13">
-      <c r="H126" t="s">
-        <v>406</v>
-      </c>
-      <c r="M126" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="127" spans="8:13">
-      <c r="H127" t="s">
-        <v>407</v>
-      </c>
-      <c r="M127" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="128" spans="8:13">
-      <c r="H128" t="s">
-        <v>408</v>
-      </c>
-      <c r="M128" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="129" spans="8:13">
-      <c r="H129" t="s">
-        <v>409</v>
-      </c>
-      <c r="M129" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="130" spans="8:13">
-      <c r="H130" t="s">
-        <v>410</v>
-      </c>
-      <c r="M130" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="8:13">
-      <c r="H131" t="s">
-        <v>411</v>
-      </c>
-      <c r="M131" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="132" spans="8:13">
-      <c r="H132" t="s">
-        <v>412</v>
-      </c>
-      <c r="M132" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="133" spans="8:13">
-      <c r="H133" t="s">
-        <v>413</v>
-      </c>
-      <c r="M133" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="134" spans="8:13">
-      <c r="H134" t="s">
-        <v>414</v>
-      </c>
-      <c r="M134" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="135" spans="8:13">
-      <c r="H135" t="s">
-        <v>415</v>
-      </c>
-      <c r="M135" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="136" spans="8:13">
-      <c r="H136" t="s">
-        <v>416</v>
-      </c>
-      <c r="M136" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="137" spans="8:13">
-      <c r="H137" t="s">
-        <v>417</v>
-      </c>
-      <c r="M137" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="138" spans="8:13">
-      <c r="H138" t="s">
-        <v>418</v>
-      </c>
-      <c r="M138" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="139" spans="8:13">
-      <c r="H139" t="s">
-        <v>419</v>
-      </c>
-      <c r="M139" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="140" spans="8:13">
-      <c r="H140" t="s">
-        <v>420</v>
-      </c>
-      <c r="M140" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="141" spans="8:13">
-      <c r="H141" t="s">
-        <v>421</v>
-      </c>
-      <c r="M141" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="142" spans="8:13">
-      <c r="H142" t="s">
-        <v>422</v>
-      </c>
-      <c r="M142" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="8:13">
-      <c r="H143" t="s">
-        <v>423</v>
-      </c>
-      <c r="M143" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="144" spans="8:13">
-      <c r="H144" t="s">
-        <v>424</v>
-      </c>
-      <c r="M144" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="145" spans="8:13">
-      <c r="H145" t="s">
-        <v>425</v>
-      </c>
-      <c r="M145" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="146" spans="8:13">
-      <c r="H146" t="s">
-        <v>426</v>
-      </c>
-      <c r="M146" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="147" spans="8:13">
-      <c r="H147" t="s">
-        <v>427</v>
-      </c>
-      <c r="M147" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="148" spans="8:13">
-      <c r="H148" t="s">
-        <v>428</v>
-      </c>
-      <c r="M148" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="149" spans="8:13">
-      <c r="H149" t="s">
-        <v>429</v>
-      </c>
-      <c r="M149" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="150" spans="8:13">
-      <c r="H150" t="s">
-        <v>430</v>
-      </c>
-      <c r="M150" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="151" spans="8:13">
-      <c r="H151" t="s">
-        <v>431</v>
-      </c>
-      <c r="M151" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="152" spans="8:13">
-      <c r="H152" t="s">
-        <v>432</v>
-      </c>
-      <c r="M152" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="153" spans="8:13">
-      <c r="H153" t="s">
-        <v>433</v>
-      </c>
-      <c r="M153" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="154" spans="8:13">
-      <c r="H154" t="s">
-        <v>434</v>
-      </c>
-      <c r="M154" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="155" spans="8:13">
-      <c r="H155" t="s">
-        <v>435</v>
-      </c>
-      <c r="M155" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="156" spans="8:13">
-      <c r="H156" t="s">
-        <v>436</v>
-      </c>
-      <c r="M156" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="157" spans="8:13">
-      <c r="H157" t="s">
-        <v>437</v>
-      </c>
-      <c r="M157" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="158" spans="8:13">
-      <c r="H158" t="s">
-        <v>438</v>
-      </c>
-      <c r="M158" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="159" spans="8:13">
-      <c r="H159" t="s">
-        <v>439</v>
-      </c>
-      <c r="M159" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="160" spans="8:13">
-      <c r="H160" t="s">
-        <v>440</v>
-      </c>
-      <c r="M160" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="161" spans="8:13">
-      <c r="H161" t="s">
-        <v>441</v>
-      </c>
-      <c r="M161" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="162" spans="8:13">
-      <c r="H162" t="s">
-        <v>442</v>
-      </c>
-      <c r="M162" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="163" spans="8:13">
-      <c r="H163" t="s">
-        <v>443</v>
-      </c>
-      <c r="M163" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="164" spans="8:13">
-      <c r="H164" t="s">
-        <v>444</v>
-      </c>
-      <c r="M164" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="165" spans="8:13">
-      <c r="H165" t="s">
-        <v>445</v>
-      </c>
-      <c r="M165" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="166" spans="8:13">
-      <c r="H166" t="s">
-        <v>446</v>
-      </c>
-      <c r="M166" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="167" spans="8:13">
-      <c r="H167" t="s">
-        <v>447</v>
-      </c>
-      <c r="M167" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="168" spans="8:13">
-      <c r="H168" t="s">
-        <v>448</v>
-      </c>
-      <c r="M168" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="169" spans="8:13">
-      <c r="H169" t="s">
-        <v>449</v>
-      </c>
-      <c r="M169" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="170" spans="8:13">
-      <c r="H170" t="s">
-        <v>450</v>
-      </c>
-      <c r="M170" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="171" spans="8:13">
-      <c r="H171" t="s">
-        <v>451</v>
-      </c>
-      <c r="M171" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="172" spans="8:13">
-      <c r="H172" t="s">
-        <v>452</v>
-      </c>
-      <c r="M172" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="173" spans="8:13">
-      <c r="H173" t="s">
-        <v>453</v>
-      </c>
-      <c r="M173" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="174" spans="8:13">
-      <c r="H174" t="s">
-        <v>454</v>
-      </c>
-      <c r="M174" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="175" spans="8:13">
-      <c r="H175" t="s">
-        <v>455</v>
-      </c>
-      <c r="M175" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="176" spans="8:13">
-      <c r="H176" t="s">
-        <v>456</v>
-      </c>
-      <c r="M176" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="177" spans="8:13">
-      <c r="H177" t="s">
-        <v>457</v>
-      </c>
-      <c r="M177" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="178" spans="8:13">
-      <c r="H178" t="s">
-        <v>458</v>
-      </c>
-      <c r="M178" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="179" spans="8:13">
-      <c r="H179" t="s">
-        <v>459</v>
-      </c>
-      <c r="M179" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="180" spans="8:13">
-      <c r="H180" t="s">
-        <v>460</v>
-      </c>
-      <c r="M180" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="181" spans="8:13">
-      <c r="H181" t="s">
-        <v>461</v>
-      </c>
-      <c r="M181" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="182" spans="8:13">
-      <c r="H182" t="s">
-        <v>462</v>
-      </c>
-      <c r="M182" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="183" spans="8:13">
-      <c r="H183" t="s">
-        <v>463</v>
-      </c>
-      <c r="M183" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="184" spans="8:13">
-      <c r="H184" t="s">
-        <v>464</v>
-      </c>
-      <c r="M184" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="185" spans="8:13">
-      <c r="H185" t="s">
-        <v>465</v>
-      </c>
-      <c r="M185" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="186" spans="8:13">
-      <c r="H186" t="s">
-        <v>466</v>
-      </c>
-      <c r="M186" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="187" spans="8:13">
-      <c r="H187" t="s">
-        <v>467</v>
-      </c>
-      <c r="M187" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="188" spans="8:13">
-      <c r="H188" t="s">
-        <v>468</v>
-      </c>
-      <c r="M188" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="189" spans="8:13">
-      <c r="H189" t="s">
-        <v>469</v>
-      </c>
-      <c r="M189" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="190" spans="8:13">
-      <c r="H190" t="s">
-        <v>470</v>
-      </c>
-      <c r="M190" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="191" spans="8:13">
-      <c r="H191" t="s">
-        <v>471</v>
-      </c>
-      <c r="M191" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="192" spans="8:13">
-      <c r="H192" t="s">
-        <v>472</v>
-      </c>
-      <c r="M192" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="193" spans="8:13">
-      <c r="H193" t="s">
-        <v>473</v>
-      </c>
-      <c r="M193" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="194" spans="8:13">
-      <c r="H194" t="s">
-        <v>474</v>
-      </c>
-      <c r="M194" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="195" spans="8:13">
-      <c r="H195" t="s">
-        <v>475</v>
-      </c>
-      <c r="M195" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="196" spans="8:13">
-      <c r="H196" t="s">
-        <v>476</v>
-      </c>
-      <c r="M196" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="197" spans="8:13">
-      <c r="H197" t="s">
-        <v>477</v>
-      </c>
-      <c r="M197" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="198" spans="8:13">
-      <c r="H198" t="s">
-        <v>478</v>
-      </c>
-      <c r="M198" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="199" spans="8:13">
-      <c r="H199" t="s">
-        <v>479</v>
-      </c>
-      <c r="M199" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="200" spans="8:13">
-      <c r="H200" t="s">
-        <v>480</v>
-      </c>
-      <c r="M200" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="201" spans="8:13">
-      <c r="H201" t="s">
-        <v>481</v>
-      </c>
-      <c r="M201" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="202" spans="8:13">
-      <c r="H202" t="s">
-        <v>482</v>
-      </c>
-      <c r="M202" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="203" spans="8:13">
-      <c r="H203" t="s">
-        <v>483</v>
-      </c>
-      <c r="M203" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="204" spans="8:13">
-      <c r="H204" t="s">
-        <v>484</v>
-      </c>
-      <c r="M204" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="205" spans="8:13">
-      <c r="H205" t="s">
-        <v>485</v>
-      </c>
-      <c r="M205" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="206" spans="8:13">
-      <c r="H206" t="s">
-        <v>486</v>
-      </c>
-      <c r="M206" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="207" spans="8:13">
-      <c r="H207" t="s">
-        <v>487</v>
-      </c>
-      <c r="M207" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="208" spans="8:13">
-      <c r="H208" t="s">
-        <v>488</v>
-      </c>
-      <c r="M208" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="209" spans="8:13">
-      <c r="H209" t="s">
-        <v>489</v>
-      </c>
-      <c r="M209" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="210" spans="8:13">
-      <c r="H210" t="s">
-        <v>490</v>
-      </c>
-      <c r="M210" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="211" spans="8:13">
-      <c r="H211" t="s">
-        <v>491</v>
-      </c>
-      <c r="M211" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="212" spans="8:13">
-      <c r="H212" t="s">
-        <v>492</v>
-      </c>
-      <c r="M212" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="213" spans="8:13">
-      <c r="H213" t="s">
-        <v>493</v>
-      </c>
-      <c r="M213" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="214" spans="8:13">
-      <c r="H214" t="s">
-        <v>494</v>
-      </c>
-      <c r="M214" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="215" spans="8:13">
-      <c r="H215" t="s">
-        <v>495</v>
-      </c>
-      <c r="M215" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="216" spans="8:13">
-      <c r="H216" t="s">
-        <v>496</v>
-      </c>
-      <c r="M216" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="217" spans="8:13">
-      <c r="H217" t="s">
-        <v>497</v>
-      </c>
-      <c r="M217" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="218" spans="8:13">
-      <c r="H218" t="s">
-        <v>498</v>
-      </c>
-      <c r="M218" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="219" spans="8:13">
-      <c r="H219" t="s">
-        <v>499</v>
-      </c>
-      <c r="M219" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="220" spans="8:13">
-      <c r="H220" t="s">
-        <v>500</v>
-      </c>
-      <c r="M220" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="221" spans="8:13">
-      <c r="H221" t="s">
-        <v>501</v>
-      </c>
-      <c r="M221" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="222" spans="8:13">
-      <c r="H222" t="s">
-        <v>502</v>
-      </c>
-      <c r="M222" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="223" spans="8:13">
-      <c r="H223" t="s">
-        <v>503</v>
-      </c>
-      <c r="M223" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="224" spans="8:13">
-      <c r="H224" t="s">
-        <v>504</v>
-      </c>
-      <c r="M224" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="225" spans="8:13">
-      <c r="H225" t="s">
-        <v>505</v>
-      </c>
-      <c r="M225" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="226" spans="8:13">
-      <c r="H226" t="s">
-        <v>506</v>
-      </c>
-      <c r="M226" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="227" spans="8:13">
-      <c r="H227" t="s">
-        <v>507</v>
-      </c>
-      <c r="M227" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="228" spans="8:13">
-      <c r="H228" t="s">
-        <v>508</v>
-      </c>
-      <c r="M228" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="229" spans="8:13">
-      <c r="H229" t="s">
-        <v>509</v>
-      </c>
-      <c r="M229" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="230" spans="8:13">
-      <c r="H230" t="s">
-        <v>510</v>
-      </c>
-      <c r="M230" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="231" spans="8:13">
-      <c r="H231" t="s">
-        <v>511</v>
-      </c>
-      <c r="M231" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="232" spans="8:13">
-      <c r="H232" t="s">
-        <v>512</v>
-      </c>
-      <c r="M232" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="233" spans="8:13">
-      <c r="H233" t="s">
-        <v>513</v>
-      </c>
-      <c r="M233" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="234" spans="8:13">
-      <c r="H234" t="s">
-        <v>514</v>
-      </c>
-      <c r="M234" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="235" spans="8:13">
-      <c r="H235" t="s">
-        <v>515</v>
-      </c>
-      <c r="M235" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="236" spans="8:13">
-      <c r="H236" t="s">
-        <v>516</v>
-      </c>
-      <c r="M236" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="237" spans="8:13">
-      <c r="H237" t="s">
-        <v>517</v>
-      </c>
-      <c r="M237" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="238" spans="8:13">
-      <c r="H238" t="s">
-        <v>518</v>
-      </c>
-      <c r="M238" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="239" spans="8:13">
-      <c r="H239" t="s">
-        <v>519</v>
-      </c>
-      <c r="M239" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="240" spans="8:13">
-      <c r="H240" t="s">
-        <v>520</v>
-      </c>
-      <c r="M240" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="241" spans="8:13">
-      <c r="H241" t="s">
-        <v>521</v>
-      </c>
-      <c r="M241" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="242" spans="8:13">
-      <c r="H242" t="s">
-        <v>522</v>
-      </c>
-      <c r="M242" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="243" spans="8:13">
-      <c r="H243" t="s">
-        <v>523</v>
-      </c>
-      <c r="M243" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="244" spans="8:13">
-      <c r="H244" t="s">
-        <v>524</v>
-      </c>
-      <c r="M244" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="245" spans="8:13">
-      <c r="H245" t="s">
-        <v>525</v>
-      </c>
-      <c r="M245" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="246" spans="8:13">
-      <c r="H246" t="s">
-        <v>526</v>
-      </c>
-      <c r="M246" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="247" spans="8:13">
-      <c r="H247" t="s">
-        <v>527</v>
-      </c>
-      <c r="M247" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="248" spans="8:13">
-      <c r="H248" t="s">
-        <v>528</v>
-      </c>
-      <c r="M248" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="249" spans="8:13">
-      <c r="H249" t="s">
-        <v>529</v>
-      </c>
-      <c r="M249" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="250" spans="8:13">
-      <c r="H250" t="s">
-        <v>530</v>
-      </c>
-      <c r="M250" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="251" spans="8:13">
-      <c r="H251" t="s">
-        <v>531</v>
-      </c>
-      <c r="M251" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="252" spans="8:13">
-      <c r="H252" t="s">
-        <v>532</v>
-      </c>
-      <c r="M252" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="253" spans="8:13">
-      <c r="H253" t="s">
-        <v>533</v>
-      </c>
-      <c r="M253" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="254" spans="8:13">
-      <c r="H254" t="s">
-        <v>534</v>
-      </c>
-      <c r="M254" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="255" spans="8:13">
-      <c r="H255" t="s">
-        <v>535</v>
-      </c>
-      <c r="M255" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="256" spans="8:13">
-      <c r="H256" t="s">
-        <v>536</v>
-      </c>
-      <c r="M256" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="257" spans="8:13">
-      <c r="H257" t="s">
-        <v>537</v>
-      </c>
-      <c r="M257" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="258" spans="8:13">
-      <c r="H258" t="s">
-        <v>538</v>
-      </c>
-      <c r="M258" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="259" spans="8:13">
-      <c r="H259" t="s">
-        <v>539</v>
-      </c>
-      <c r="M259" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="260" spans="8:13">
-      <c r="H260" t="s">
-        <v>540</v>
-      </c>
-      <c r="M260" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="261" spans="8:13">
-      <c r="H261" t="s">
-        <v>541</v>
-      </c>
-      <c r="M261" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="262" spans="8:13">
-      <c r="H262" t="s">
-        <v>542</v>
-      </c>
-      <c r="M262" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="263" spans="8:13">
-      <c r="H263" t="s">
-        <v>543</v>
-      </c>
-      <c r="M263" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="264" spans="8:13">
-      <c r="H264" t="s">
-        <v>544</v>
-      </c>
-      <c r="M264" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="265" spans="8:13">
-      <c r="H265" t="s">
-        <v>545</v>
-      </c>
-      <c r="M265" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="266" spans="8:13">
-      <c r="H266" t="s">
-        <v>546</v>
-      </c>
-      <c r="M266" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="267" spans="8:13">
-      <c r="H267" t="s">
-        <v>547</v>
-      </c>
-      <c r="M267" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="268" spans="8:13">
-      <c r="H268" t="s">
-        <v>548</v>
-      </c>
-      <c r="M268" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="269" spans="8:13">
-      <c r="H269" t="s">
-        <v>549</v>
-      </c>
-      <c r="M269" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="270" spans="8:13">
-      <c r="H270" t="s">
-        <v>550</v>
-      </c>
-      <c r="M270" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="271" spans="8:13">
-      <c r="H271" t="s">
-        <v>551</v>
-      </c>
-      <c r="M271" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="272" spans="8:13">
-      <c r="H272" t="s">
-        <v>552</v>
-      </c>
-      <c r="M272" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="273" spans="8:13">
-      <c r="H273" t="s">
-        <v>553</v>
-      </c>
-      <c r="M273" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="274" spans="8:13">
-      <c r="M274" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="275" spans="8:13">
-      <c r="M275" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="276" spans="8:13">
-      <c r="M276" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="277" spans="8:13">
-      <c r="M277" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="278" spans="8:13">
-      <c r="M278" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="279" spans="8:13">
-      <c r="M279" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="280" spans="8:13">
-      <c r="M280" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="281" spans="8:13">
-      <c r="M281" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="282" spans="8:13">
-      <c r="M282" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="283" spans="8:13">
-      <c r="M283" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="284" spans="8:13">
-      <c r="M284" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="285" spans="8:13">
-      <c r="M285" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="286" spans="8:13">
-      <c r="M286" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="287" spans="8:13">
-      <c r="M287" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="288" spans="8:13">
-      <c r="M288" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="289" spans="13:13">
-      <c r="M289" t="s">
-        <v>594</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000044/metadata_template_ERC000044.xlsx
+++ b/templates/ERC000044/metadata_template_ERC000044.xlsx
@@ -17,25 +17,25 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="clinicalsetting">'cv_sample'!$H$1:$H$2</definedName>
-    <definedName name="countryoftravel">'cv_sample'!$I$1:$I$273</definedName>
+    <definedName name="clinicalsetting">'cv_sample'!$I$1:$I$2</definedName>
+    <definedName name="countryoftravel">'cv_sample'!$J$1:$J$273</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$294</definedName>
-    <definedName name="hostdiseaseoutcome">'cv_sample'!$P$1:$P$3</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
+    <definedName name="hostdiseaseoutcome">'cv_sample'!$Q$1:$Q$3</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="travelrelation">'cv_sample'!$G$1:$G$3</definedName>
+    <definedName name="travelrelation">'cv_sample'!$H$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="625">
   <si>
     <t>alias</t>
   </si>
@@ -851,6 +851,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3427,13 +3433,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3453,13 +3459,13 @@
         <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>558</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>560</v>
@@ -3474,13 +3480,13 @@
         <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>602</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>604</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>611</v>
@@ -3500,8 +3506,11 @@
       <c r="V1" s="1" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" ht="150" customHeight="1">
+      <c r="W1" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3521,13 +3530,13 @@
         <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>559</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>561</v>
@@ -3542,13 +3551,13 @@
         <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>605</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>612</v>
@@ -3568,22 +3577,25 @@
       <c r="V2" s="2" t="s">
         <v>622</v>
       </c>
+      <c r="W2" s="2" t="s">
+        <v>624</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>travelrelation</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>clinicalsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>countryoftravel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
       <formula1>hostdiseaseoutcome</formula1>
     </dataValidation>
   </dataValidations>
@@ -3593,2320 +3605,2320 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:P294"/>
+  <dimension ref="H1:Q294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:16">
-      <c r="G1" t="s">
-        <v>276</v>
-      </c>
+    <row r="1" spans="8:17">
       <c r="H1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>285</v>
-      </c>
-      <c r="N1" t="s">
-        <v>285</v>
-      </c>
-      <c r="P1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="2" spans="7:16">
-      <c r="G2" t="s">
-        <v>277</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="J1" t="s">
+        <v>287</v>
+      </c>
+      <c r="O1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="2" spans="8:17">
       <c r="H2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>286</v>
-      </c>
-      <c r="N2" t="s">
-        <v>286</v>
-      </c>
-      <c r="P2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="3" spans="7:16">
-      <c r="G3" t="s">
-        <v>278</v>
-      </c>
-      <c r="I3" t="s">
-        <v>287</v>
-      </c>
-      <c r="N3" t="s">
-        <v>287</v>
-      </c>
-      <c r="P3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="4" spans="7:16">
-      <c r="I4" t="s">
+        <v>284</v>
+      </c>
+      <c r="J2" t="s">
         <v>288</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O2" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="5" spans="7:16">
-      <c r="I5" t="s">
+      <c r="Q2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3" spans="8:17">
+      <c r="H3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J3" t="s">
         <v>289</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O3" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="6" spans="7:16">
-      <c r="I6" t="s">
+      <c r="Q3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="4" spans="8:17">
+      <c r="J4" t="s">
         <v>290</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="7:16">
-      <c r="I7" t="s">
+    <row r="5" spans="8:17">
+      <c r="J5" t="s">
         <v>291</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="7:16">
-      <c r="I8" t="s">
+    <row r="6" spans="8:17">
+      <c r="J6" t="s">
         <v>292</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="7:16">
-      <c r="I9" t="s">
+    <row r="7" spans="8:17">
+      <c r="J7" t="s">
         <v>293</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="7:16">
-      <c r="I10" t="s">
+    <row r="8" spans="8:17">
+      <c r="J8" t="s">
         <v>294</v>
       </c>
-      <c r="N10" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="11" spans="7:16">
-      <c r="I11" t="s">
+      <c r="O8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="8:17">
+      <c r="J9" t="s">
         <v>295</v>
       </c>
-      <c r="N11" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="7:16">
-      <c r="I12" t="s">
+      <c r="O9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="8:17">
+      <c r="J10" t="s">
         <v>296</v>
       </c>
-      <c r="N12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="13" spans="7:16">
-      <c r="I13" t="s">
+      <c r="O10" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" spans="8:17">
+      <c r="J11" t="s">
         <v>297</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O11" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="14" spans="7:16">
-      <c r="I14" t="s">
+    <row r="12" spans="8:17">
+      <c r="J12" t="s">
         <v>298</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O12" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="15" spans="7:16">
-      <c r="I15" t="s">
+    <row r="13" spans="8:17">
+      <c r="J13" t="s">
         <v>299</v>
       </c>
-      <c r="N15" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="16" spans="7:16">
-      <c r="I16" t="s">
+      <c r="O13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="8:17">
+      <c r="J14" t="s">
         <v>300</v>
       </c>
-      <c r="N16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="17" spans="9:14">
-      <c r="I17" t="s">
+      <c r="O14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="15" spans="8:17">
+      <c r="J15" t="s">
         <v>301</v>
       </c>
-      <c r="N17" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="18" spans="9:14">
-      <c r="I18" t="s">
+      <c r="O15" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="16" spans="8:17">
+      <c r="J16" t="s">
         <v>302</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="9:14">
-      <c r="I19" t="s">
+    <row r="17" spans="10:15">
+      <c r="J17" t="s">
         <v>303</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O17" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="9:14">
-      <c r="I20" t="s">
+    <row r="18" spans="10:15">
+      <c r="J18" t="s">
         <v>304</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O18" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="9:14">
-      <c r="I21" t="s">
+    <row r="19" spans="10:15">
+      <c r="J19" t="s">
         <v>305</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O19" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="9:14">
-      <c r="I22" t="s">
+    <row r="20" spans="10:15">
+      <c r="J20" t="s">
         <v>306</v>
       </c>
-      <c r="N22" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="23" spans="9:14">
-      <c r="I23" t="s">
+      <c r="O20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="10:15">
+      <c r="J21" t="s">
         <v>307</v>
       </c>
-      <c r="N23" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="24" spans="9:14">
-      <c r="I24" t="s">
+      <c r="O21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="10:15">
+      <c r="J22" t="s">
         <v>308</v>
       </c>
-      <c r="N24" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="25" spans="9:14">
-      <c r="I25" t="s">
+      <c r="O22" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="23" spans="10:15">
+      <c r="J23" t="s">
         <v>309</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O23" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="26" spans="9:14">
-      <c r="I26" t="s">
+    <row r="24" spans="10:15">
+      <c r="J24" t="s">
         <v>310</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O24" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="9:14">
-      <c r="I27" t="s">
+    <row r="25" spans="10:15">
+      <c r="J25" t="s">
         <v>311</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O25" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="28" spans="9:14">
-      <c r="I28" t="s">
+    <row r="26" spans="10:15">
+      <c r="J26" t="s">
         <v>312</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O26" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="29" spans="9:14">
-      <c r="I29" t="s">
+    <row r="27" spans="10:15">
+      <c r="J27" t="s">
         <v>313</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O27" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="30" spans="9:14">
-      <c r="I30" t="s">
+    <row r="28" spans="10:15">
+      <c r="J28" t="s">
         <v>314</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O28" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="31" spans="9:14">
-      <c r="I31" t="s">
+    <row r="29" spans="10:15">
+      <c r="J29" t="s">
         <v>315</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O29" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="9:14">
-      <c r="I32" t="s">
+    <row r="30" spans="10:15">
+      <c r="J30" t="s">
         <v>316</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O30" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="9:14">
-      <c r="I33" t="s">
+    <row r="31" spans="10:15">
+      <c r="J31" t="s">
         <v>317</v>
       </c>
-      <c r="N33" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="34" spans="9:14">
-      <c r="I34" t="s">
+      <c r="O31" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="10:15">
+      <c r="J32" t="s">
         <v>318</v>
       </c>
-      <c r="N34" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="35" spans="9:14">
-      <c r="I35" t="s">
+      <c r="O32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="10:15">
+      <c r="J33" t="s">
         <v>319</v>
       </c>
-      <c r="N35" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="36" spans="9:14">
-      <c r="I36" t="s">
+      <c r="O33" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="34" spans="10:15">
+      <c r="J34" t="s">
         <v>320</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O34" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="37" spans="9:14">
-      <c r="I37" t="s">
+    <row r="35" spans="10:15">
+      <c r="J35" t="s">
         <v>321</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O35" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="38" spans="9:14">
-      <c r="I38" t="s">
+    <row r="36" spans="10:15">
+      <c r="J36" t="s">
         <v>322</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O36" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="39" spans="9:14">
-      <c r="I39" t="s">
+    <row r="37" spans="10:15">
+      <c r="J37" t="s">
         <v>323</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O37" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="40" spans="9:14">
-      <c r="I40" t="s">
+    <row r="38" spans="10:15">
+      <c r="J38" t="s">
         <v>324</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O38" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="41" spans="9:14">
-      <c r="I41" t="s">
+    <row r="39" spans="10:15">
+      <c r="J39" t="s">
         <v>325</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O39" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="42" spans="9:14">
-      <c r="I42" t="s">
+    <row r="40" spans="10:15">
+      <c r="J40" t="s">
         <v>326</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O40" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" spans="10:15">
+      <c r="J41" t="s">
+        <v>327</v>
+      </c>
+      <c r="O41" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="43" spans="9:14">
-      <c r="I43" t="s">
+    <row r="42" spans="10:15">
+      <c r="J42" t="s">
+        <v>328</v>
+      </c>
+      <c r="O42" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" spans="10:15">
+      <c r="J43" t="s">
+        <v>329</v>
+      </c>
+      <c r="O43" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="44" spans="10:15">
+      <c r="J44" t="s">
+        <v>330</v>
+      </c>
+      <c r="O44" t="s">
         <v>327</v>
       </c>
-      <c r="N43" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="44" spans="9:14">
-      <c r="I44" t="s">
+    </row>
+    <row r="45" spans="10:15">
+      <c r="J45" t="s">
+        <v>331</v>
+      </c>
+      <c r="O45" t="s">
         <v>328</v>
       </c>
-      <c r="N44" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="45" spans="9:14">
-      <c r="I45" t="s">
+    </row>
+    <row r="46" spans="10:15">
+      <c r="J46" t="s">
+        <v>332</v>
+      </c>
+      <c r="O46" t="s">
         <v>329</v>
       </c>
-      <c r="N45" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="46" spans="9:14">
-      <c r="I46" t="s">
+    </row>
+    <row r="47" spans="10:15">
+      <c r="J47" t="s">
+        <v>333</v>
+      </c>
+      <c r="O47" t="s">
         <v>330</v>
       </c>
-      <c r="N46" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="47" spans="9:14">
-      <c r="I47" t="s">
+    </row>
+    <row r="48" spans="10:15">
+      <c r="J48" t="s">
+        <v>334</v>
+      </c>
+      <c r="O48" t="s">
         <v>331</v>
       </c>
-      <c r="N47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="48" spans="9:14">
-      <c r="I48" t="s">
+    </row>
+    <row r="49" spans="10:15">
+      <c r="J49" t="s">
+        <v>335</v>
+      </c>
+      <c r="O49" t="s">
         <v>332</v>
       </c>
-      <c r="N48" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="49" spans="9:14">
-      <c r="I49" t="s">
+    </row>
+    <row r="50" spans="10:15">
+      <c r="J50" t="s">
+        <v>336</v>
+      </c>
+      <c r="O50" t="s">
         <v>333</v>
       </c>
-      <c r="N49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="50" spans="9:14">
-      <c r="I50" t="s">
+    </row>
+    <row r="51" spans="10:15">
+      <c r="J51" t="s">
+        <v>337</v>
+      </c>
+      <c r="O51" t="s">
         <v>334</v>
       </c>
-      <c r="N50" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="51" spans="9:14">
-      <c r="I51" t="s">
+    </row>
+    <row r="52" spans="10:15">
+      <c r="J52" t="s">
+        <v>338</v>
+      </c>
+      <c r="O52" t="s">
         <v>335</v>
       </c>
-      <c r="N51" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="52" spans="9:14">
-      <c r="I52" t="s">
+    </row>
+    <row r="53" spans="10:15">
+      <c r="J53" t="s">
+        <v>339</v>
+      </c>
+      <c r="O53" t="s">
         <v>336</v>
       </c>
-      <c r="N52" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="53" spans="9:14">
-      <c r="I53" t="s">
+    </row>
+    <row r="54" spans="10:15">
+      <c r="J54" t="s">
+        <v>340</v>
+      </c>
+      <c r="O54" t="s">
         <v>337</v>
       </c>
-      <c r="N53" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="9:14">
-      <c r="I54" t="s">
+    </row>
+    <row r="55" spans="10:15">
+      <c r="J55" t="s">
+        <v>341</v>
+      </c>
+      <c r="O55" t="s">
         <v>338</v>
       </c>
-      <c r="N54" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="55" spans="9:14">
-      <c r="I55" t="s">
+    </row>
+    <row r="56" spans="10:15">
+      <c r="J56" t="s">
+        <v>342</v>
+      </c>
+      <c r="O56" t="s">
         <v>339</v>
       </c>
-      <c r="N55" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="56" spans="9:14">
-      <c r="I56" t="s">
+    </row>
+    <row r="57" spans="10:15">
+      <c r="J57" t="s">
+        <v>343</v>
+      </c>
+      <c r="O57" t="s">
         <v>340</v>
       </c>
-      <c r="N56" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="57" spans="9:14">
-      <c r="I57" t="s">
+    </row>
+    <row r="58" spans="10:15">
+      <c r="J58" t="s">
+        <v>344</v>
+      </c>
+      <c r="O58" t="s">
         <v>341</v>
       </c>
-      <c r="N57" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="58" spans="9:14">
-      <c r="I58" t="s">
+    </row>
+    <row r="59" spans="10:15">
+      <c r="J59" t="s">
+        <v>345</v>
+      </c>
+      <c r="O59" t="s">
         <v>342</v>
       </c>
-      <c r="N58" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="59" spans="9:14">
-      <c r="I59" t="s">
+    </row>
+    <row r="60" spans="10:15">
+      <c r="J60" t="s">
+        <v>346</v>
+      </c>
+      <c r="O60" t="s">
         <v>343</v>
       </c>
-      <c r="N59" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="60" spans="9:14">
-      <c r="I60" t="s">
+    </row>
+    <row r="61" spans="10:15">
+      <c r="J61" t="s">
+        <v>347</v>
+      </c>
+      <c r="O61" t="s">
         <v>344</v>
       </c>
-      <c r="N60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="9:14">
-      <c r="I61" t="s">
+    </row>
+    <row r="62" spans="10:15">
+      <c r="J62" t="s">
+        <v>348</v>
+      </c>
+      <c r="O62" t="s">
         <v>345</v>
       </c>
-      <c r="N61" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="62" spans="9:14">
-      <c r="I62" t="s">
+    </row>
+    <row r="63" spans="10:15">
+      <c r="J63" t="s">
+        <v>349</v>
+      </c>
+      <c r="O63" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="10:15">
+      <c r="J64" t="s">
+        <v>350</v>
+      </c>
+      <c r="O64" t="s">
         <v>346</v>
       </c>
-      <c r="N62" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="63" spans="9:14">
-      <c r="I63" t="s">
+    </row>
+    <row r="65" spans="10:15">
+      <c r="J65" t="s">
+        <v>351</v>
+      </c>
+      <c r="O65" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="66" spans="10:15">
+      <c r="J66" t="s">
+        <v>352</v>
+      </c>
+      <c r="O66" t="s">
         <v>347</v>
       </c>
-      <c r="N63" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="64" spans="9:14">
-      <c r="I64" t="s">
-        <v>348</v>
-      </c>
-      <c r="N64" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="65" spans="9:14">
-      <c r="I65" t="s">
+    </row>
+    <row r="67" spans="10:15">
+      <c r="J67" t="s">
+        <v>353</v>
+      </c>
+      <c r="O67" t="s">
         <v>349</v>
       </c>
-      <c r="N65" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="66" spans="9:14">
-      <c r="I66" t="s">
+    </row>
+    <row r="68" spans="10:15">
+      <c r="J68" t="s">
+        <v>354</v>
+      </c>
+      <c r="O68" t="s">
         <v>350</v>
       </c>
-      <c r="N66" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="67" spans="9:14">
-      <c r="I67" t="s">
+    </row>
+    <row r="69" spans="10:15">
+      <c r="J69" t="s">
+        <v>355</v>
+      </c>
+      <c r="O69" t="s">
         <v>351</v>
       </c>
-      <c r="N67" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="68" spans="9:14">
-      <c r="I68" t="s">
+    </row>
+    <row r="70" spans="10:15">
+      <c r="J70" t="s">
+        <v>356</v>
+      </c>
+      <c r="O70" t="s">
         <v>352</v>
       </c>
-      <c r="N68" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" spans="9:14">
-      <c r="I69" t="s">
+    </row>
+    <row r="71" spans="10:15">
+      <c r="J71" t="s">
+        <v>357</v>
+      </c>
+      <c r="O71" t="s">
         <v>353</v>
       </c>
-      <c r="N69" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="70" spans="9:14">
-      <c r="I70" t="s">
+    </row>
+    <row r="72" spans="10:15">
+      <c r="J72" t="s">
+        <v>358</v>
+      </c>
+      <c r="O72" t="s">
         <v>354</v>
       </c>
-      <c r="N70" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="71" spans="9:14">
-      <c r="I71" t="s">
+    </row>
+    <row r="73" spans="10:15">
+      <c r="J73" t="s">
+        <v>359</v>
+      </c>
+      <c r="O73" t="s">
         <v>355</v>
       </c>
-      <c r="N71" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="72" spans="9:14">
-      <c r="I72" t="s">
+    </row>
+    <row r="74" spans="10:15">
+      <c r="J74" t="s">
+        <v>360</v>
+      </c>
+      <c r="O74" t="s">
         <v>356</v>
       </c>
-      <c r="N72" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="73" spans="9:14">
-      <c r="I73" t="s">
+    </row>
+    <row r="75" spans="10:15">
+      <c r="J75" t="s">
+        <v>361</v>
+      </c>
+      <c r="O75" t="s">
         <v>357</v>
       </c>
-      <c r="N73" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="74" spans="9:14">
-      <c r="I74" t="s">
+    </row>
+    <row r="76" spans="10:15">
+      <c r="J76" t="s">
+        <v>362</v>
+      </c>
+      <c r="O76" t="s">
         <v>358</v>
       </c>
-      <c r="N74" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="75" spans="9:14">
-      <c r="I75" t="s">
+    </row>
+    <row r="77" spans="10:15">
+      <c r="J77" t="s">
+        <v>363</v>
+      </c>
+      <c r="O77" t="s">
         <v>359</v>
       </c>
-      <c r="N75" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="76" spans="9:14">
-      <c r="I76" t="s">
+    </row>
+    <row r="78" spans="10:15">
+      <c r="J78" t="s">
+        <v>364</v>
+      </c>
+      <c r="O78" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="79" spans="10:15">
+      <c r="J79" t="s">
+        <v>365</v>
+      </c>
+      <c r="O79" t="s">
         <v>360</v>
       </c>
-      <c r="N76" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="77" spans="9:14">
-      <c r="I77" t="s">
+    </row>
+    <row r="80" spans="10:15">
+      <c r="J80" t="s">
+        <v>366</v>
+      </c>
+      <c r="O80" t="s">
         <v>361</v>
       </c>
-      <c r="N77" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="78" spans="9:14">
-      <c r="I78" t="s">
-        <v>362</v>
-      </c>
-      <c r="N78" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="79" spans="9:14">
-      <c r="I79" t="s">
+    </row>
+    <row r="81" spans="10:15">
+      <c r="J81" t="s">
+        <v>367</v>
+      </c>
+      <c r="O81" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="82" spans="10:15">
+      <c r="J82" t="s">
+        <v>368</v>
+      </c>
+      <c r="O82" t="s">
         <v>363</v>
       </c>
-      <c r="N79" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="80" spans="9:14">
-      <c r="I80" t="s">
-        <v>364</v>
-      </c>
-      <c r="N80" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="81" spans="9:14">
-      <c r="I81" t="s">
+    </row>
+    <row r="83" spans="10:15">
+      <c r="J83" t="s">
+        <v>369</v>
+      </c>
+      <c r="O83" t="s">
         <v>365</v>
       </c>
-      <c r="N81" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="82" spans="9:14">
-      <c r="I82" t="s">
+    </row>
+    <row r="84" spans="10:15">
+      <c r="J84" t="s">
+        <v>370</v>
+      </c>
+      <c r="O84" t="s">
         <v>366</v>
       </c>
-      <c r="N82" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="83" spans="9:14">
-      <c r="I83" t="s">
-        <v>367</v>
-      </c>
-      <c r="N83" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="84" spans="9:14">
-      <c r="I84" t="s">
+    </row>
+    <row r="85" spans="10:15">
+      <c r="J85" t="s">
+        <v>371</v>
+      </c>
+      <c r="O85" t="s">
         <v>368</v>
       </c>
-      <c r="N84" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="85" spans="9:14">
-      <c r="I85" t="s">
+    </row>
+    <row r="86" spans="10:15">
+      <c r="J86" t="s">
+        <v>372</v>
+      </c>
+      <c r="O86" t="s">
         <v>369</v>
       </c>
-      <c r="N85" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="86" spans="9:14">
-      <c r="I86" t="s">
+    </row>
+    <row r="87" spans="10:15">
+      <c r="J87" t="s">
+        <v>373</v>
+      </c>
+      <c r="O87" t="s">
         <v>370</v>
       </c>
-      <c r="N86" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="87" spans="9:14">
-      <c r="I87" t="s">
+    </row>
+    <row r="88" spans="10:15">
+      <c r="J88" t="s">
+        <v>374</v>
+      </c>
+      <c r="O88" t="s">
         <v>371</v>
       </c>
-      <c r="N87" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="88" spans="9:14">
-      <c r="I88" t="s">
-        <v>372</v>
-      </c>
-      <c r="N88" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="89" spans="9:14">
-      <c r="I89" t="s">
+    </row>
+    <row r="89" spans="10:15">
+      <c r="J89" t="s">
+        <v>375</v>
+      </c>
+      <c r="O89" t="s">
         <v>373</v>
       </c>
-      <c r="N89" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="90" spans="9:14">
-      <c r="I90" t="s">
+    </row>
+    <row r="90" spans="10:15">
+      <c r="J90" t="s">
+        <v>376</v>
+      </c>
+      <c r="O90" t="s">
         <v>374</v>
       </c>
-      <c r="N90" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="91" spans="9:14">
-      <c r="I91" t="s">
+    </row>
+    <row r="91" spans="10:15">
+      <c r="J91" t="s">
+        <v>377</v>
+      </c>
+      <c r="O91" t="s">
         <v>375</v>
       </c>
-      <c r="N91" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="92" spans="9:14">
-      <c r="I92" t="s">
+    </row>
+    <row r="92" spans="10:15">
+      <c r="J92" t="s">
+        <v>378</v>
+      </c>
+      <c r="O92" t="s">
         <v>376</v>
       </c>
-      <c r="N92" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="93" spans="9:14">
-      <c r="I93" t="s">
+    </row>
+    <row r="93" spans="10:15">
+      <c r="J93" t="s">
+        <v>379</v>
+      </c>
+      <c r="O93" t="s">
         <v>377</v>
       </c>
-      <c r="N93" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="94" spans="9:14">
-      <c r="I94" t="s">
+    </row>
+    <row r="94" spans="10:15">
+      <c r="J94" t="s">
+        <v>380</v>
+      </c>
+      <c r="O94" t="s">
         <v>378</v>
       </c>
-      <c r="N94" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="95" spans="9:14">
-      <c r="I95" t="s">
+    </row>
+    <row r="95" spans="10:15">
+      <c r="J95" t="s">
+        <v>381</v>
+      </c>
+      <c r="O95" t="s">
         <v>379</v>
       </c>
-      <c r="N95" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="96" spans="9:14">
-      <c r="I96" t="s">
+    </row>
+    <row r="96" spans="10:15">
+      <c r="J96" t="s">
+        <v>382</v>
+      </c>
+      <c r="O96" t="s">
         <v>380</v>
       </c>
-      <c r="N96" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="97" spans="9:14">
-      <c r="I97" t="s">
+    </row>
+    <row r="97" spans="10:15">
+      <c r="J97" t="s">
+        <v>383</v>
+      </c>
+      <c r="O97" t="s">
         <v>381</v>
       </c>
-      <c r="N97" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="98" spans="9:14">
-      <c r="I98" t="s">
+    </row>
+    <row r="98" spans="10:15">
+      <c r="J98" t="s">
+        <v>384</v>
+      </c>
+      <c r="O98" t="s">
         <v>382</v>
       </c>
-      <c r="N98" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="99" spans="9:14">
-      <c r="I99" t="s">
+    </row>
+    <row r="99" spans="10:15">
+      <c r="J99" t="s">
+        <v>385</v>
+      </c>
+      <c r="O99" t="s">
         <v>383</v>
       </c>
-      <c r="N99" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="100" spans="9:14">
-      <c r="I100" t="s">
+    </row>
+    <row r="100" spans="10:15">
+      <c r="J100" t="s">
+        <v>386</v>
+      </c>
+      <c r="O100" t="s">
         <v>384</v>
       </c>
-      <c r="N100" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="101" spans="9:14">
-      <c r="I101" t="s">
+    </row>
+    <row r="101" spans="10:15">
+      <c r="J101" t="s">
+        <v>387</v>
+      </c>
+      <c r="O101" t="s">
         <v>385</v>
       </c>
-      <c r="N101" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="102" spans="9:14">
-      <c r="I102" t="s">
+    </row>
+    <row r="102" spans="10:15">
+      <c r="J102" t="s">
+        <v>388</v>
+      </c>
+      <c r="O102" t="s">
         <v>386</v>
       </c>
-      <c r="N102" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="103" spans="9:14">
-      <c r="I103" t="s">
+    </row>
+    <row r="103" spans="10:15">
+      <c r="J103" t="s">
+        <v>389</v>
+      </c>
+      <c r="O103" t="s">
         <v>387</v>
       </c>
-      <c r="N103" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="104" spans="9:14">
-      <c r="I104" t="s">
+    </row>
+    <row r="104" spans="10:15">
+      <c r="J104" t="s">
+        <v>390</v>
+      </c>
+      <c r="O104" t="s">
         <v>388</v>
       </c>
-      <c r="N104" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="105" spans="9:14">
-      <c r="I105" t="s">
+    </row>
+    <row r="105" spans="10:15">
+      <c r="J105" t="s">
+        <v>391</v>
+      </c>
+      <c r="O105" t="s">
         <v>389</v>
       </c>
-      <c r="N105" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="106" spans="9:14">
-      <c r="I106" t="s">
+    </row>
+    <row r="106" spans="10:15">
+      <c r="J106" t="s">
+        <v>392</v>
+      </c>
+      <c r="O106" t="s">
         <v>390</v>
       </c>
-      <c r="N106" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="107" spans="9:14">
-      <c r="I107" t="s">
+    </row>
+    <row r="107" spans="10:15">
+      <c r="J107" t="s">
+        <v>393</v>
+      </c>
+      <c r="O107" t="s">
         <v>391</v>
       </c>
-      <c r="N107" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="108" spans="9:14">
-      <c r="I108" t="s">
+    </row>
+    <row r="108" spans="10:15">
+      <c r="J108" t="s">
+        <v>394</v>
+      </c>
+      <c r="O108" t="s">
         <v>392</v>
       </c>
-      <c r="N108" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="109" spans="9:14">
-      <c r="I109" t="s">
+    </row>
+    <row r="109" spans="10:15">
+      <c r="J109" t="s">
+        <v>395</v>
+      </c>
+      <c r="O109" t="s">
         <v>393</v>
       </c>
-      <c r="N109" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="110" spans="9:14">
-      <c r="I110" t="s">
+    </row>
+    <row r="110" spans="10:15">
+      <c r="J110" t="s">
+        <v>396</v>
+      </c>
+      <c r="O110" t="s">
         <v>394</v>
       </c>
-      <c r="N110" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="111" spans="9:14">
-      <c r="I111" t="s">
+    </row>
+    <row r="111" spans="10:15">
+      <c r="J111" t="s">
+        <v>397</v>
+      </c>
+      <c r="O111" t="s">
         <v>395</v>
       </c>
-      <c r="N111" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="112" spans="9:14">
-      <c r="I112" t="s">
+    </row>
+    <row r="112" spans="10:15">
+      <c r="J112" t="s">
+        <v>398</v>
+      </c>
+      <c r="O112" t="s">
         <v>396</v>
       </c>
-      <c r="N112" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="113" spans="9:14">
-      <c r="I113" t="s">
+    </row>
+    <row r="113" spans="10:15">
+      <c r="J113" t="s">
+        <v>399</v>
+      </c>
+      <c r="O113" t="s">
         <v>397</v>
       </c>
-      <c r="N113" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="114" spans="9:14">
-      <c r="I114" t="s">
+    </row>
+    <row r="114" spans="10:15">
+      <c r="J114" t="s">
+        <v>400</v>
+      </c>
+      <c r="O114" t="s">
         <v>398</v>
       </c>
-      <c r="N114" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="115" spans="9:14">
-      <c r="I115" t="s">
+    </row>
+    <row r="115" spans="10:15">
+      <c r="J115" t="s">
+        <v>401</v>
+      </c>
+      <c r="O115" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="116" spans="10:15">
+      <c r="J116" t="s">
+        <v>402</v>
+      </c>
+      <c r="O116" t="s">
         <v>399</v>
       </c>
-      <c r="N115" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="116" spans="9:14">
-      <c r="I116" t="s">
+    </row>
+    <row r="117" spans="10:15">
+      <c r="J117" t="s">
+        <v>403</v>
+      </c>
+      <c r="O117" t="s">
         <v>400</v>
       </c>
-      <c r="N116" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="117" spans="9:14">
-      <c r="I117" t="s">
+    </row>
+    <row r="118" spans="10:15">
+      <c r="J118" t="s">
+        <v>404</v>
+      </c>
+      <c r="O118" t="s">
         <v>401</v>
       </c>
-      <c r="N117" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="118" spans="9:14">
-      <c r="I118" t="s">
+    </row>
+    <row r="119" spans="10:15">
+      <c r="J119" t="s">
+        <v>405</v>
+      </c>
+      <c r="O119" t="s">
         <v>402</v>
       </c>
-      <c r="N118" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="119" spans="9:14">
-      <c r="I119" t="s">
+    </row>
+    <row r="120" spans="10:15">
+      <c r="J120" t="s">
+        <v>406</v>
+      </c>
+      <c r="O120" t="s">
         <v>403</v>
       </c>
-      <c r="N119" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="120" spans="9:14">
-      <c r="I120" t="s">
+    </row>
+    <row r="121" spans="10:15">
+      <c r="J121" t="s">
+        <v>407</v>
+      </c>
+      <c r="O121" t="s">
         <v>404</v>
       </c>
-      <c r="N120" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="121" spans="9:14">
-      <c r="I121" t="s">
+    </row>
+    <row r="122" spans="10:15">
+      <c r="J122" t="s">
+        <v>408</v>
+      </c>
+      <c r="O122" t="s">
         <v>405</v>
       </c>
-      <c r="N121" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="122" spans="9:14">
-      <c r="I122" t="s">
+    </row>
+    <row r="123" spans="10:15">
+      <c r="J123" t="s">
+        <v>409</v>
+      </c>
+      <c r="O123" t="s">
         <v>406</v>
       </c>
-      <c r="N122" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="123" spans="9:14">
-      <c r="I123" t="s">
+    </row>
+    <row r="124" spans="10:15">
+      <c r="J124" t="s">
+        <v>410</v>
+      </c>
+      <c r="O124" t="s">
         <v>407</v>
       </c>
-      <c r="N123" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="124" spans="9:14">
-      <c r="I124" t="s">
+    </row>
+    <row r="125" spans="10:15">
+      <c r="J125" t="s">
+        <v>411</v>
+      </c>
+      <c r="O125" t="s">
         <v>408</v>
       </c>
-      <c r="N124" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="125" spans="9:14">
-      <c r="I125" t="s">
+    </row>
+    <row r="126" spans="10:15">
+      <c r="J126" t="s">
+        <v>412</v>
+      </c>
+      <c r="O126" t="s">
         <v>409</v>
       </c>
-      <c r="N125" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="126" spans="9:14">
-      <c r="I126" t="s">
+    </row>
+    <row r="127" spans="10:15">
+      <c r="J127" t="s">
+        <v>413</v>
+      </c>
+      <c r="O127" t="s">
         <v>410</v>
       </c>
-      <c r="N126" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="127" spans="9:14">
-      <c r="I127" t="s">
+    </row>
+    <row r="128" spans="10:15">
+      <c r="J128" t="s">
+        <v>414</v>
+      </c>
+      <c r="O128" t="s">
         <v>411</v>
       </c>
-      <c r="N127" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="128" spans="9:14">
-      <c r="I128" t="s">
+    </row>
+    <row r="129" spans="10:15">
+      <c r="J129" t="s">
+        <v>415</v>
+      </c>
+      <c r="O129" t="s">
         <v>412</v>
       </c>
-      <c r="N128" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="129" spans="9:14">
-      <c r="I129" t="s">
+    </row>
+    <row r="130" spans="10:15">
+      <c r="J130" t="s">
+        <v>416</v>
+      </c>
+      <c r="O130" t="s">
         <v>413</v>
       </c>
-      <c r="N129" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="130" spans="9:14">
-      <c r="I130" t="s">
+    </row>
+    <row r="131" spans="10:15">
+      <c r="J131" t="s">
+        <v>417</v>
+      </c>
+      <c r="O131" t="s">
         <v>414</v>
       </c>
-      <c r="N130" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="131" spans="9:14">
-      <c r="I131" t="s">
+    </row>
+    <row r="132" spans="10:15">
+      <c r="J132" t="s">
+        <v>418</v>
+      </c>
+      <c r="O132" t="s">
         <v>415</v>
       </c>
-      <c r="N131" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="132" spans="9:14">
-      <c r="I132" t="s">
+    </row>
+    <row r="133" spans="10:15">
+      <c r="J133" t="s">
+        <v>419</v>
+      </c>
+      <c r="O133" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="134" spans="10:15">
+      <c r="J134" t="s">
+        <v>420</v>
+      </c>
+      <c r="O134" t="s">
         <v>416</v>
       </c>
-      <c r="N132" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="133" spans="9:14">
-      <c r="I133" t="s">
+    </row>
+    <row r="135" spans="10:15">
+      <c r="J135" t="s">
+        <v>421</v>
+      </c>
+      <c r="O135" t="s">
         <v>417</v>
       </c>
-      <c r="N133" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="134" spans="9:14">
-      <c r="I134" t="s">
-        <v>418</v>
-      </c>
-      <c r="N134" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="135" spans="9:14">
-      <c r="I135" t="s">
+    </row>
+    <row r="136" spans="10:15">
+      <c r="J136" t="s">
+        <v>422</v>
+      </c>
+      <c r="O136" t="s">
         <v>419</v>
       </c>
-      <c r="N135" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="136" spans="9:14">
-      <c r="I136" t="s">
+    </row>
+    <row r="137" spans="10:15">
+      <c r="J137" t="s">
+        <v>423</v>
+      </c>
+      <c r="O137" t="s">
         <v>420</v>
       </c>
-      <c r="N136" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="9:14">
-      <c r="I137" t="s">
+    </row>
+    <row r="138" spans="10:15">
+      <c r="J138" t="s">
+        <v>424</v>
+      </c>
+      <c r="O138" t="s">
         <v>421</v>
       </c>
-      <c r="N137" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="138" spans="9:14">
-      <c r="I138" t="s">
+    </row>
+    <row r="139" spans="10:15">
+      <c r="J139" t="s">
+        <v>425</v>
+      </c>
+      <c r="O139" t="s">
         <v>422</v>
       </c>
-      <c r="N138" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="139" spans="9:14">
-      <c r="I139" t="s">
+    </row>
+    <row r="140" spans="10:15">
+      <c r="J140" t="s">
+        <v>426</v>
+      </c>
+      <c r="O140" t="s">
         <v>423</v>
       </c>
-      <c r="N139" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="140" spans="9:14">
-      <c r="I140" t="s">
+    </row>
+    <row r="141" spans="10:15">
+      <c r="J141" t="s">
+        <v>427</v>
+      </c>
+      <c r="O141" t="s">
         <v>424</v>
       </c>
-      <c r="N140" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="141" spans="9:14">
-      <c r="I141" t="s">
+    </row>
+    <row r="142" spans="10:15">
+      <c r="J142" t="s">
+        <v>428</v>
+      </c>
+      <c r="O142" t="s">
         <v>425</v>
       </c>
-      <c r="N141" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="142" spans="9:14">
-      <c r="I142" t="s">
+    </row>
+    <row r="143" spans="10:15">
+      <c r="J143" t="s">
+        <v>429</v>
+      </c>
+      <c r="O143" t="s">
         <v>426</v>
       </c>
-      <c r="N142" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="143" spans="9:14">
-      <c r="I143" t="s">
+    </row>
+    <row r="144" spans="10:15">
+      <c r="J144" t="s">
+        <v>430</v>
+      </c>
+      <c r="O144" t="s">
         <v>427</v>
       </c>
-      <c r="N143" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="144" spans="9:14">
-      <c r="I144" t="s">
+    </row>
+    <row r="145" spans="10:15">
+      <c r="J145" t="s">
+        <v>431</v>
+      </c>
+      <c r="O145" t="s">
         <v>428</v>
       </c>
-      <c r="N144" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="145" spans="9:14">
-      <c r="I145" t="s">
+    </row>
+    <row r="146" spans="10:15">
+      <c r="J146" t="s">
+        <v>432</v>
+      </c>
+      <c r="O146" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="147" spans="10:15">
+      <c r="J147" t="s">
+        <v>433</v>
+      </c>
+      <c r="O147" t="s">
         <v>429</v>
       </c>
-      <c r="N145" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="146" spans="9:14">
-      <c r="I146" t="s">
+    </row>
+    <row r="148" spans="10:15">
+      <c r="J148" t="s">
+        <v>434</v>
+      </c>
+      <c r="O148" t="s">
         <v>430</v>
       </c>
-      <c r="N146" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="147" spans="9:14">
-      <c r="I147" t="s">
+    </row>
+    <row r="149" spans="10:15">
+      <c r="J149" t="s">
+        <v>435</v>
+      </c>
+      <c r="O149" t="s">
         <v>431</v>
       </c>
-      <c r="N147" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="148" spans="9:14">
-      <c r="I148" t="s">
-        <v>432</v>
-      </c>
-      <c r="N148" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="149" spans="9:14">
-      <c r="I149" t="s">
+    </row>
+    <row r="150" spans="10:15">
+      <c r="J150" t="s">
+        <v>436</v>
+      </c>
+      <c r="O150" t="s">
         <v>433</v>
       </c>
-      <c r="N149" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="150" spans="9:14">
-      <c r="I150" t="s">
+    </row>
+    <row r="151" spans="10:15">
+      <c r="J151" t="s">
+        <v>437</v>
+      </c>
+      <c r="O151" t="s">
         <v>434</v>
       </c>
-      <c r="N150" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="151" spans="9:14">
-      <c r="I151" t="s">
+    </row>
+    <row r="152" spans="10:15">
+      <c r="J152" t="s">
+        <v>438</v>
+      </c>
+      <c r="O152" t="s">
         <v>435</v>
       </c>
-      <c r="N151" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="152" spans="9:14">
-      <c r="I152" t="s">
+    </row>
+    <row r="153" spans="10:15">
+      <c r="J153" t="s">
+        <v>439</v>
+      </c>
+      <c r="O153" t="s">
         <v>436</v>
       </c>
-      <c r="N152" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="153" spans="9:14">
-      <c r="I153" t="s">
+    </row>
+    <row r="154" spans="10:15">
+      <c r="J154" t="s">
+        <v>440</v>
+      </c>
+      <c r="O154" t="s">
         <v>437</v>
       </c>
-      <c r="N153" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="154" spans="9:14">
-      <c r="I154" t="s">
+    </row>
+    <row r="155" spans="10:15">
+      <c r="J155" t="s">
+        <v>441</v>
+      </c>
+      <c r="O155" t="s">
         <v>438</v>
       </c>
-      <c r="N154" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="155" spans="9:14">
-      <c r="I155" t="s">
+    </row>
+    <row r="156" spans="10:15">
+      <c r="J156" t="s">
+        <v>442</v>
+      </c>
+      <c r="O156" t="s">
         <v>439</v>
       </c>
-      <c r="N155" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="156" spans="9:14">
-      <c r="I156" t="s">
+    </row>
+    <row r="157" spans="10:15">
+      <c r="J157" t="s">
+        <v>443</v>
+      </c>
+      <c r="O157" t="s">
         <v>440</v>
       </c>
-      <c r="N156" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="157" spans="9:14">
-      <c r="I157" t="s">
+    </row>
+    <row r="158" spans="10:15">
+      <c r="J158" t="s">
+        <v>444</v>
+      </c>
+      <c r="O158" t="s">
         <v>441</v>
       </c>
-      <c r="N157" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="158" spans="9:14">
-      <c r="I158" t="s">
+    </row>
+    <row r="159" spans="10:15">
+      <c r="J159" t="s">
+        <v>445</v>
+      </c>
+      <c r="O159" t="s">
         <v>442</v>
       </c>
-      <c r="N158" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="159" spans="9:14">
-      <c r="I159" t="s">
+    </row>
+    <row r="160" spans="10:15">
+      <c r="J160" t="s">
+        <v>446</v>
+      </c>
+      <c r="O160" t="s">
         <v>443</v>
       </c>
-      <c r="N159" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="160" spans="9:14">
-      <c r="I160" t="s">
+    </row>
+    <row r="161" spans="10:15">
+      <c r="J161" t="s">
+        <v>447</v>
+      </c>
+      <c r="O161" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="162" spans="10:15">
+      <c r="J162" t="s">
+        <v>448</v>
+      </c>
+      <c r="O162" t="s">
         <v>444</v>
       </c>
-      <c r="N160" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="161" spans="9:14">
-      <c r="I161" t="s">
-        <v>445</v>
-      </c>
-      <c r="N161" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="162" spans="9:14">
-      <c r="I162" t="s">
+    </row>
+    <row r="163" spans="10:15">
+      <c r="J163" t="s">
+        <v>449</v>
+      </c>
+      <c r="O163" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="164" spans="10:15">
+      <c r="J164" t="s">
+        <v>450</v>
+      </c>
+      <c r="O164" t="s">
         <v>446</v>
       </c>
-      <c r="N162" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="163" spans="9:14">
-      <c r="I163" t="s">
+    </row>
+    <row r="165" spans="10:15">
+      <c r="J165" t="s">
+        <v>451</v>
+      </c>
+      <c r="O165" t="s">
         <v>447</v>
       </c>
-      <c r="N163" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="164" spans="9:14">
-      <c r="I164" t="s">
+    </row>
+    <row r="166" spans="10:15">
+      <c r="J166" t="s">
+        <v>452</v>
+      </c>
+      <c r="O166" t="s">
         <v>448</v>
       </c>
-      <c r="N164" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="165" spans="9:14">
-      <c r="I165" t="s">
+    </row>
+    <row r="167" spans="10:15">
+      <c r="J167" t="s">
+        <v>453</v>
+      </c>
+      <c r="O167" t="s">
         <v>449</v>
       </c>
-      <c r="N165" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="166" spans="9:14">
-      <c r="I166" t="s">
+    </row>
+    <row r="168" spans="10:15">
+      <c r="J168" t="s">
+        <v>454</v>
+      </c>
+      <c r="O168" t="s">
         <v>450</v>
       </c>
-      <c r="N166" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="167" spans="9:14">
-      <c r="I167" t="s">
+    </row>
+    <row r="169" spans="10:15">
+      <c r="J169" t="s">
+        <v>455</v>
+      </c>
+      <c r="O169" t="s">
         <v>451</v>
       </c>
-      <c r="N167" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="168" spans="9:14">
-      <c r="I168" t="s">
+    </row>
+    <row r="170" spans="10:15">
+      <c r="J170" t="s">
+        <v>456</v>
+      </c>
+      <c r="O170" t="s">
         <v>452</v>
       </c>
-      <c r="N168" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="169" spans="9:14">
-      <c r="I169" t="s">
+    </row>
+    <row r="171" spans="10:15">
+      <c r="J171" t="s">
+        <v>457</v>
+      </c>
+      <c r="O171" t="s">
         <v>453</v>
       </c>
-      <c r="N169" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="170" spans="9:14">
-      <c r="I170" t="s">
+    </row>
+    <row r="172" spans="10:15">
+      <c r="J172" t="s">
+        <v>458</v>
+      </c>
+      <c r="O172" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="173" spans="10:15">
+      <c r="J173" t="s">
+        <v>459</v>
+      </c>
+      <c r="O173" t="s">
         <v>454</v>
       </c>
-      <c r="N170" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="171" spans="9:14">
-      <c r="I171" t="s">
+    </row>
+    <row r="174" spans="10:15">
+      <c r="J174" t="s">
+        <v>460</v>
+      </c>
+      <c r="O174" t="s">
         <v>455</v>
       </c>
-      <c r="N171" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="172" spans="9:14">
-      <c r="I172" t="s">
+    </row>
+    <row r="175" spans="10:15">
+      <c r="J175" t="s">
+        <v>461</v>
+      </c>
+      <c r="O175" t="s">
         <v>456</v>
       </c>
-      <c r="N172" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="173" spans="9:14">
-      <c r="I173" t="s">
+    </row>
+    <row r="176" spans="10:15">
+      <c r="J176" t="s">
+        <v>462</v>
+      </c>
+      <c r="O176" t="s">
         <v>457</v>
       </c>
-      <c r="N173" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="174" spans="9:14">
-      <c r="I174" t="s">
+    </row>
+    <row r="177" spans="10:15">
+      <c r="J177" t="s">
+        <v>463</v>
+      </c>
+      <c r="O177" t="s">
         <v>458</v>
       </c>
-      <c r="N174" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="175" spans="9:14">
-      <c r="I175" t="s">
-        <v>459</v>
-      </c>
-      <c r="N175" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="176" spans="9:14">
-      <c r="I176" t="s">
+    </row>
+    <row r="178" spans="10:15">
+      <c r="J178" t="s">
+        <v>464</v>
+      </c>
+      <c r="O178" t="s">
         <v>460</v>
       </c>
-      <c r="N176" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="177" spans="9:14">
-      <c r="I177" t="s">
+    </row>
+    <row r="179" spans="10:15">
+      <c r="J179" t="s">
+        <v>465</v>
+      </c>
+      <c r="O179" t="s">
         <v>461</v>
       </c>
-      <c r="N177" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="178" spans="9:14">
-      <c r="I178" t="s">
+    </row>
+    <row r="180" spans="10:15">
+      <c r="J180" t="s">
+        <v>466</v>
+      </c>
+      <c r="O180" t="s">
         <v>462</v>
       </c>
-      <c r="N178" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="179" spans="9:14">
-      <c r="I179" t="s">
+    </row>
+    <row r="181" spans="10:15">
+      <c r="J181" t="s">
+        <v>467</v>
+      </c>
+      <c r="O181" t="s">
         <v>463</v>
       </c>
-      <c r="N179" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="180" spans="9:14">
-      <c r="I180" t="s">
+    </row>
+    <row r="182" spans="10:15">
+      <c r="J182" t="s">
+        <v>468</v>
+      </c>
+      <c r="O182" t="s">
         <v>464</v>
       </c>
-      <c r="N180" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="181" spans="9:14">
-      <c r="I181" t="s">
+    </row>
+    <row r="183" spans="10:15">
+      <c r="J183" t="s">
+        <v>469</v>
+      </c>
+      <c r="O183" t="s">
         <v>465</v>
       </c>
-      <c r="N181" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="182" spans="9:14">
-      <c r="I182" t="s">
+    </row>
+    <row r="184" spans="10:15">
+      <c r="J184" t="s">
+        <v>470</v>
+      </c>
+      <c r="O184" t="s">
         <v>466</v>
       </c>
-      <c r="N182" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="183" spans="9:14">
-      <c r="I183" t="s">
+    </row>
+    <row r="185" spans="10:15">
+      <c r="J185" t="s">
+        <v>471</v>
+      </c>
+      <c r="O185" t="s">
         <v>467</v>
       </c>
-      <c r="N183" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="184" spans="9:14">
-      <c r="I184" t="s">
+    </row>
+    <row r="186" spans="10:15">
+      <c r="J186" t="s">
+        <v>472</v>
+      </c>
+      <c r="O186" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="187" spans="10:15">
+      <c r="J187" t="s">
+        <v>473</v>
+      </c>
+      <c r="O187" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="188" spans="10:15">
+      <c r="J188" t="s">
+        <v>474</v>
+      </c>
+      <c r="O188" t="s">
         <v>468</v>
       </c>
-      <c r="N184" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="185" spans="9:14">
-      <c r="I185" t="s">
+    </row>
+    <row r="189" spans="10:15">
+      <c r="J189" t="s">
+        <v>475</v>
+      </c>
+      <c r="O189" t="s">
         <v>469</v>
       </c>
-      <c r="N185" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="186" spans="9:14">
-      <c r="I186" t="s">
+    </row>
+    <row r="190" spans="10:15">
+      <c r="J190" t="s">
+        <v>476</v>
+      </c>
+      <c r="O190" t="s">
         <v>470</v>
       </c>
-      <c r="N186" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="187" spans="9:14">
-      <c r="I187" t="s">
+    </row>
+    <row r="191" spans="10:15">
+      <c r="J191" t="s">
+        <v>477</v>
+      </c>
+      <c r="O191" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="192" spans="10:15">
+      <c r="J192" t="s">
+        <v>478</v>
+      </c>
+      <c r="O192" t="s">
         <v>471</v>
       </c>
-      <c r="N187" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="188" spans="9:14">
-      <c r="I188" t="s">
+    </row>
+    <row r="193" spans="10:15">
+      <c r="J193" t="s">
+        <v>479</v>
+      </c>
+      <c r="O193" t="s">
         <v>472</v>
       </c>
-      <c r="N188" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="189" spans="9:14">
-      <c r="I189" t="s">
+    </row>
+    <row r="194" spans="10:15">
+      <c r="J194" t="s">
+        <v>480</v>
+      </c>
+      <c r="O194" t="s">
         <v>473</v>
       </c>
-      <c r="N189" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="190" spans="9:14">
-      <c r="I190" t="s">
+    </row>
+    <row r="195" spans="10:15">
+      <c r="J195" t="s">
+        <v>481</v>
+      </c>
+      <c r="O195" t="s">
         <v>474</v>
       </c>
-      <c r="N190" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="191" spans="9:14">
-      <c r="I191" t="s">
+    </row>
+    <row r="196" spans="10:15">
+      <c r="J196" t="s">
+        <v>482</v>
+      </c>
+      <c r="O196" t="s">
         <v>475</v>
       </c>
-      <c r="N191" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="192" spans="9:14">
-      <c r="I192" t="s">
+    </row>
+    <row r="197" spans="10:15">
+      <c r="J197" t="s">
+        <v>483</v>
+      </c>
+      <c r="O197" t="s">
         <v>476</v>
       </c>
-      <c r="N192" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="193" spans="9:14">
-      <c r="I193" t="s">
+    </row>
+    <row r="198" spans="10:15">
+      <c r="J198" t="s">
+        <v>484</v>
+      </c>
+      <c r="O198" t="s">
         <v>477</v>
       </c>
-      <c r="N193" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="194" spans="9:14">
-      <c r="I194" t="s">
+    </row>
+    <row r="199" spans="10:15">
+      <c r="J199" t="s">
+        <v>485</v>
+      </c>
+      <c r="O199" t="s">
         <v>478</v>
       </c>
-      <c r="N194" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="195" spans="9:14">
-      <c r="I195" t="s">
+    </row>
+    <row r="200" spans="10:15">
+      <c r="J200" t="s">
+        <v>486</v>
+      </c>
+      <c r="O200" t="s">
         <v>479</v>
       </c>
-      <c r="N195" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="196" spans="9:14">
-      <c r="I196" t="s">
+    </row>
+    <row r="201" spans="10:15">
+      <c r="J201" t="s">
+        <v>487</v>
+      </c>
+      <c r="O201" t="s">
         <v>480</v>
       </c>
-      <c r="N196" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="197" spans="9:14">
-      <c r="I197" t="s">
+    </row>
+    <row r="202" spans="10:15">
+      <c r="J202" t="s">
+        <v>488</v>
+      </c>
+      <c r="O202" t="s">
         <v>481</v>
       </c>
-      <c r="N197" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="198" spans="9:14">
-      <c r="I198" t="s">
+    </row>
+    <row r="203" spans="10:15">
+      <c r="J203" t="s">
+        <v>489</v>
+      </c>
+      <c r="O203" t="s">
         <v>482</v>
       </c>
-      <c r="N198" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="199" spans="9:14">
-      <c r="I199" t="s">
+    </row>
+    <row r="204" spans="10:15">
+      <c r="J204" t="s">
+        <v>490</v>
+      </c>
+      <c r="O204" t="s">
         <v>483</v>
       </c>
-      <c r="N199" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="200" spans="9:14">
-      <c r="I200" t="s">
+    </row>
+    <row r="205" spans="10:15">
+      <c r="J205" t="s">
+        <v>491</v>
+      </c>
+      <c r="O205" t="s">
         <v>484</v>
       </c>
-      <c r="N200" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="201" spans="9:14">
-      <c r="I201" t="s">
+    </row>
+    <row r="206" spans="10:15">
+      <c r="J206" t="s">
+        <v>492</v>
+      </c>
+      <c r="O206" t="s">
         <v>485</v>
       </c>
-      <c r="N201" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="202" spans="9:14">
-      <c r="I202" t="s">
+    </row>
+    <row r="207" spans="10:15">
+      <c r="J207" t="s">
+        <v>493</v>
+      </c>
+      <c r="O207" t="s">
         <v>486</v>
       </c>
-      <c r="N202" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="203" spans="9:14">
-      <c r="I203" t="s">
+    </row>
+    <row r="208" spans="10:15">
+      <c r="J208" t="s">
+        <v>494</v>
+      </c>
+      <c r="O208" t="s">
         <v>487</v>
       </c>
-      <c r="N203" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="204" spans="9:14">
-      <c r="I204" t="s">
+    </row>
+    <row r="209" spans="10:15">
+      <c r="J209" t="s">
+        <v>495</v>
+      </c>
+      <c r="O209" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="210" spans="10:15">
+      <c r="J210" t="s">
+        <v>496</v>
+      </c>
+      <c r="O210" t="s">
         <v>488</v>
       </c>
-      <c r="N204" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="205" spans="9:14">
-      <c r="I205" t="s">
+    </row>
+    <row r="211" spans="10:15">
+      <c r="J211" t="s">
+        <v>497</v>
+      </c>
+      <c r="O211" t="s">
         <v>489</v>
       </c>
-      <c r="N205" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="206" spans="9:14">
-      <c r="I206" t="s">
+    </row>
+    <row r="212" spans="10:15">
+      <c r="J212" t="s">
+        <v>498</v>
+      </c>
+      <c r="O212" t="s">
         <v>490</v>
       </c>
-      <c r="N206" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="207" spans="9:14">
-      <c r="I207" t="s">
+    </row>
+    <row r="213" spans="10:15">
+      <c r="J213" t="s">
+        <v>499</v>
+      </c>
+      <c r="O213" t="s">
         <v>491</v>
       </c>
-      <c r="N207" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="208" spans="9:14">
-      <c r="I208" t="s">
+    </row>
+    <row r="214" spans="10:15">
+      <c r="J214" t="s">
+        <v>500</v>
+      </c>
+      <c r="O214" t="s">
         <v>492</v>
       </c>
-      <c r="N208" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="209" spans="9:14">
-      <c r="I209" t="s">
+    </row>
+    <row r="215" spans="10:15">
+      <c r="J215" t="s">
+        <v>501</v>
+      </c>
+      <c r="O215" t="s">
         <v>493</v>
       </c>
-      <c r="N209" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="210" spans="9:14">
-      <c r="I210" t="s">
+    </row>
+    <row r="216" spans="10:15">
+      <c r="J216" t="s">
+        <v>502</v>
+      </c>
+      <c r="O216" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="217" spans="10:15">
+      <c r="J217" t="s">
+        <v>503</v>
+      </c>
+      <c r="O217" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="218" spans="10:15">
+      <c r="J218" t="s">
+        <v>504</v>
+      </c>
+      <c r="O218" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="219" spans="10:15">
+      <c r="J219" t="s">
+        <v>505</v>
+      </c>
+      <c r="O219" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="220" spans="10:15">
+      <c r="J220" t="s">
+        <v>506</v>
+      </c>
+      <c r="O220" t="s">
         <v>494</v>
       </c>
-      <c r="N210" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="211" spans="9:14">
-      <c r="I211" t="s">
-        <v>495</v>
-      </c>
-      <c r="N211" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="212" spans="9:14">
-      <c r="I212" t="s">
-        <v>496</v>
-      </c>
-      <c r="N212" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="213" spans="9:14">
-      <c r="I213" t="s">
-        <v>497</v>
-      </c>
-      <c r="N213" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="214" spans="9:14">
-      <c r="I214" t="s">
-        <v>498</v>
-      </c>
-      <c r="N214" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="215" spans="9:14">
-      <c r="I215" t="s">
+    </row>
+    <row r="221" spans="10:15">
+      <c r="J221" t="s">
+        <v>507</v>
+      </c>
+      <c r="O221" t="s">
         <v>499</v>
       </c>
-      <c r="N215" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="216" spans="9:14">
-      <c r="I216" t="s">
+    </row>
+    <row r="222" spans="10:15">
+      <c r="J222" t="s">
+        <v>508</v>
+      </c>
+      <c r="O222" t="s">
         <v>500</v>
       </c>
-      <c r="N216" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="217" spans="9:14">
-      <c r="I217" t="s">
+    </row>
+    <row r="223" spans="10:15">
+      <c r="J223" t="s">
+        <v>509</v>
+      </c>
+      <c r="O223" t="s">
         <v>501</v>
       </c>
-      <c r="N217" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="218" spans="9:14">
-      <c r="I218" t="s">
+    </row>
+    <row r="224" spans="10:15">
+      <c r="J224" t="s">
+        <v>510</v>
+      </c>
+      <c r="O224" t="s">
         <v>502</v>
       </c>
-      <c r="N218" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="219" spans="9:14">
-      <c r="I219" t="s">
-        <v>503</v>
-      </c>
-      <c r="N219" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="220" spans="9:14">
-      <c r="I220" t="s">
+    </row>
+    <row r="225" spans="10:15">
+      <c r="J225" t="s">
+        <v>511</v>
+      </c>
+      <c r="O225" t="s">
         <v>504</v>
       </c>
-      <c r="N220" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="221" spans="9:14">
-      <c r="I221" t="s">
+    </row>
+    <row r="226" spans="10:15">
+      <c r="J226" t="s">
+        <v>512</v>
+      </c>
+      <c r="O226" t="s">
         <v>505</v>
       </c>
-      <c r="N221" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="222" spans="9:14">
-      <c r="I222" t="s">
+    </row>
+    <row r="227" spans="10:15">
+      <c r="J227" t="s">
+        <v>513</v>
+      </c>
+      <c r="O227" t="s">
         <v>506</v>
       </c>
-      <c r="N222" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="223" spans="9:14">
-      <c r="I223" t="s">
+    </row>
+    <row r="228" spans="10:15">
+      <c r="J228" t="s">
+        <v>514</v>
+      </c>
+      <c r="O228" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="229" spans="10:15">
+      <c r="J229" t="s">
+        <v>515</v>
+      </c>
+      <c r="O229" t="s">
         <v>507</v>
       </c>
-      <c r="N223" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="224" spans="9:14">
-      <c r="I224" t="s">
+    </row>
+    <row r="230" spans="10:15">
+      <c r="J230" t="s">
+        <v>516</v>
+      </c>
+      <c r="O230" t="s">
         <v>508</v>
       </c>
-      <c r="N224" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="225" spans="9:14">
-      <c r="I225" t="s">
+    </row>
+    <row r="231" spans="10:15">
+      <c r="J231" t="s">
+        <v>517</v>
+      </c>
+      <c r="O231" t="s">
         <v>509</v>
       </c>
-      <c r="N225" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="226" spans="9:14">
-      <c r="I226" t="s">
+    </row>
+    <row r="232" spans="10:15">
+      <c r="J232" t="s">
+        <v>518</v>
+      </c>
+      <c r="O232" t="s">
         <v>510</v>
       </c>
-      <c r="N226" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="227" spans="9:14">
-      <c r="I227" t="s">
+    </row>
+    <row r="233" spans="10:15">
+      <c r="J233" t="s">
+        <v>519</v>
+      </c>
+      <c r="O233" t="s">
         <v>511</v>
       </c>
-      <c r="N227" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="228" spans="9:14">
-      <c r="I228" t="s">
+    </row>
+    <row r="234" spans="10:15">
+      <c r="J234" t="s">
+        <v>520</v>
+      </c>
+      <c r="O234" t="s">
         <v>512</v>
       </c>
-      <c r="N228" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="229" spans="9:14">
-      <c r="I229" t="s">
+    </row>
+    <row r="235" spans="10:15">
+      <c r="J235" t="s">
+        <v>521</v>
+      </c>
+      <c r="O235" t="s">
         <v>513</v>
       </c>
-      <c r="N229" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="230" spans="9:14">
-      <c r="I230" t="s">
+    </row>
+    <row r="236" spans="10:15">
+      <c r="J236" t="s">
+        <v>522</v>
+      </c>
+      <c r="O236" t="s">
         <v>514</v>
       </c>
-      <c r="N230" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="231" spans="9:14">
-      <c r="I231" t="s">
+    </row>
+    <row r="237" spans="10:15">
+      <c r="J237" t="s">
+        <v>523</v>
+      </c>
+      <c r="O237" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="238" spans="10:15">
+      <c r="J238" t="s">
+        <v>524</v>
+      </c>
+      <c r="O238" t="s">
         <v>515</v>
       </c>
-      <c r="N231" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="232" spans="9:14">
-      <c r="I232" t="s">
+    </row>
+    <row r="239" spans="10:15">
+      <c r="J239" t="s">
+        <v>525</v>
+      </c>
+      <c r="O239" t="s">
         <v>516</v>
       </c>
-      <c r="N232" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="233" spans="9:14">
-      <c r="I233" t="s">
+    </row>
+    <row r="240" spans="10:15">
+      <c r="J240" t="s">
+        <v>526</v>
+      </c>
+      <c r="O240" t="s">
         <v>517</v>
       </c>
-      <c r="N233" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="234" spans="9:14">
-      <c r="I234" t="s">
+    </row>
+    <row r="241" spans="10:15">
+      <c r="J241" t="s">
+        <v>527</v>
+      </c>
+      <c r="O241" t="s">
         <v>518</v>
       </c>
-      <c r="N234" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="235" spans="9:14">
-      <c r="I235" t="s">
+    </row>
+    <row r="242" spans="10:15">
+      <c r="J242" t="s">
+        <v>528</v>
+      </c>
+      <c r="O242" t="s">
         <v>519</v>
       </c>
-      <c r="N235" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="236" spans="9:14">
-      <c r="I236" t="s">
+    </row>
+    <row r="243" spans="10:15">
+      <c r="J243" t="s">
+        <v>529</v>
+      </c>
+      <c r="O243" t="s">
         <v>520</v>
       </c>
-      <c r="N236" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="237" spans="9:14">
-      <c r="I237" t="s">
+    </row>
+    <row r="244" spans="10:15">
+      <c r="J244" t="s">
+        <v>530</v>
+      </c>
+      <c r="O244" t="s">
         <v>521</v>
       </c>
-      <c r="N237" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="238" spans="9:14">
-      <c r="I238" t="s">
-        <v>522</v>
-      </c>
-      <c r="N238" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="239" spans="9:14">
-      <c r="I239" t="s">
+    </row>
+    <row r="245" spans="10:15">
+      <c r="J245" t="s">
+        <v>531</v>
+      </c>
+      <c r="O245" t="s">
         <v>523</v>
       </c>
-      <c r="N239" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="240" spans="9:14">
-      <c r="I240" t="s">
+    </row>
+    <row r="246" spans="10:15">
+      <c r="J246" t="s">
+        <v>532</v>
+      </c>
+      <c r="O246" t="s">
         <v>524</v>
       </c>
-      <c r="N240" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="241" spans="9:14">
-      <c r="I241" t="s">
+    </row>
+    <row r="247" spans="10:15">
+      <c r="J247" t="s">
+        <v>533</v>
+      </c>
+      <c r="O247" t="s">
         <v>525</v>
       </c>
-      <c r="N241" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="242" spans="9:14">
-      <c r="I242" t="s">
+    </row>
+    <row r="248" spans="10:15">
+      <c r="J248" t="s">
+        <v>534</v>
+      </c>
+      <c r="O248" t="s">
         <v>526</v>
       </c>
-      <c r="N242" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="243" spans="9:14">
-      <c r="I243" t="s">
+    </row>
+    <row r="249" spans="10:15">
+      <c r="J249" t="s">
+        <v>535</v>
+      </c>
+      <c r="O249" t="s">
         <v>527</v>
       </c>
-      <c r="N243" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="244" spans="9:14">
-      <c r="I244" t="s">
+    </row>
+    <row r="250" spans="10:15">
+      <c r="J250" t="s">
+        <v>536</v>
+      </c>
+      <c r="O250" t="s">
         <v>528</v>
       </c>
-      <c r="N244" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="245" spans="9:14">
-      <c r="I245" t="s">
+    </row>
+    <row r="251" spans="10:15">
+      <c r="J251" t="s">
+        <v>537</v>
+      </c>
+      <c r="O251" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="252" spans="10:15">
+      <c r="J252" t="s">
+        <v>538</v>
+      </c>
+      <c r="O252" t="s">
         <v>529</v>
       </c>
-      <c r="N245" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="246" spans="9:14">
-      <c r="I246" t="s">
+    </row>
+    <row r="253" spans="10:15">
+      <c r="J253" t="s">
+        <v>539</v>
+      </c>
+      <c r="O253" t="s">
         <v>530</v>
       </c>
-      <c r="N246" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="247" spans="9:14">
-      <c r="I247" t="s">
+    </row>
+    <row r="254" spans="10:15">
+      <c r="J254" t="s">
+        <v>540</v>
+      </c>
+      <c r="O254" t="s">
         <v>531</v>
       </c>
-      <c r="N247" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="248" spans="9:14">
-      <c r="I248" t="s">
+    </row>
+    <row r="255" spans="10:15">
+      <c r="J255" t="s">
+        <v>541</v>
+      </c>
+      <c r="O255" t="s">
         <v>532</v>
       </c>
-      <c r="N248" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="249" spans="9:14">
-      <c r="I249" t="s">
+    </row>
+    <row r="256" spans="10:15">
+      <c r="J256" t="s">
+        <v>542</v>
+      </c>
+      <c r="O256" t="s">
         <v>533</v>
       </c>
-      <c r="N249" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="250" spans="9:14">
-      <c r="I250" t="s">
+    </row>
+    <row r="257" spans="10:15">
+      <c r="J257" t="s">
+        <v>543</v>
+      </c>
+      <c r="O257" t="s">
         <v>534</v>
       </c>
-      <c r="N250" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="251" spans="9:14">
-      <c r="I251" t="s">
+    </row>
+    <row r="258" spans="10:15">
+      <c r="J258" t="s">
+        <v>544</v>
+      </c>
+      <c r="O258" t="s">
         <v>535</v>
       </c>
-      <c r="N251" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="252" spans="9:14">
-      <c r="I252" t="s">
+    </row>
+    <row r="259" spans="10:15">
+      <c r="J259" t="s">
+        <v>545</v>
+      </c>
+      <c r="O259" t="s">
         <v>536</v>
       </c>
-      <c r="N252" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="253" spans="9:14">
-      <c r="I253" t="s">
+    </row>
+    <row r="260" spans="10:15">
+      <c r="J260" t="s">
+        <v>546</v>
+      </c>
+      <c r="O260" t="s">
         <v>537</v>
       </c>
-      <c r="N253" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="254" spans="9:14">
-      <c r="I254" t="s">
+    </row>
+    <row r="261" spans="10:15">
+      <c r="J261" t="s">
+        <v>547</v>
+      </c>
+      <c r="O261" t="s">
         <v>538</v>
       </c>
-      <c r="N254" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="255" spans="9:14">
-      <c r="I255" t="s">
+    </row>
+    <row r="262" spans="10:15">
+      <c r="J262" t="s">
+        <v>548</v>
+      </c>
+      <c r="O262" t="s">
         <v>539</v>
       </c>
-      <c r="N255" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="256" spans="9:14">
-      <c r="I256" t="s">
+    </row>
+    <row r="263" spans="10:15">
+      <c r="J263" t="s">
+        <v>549</v>
+      </c>
+      <c r="O263" t="s">
         <v>540</v>
       </c>
-      <c r="N256" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="257" spans="9:14">
-      <c r="I257" t="s">
+    </row>
+    <row r="264" spans="10:15">
+      <c r="J264" t="s">
+        <v>550</v>
+      </c>
+      <c r="O264" t="s">
         <v>541</v>
       </c>
-      <c r="N257" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="258" spans="9:14">
-      <c r="I258" t="s">
-        <v>542</v>
-      </c>
-      <c r="N258" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="259" spans="9:14">
-      <c r="I259" t="s">
+    </row>
+    <row r="265" spans="10:15">
+      <c r="J265" t="s">
+        <v>551</v>
+      </c>
+      <c r="O265" t="s">
         <v>543</v>
       </c>
-      <c r="N259" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="260" spans="9:14">
-      <c r="I260" t="s">
+    </row>
+    <row r="266" spans="10:15">
+      <c r="J266" t="s">
+        <v>552</v>
+      </c>
+      <c r="O266" t="s">
         <v>544</v>
       </c>
-      <c r="N260" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="261" spans="9:14">
-      <c r="I261" t="s">
+    </row>
+    <row r="267" spans="10:15">
+      <c r="J267" t="s">
+        <v>553</v>
+      </c>
+      <c r="O267" t="s">
         <v>545</v>
       </c>
-      <c r="N261" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="262" spans="9:14">
-      <c r="I262" t="s">
+    </row>
+    <row r="268" spans="10:15">
+      <c r="J268" t="s">
+        <v>554</v>
+      </c>
+      <c r="O268" t="s">
         <v>546</v>
       </c>
-      <c r="N262" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="263" spans="9:14">
-      <c r="I263" t="s">
+    </row>
+    <row r="269" spans="10:15">
+      <c r="J269" t="s">
+        <v>555</v>
+      </c>
+      <c r="O269" t="s">
         <v>547</v>
       </c>
-      <c r="N263" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="264" spans="9:14">
-      <c r="I264" t="s">
+    </row>
+    <row r="270" spans="10:15">
+      <c r="J270" t="s">
+        <v>556</v>
+      </c>
+      <c r="O270" t="s">
         <v>548</v>
       </c>
-      <c r="N264" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="265" spans="9:14">
-      <c r="I265" t="s">
+    </row>
+    <row r="271" spans="10:15">
+      <c r="J271" t="s">
+        <v>557</v>
+      </c>
+      <c r="O271" t="s">
         <v>549</v>
       </c>
-      <c r="N265" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="266" spans="9:14">
-      <c r="I266" t="s">
+    </row>
+    <row r="272" spans="10:15">
+      <c r="J272" t="s">
+        <v>558</v>
+      </c>
+      <c r="O272" t="s">
         <v>550</v>
       </c>
-      <c r="N266" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="267" spans="9:14">
-      <c r="I267" t="s">
+    </row>
+    <row r="273" spans="10:15">
+      <c r="J273" t="s">
+        <v>559</v>
+      </c>
+      <c r="O273" t="s">
         <v>551</v>
       </c>
-      <c r="N267" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="268" spans="9:14">
-      <c r="I268" t="s">
+    </row>
+    <row r="274" spans="10:15">
+      <c r="O274" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="275" spans="10:15">
+      <c r="O275" t="s">
         <v>552</v>
       </c>
-      <c r="N268" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="269" spans="9:14">
-      <c r="I269" t="s">
-        <v>553</v>
-      </c>
-      <c r="N269" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="270" spans="9:14">
-      <c r="I270" t="s">
+    </row>
+    <row r="276" spans="10:15">
+      <c r="O276" t="s">
         <v>554</v>
       </c>
-      <c r="N270" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="271" spans="9:14">
-      <c r="I271" t="s">
+    </row>
+    <row r="277" spans="10:15">
+      <c r="O277" t="s">
         <v>555</v>
       </c>
-      <c r="N271" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="272" spans="9:14">
-      <c r="I272" t="s">
+    </row>
+    <row r="278" spans="10:15">
+      <c r="O278" t="s">
         <v>556</v>
       </c>
-      <c r="N272" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="273" spans="9:14">
-      <c r="I273" t="s">
+    </row>
+    <row r="279" spans="10:15">
+      <c r="O279" t="s">
         <v>557</v>
       </c>
-      <c r="N273" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="274" spans="9:14">
-      <c r="N274" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="275" spans="9:14">
-      <c r="N275" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="276" spans="9:14">
-      <c r="N276" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="277" spans="9:14">
-      <c r="N277" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="278" spans="9:14">
-      <c r="N278" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="279" spans="9:14">
-      <c r="N279" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="280" spans="9:14">
-      <c r="N280" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="281" spans="9:14">
-      <c r="N281" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="282" spans="9:14">
-      <c r="N282" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="283" spans="9:14">
-      <c r="N283" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="284" spans="9:14">
-      <c r="N284" t="s">
+    </row>
+    <row r="280" spans="10:15">
+      <c r="O280" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="281" spans="10:15">
+      <c r="O281" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="282" spans="10:15">
+      <c r="O282" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="285" spans="9:14">
-      <c r="N285" t="s">
+    <row r="283" spans="10:15">
+      <c r="O283" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="286" spans="9:14">
-      <c r="N286" t="s">
+    <row r="284" spans="10:15">
+      <c r="O284" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="287" spans="9:14">
-      <c r="N287" t="s">
+    <row r="285" spans="10:15">
+      <c r="O285" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="288" spans="9:14">
-      <c r="N288" t="s">
+    <row r="286" spans="10:15">
+      <c r="O286" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="289" spans="14:14">
-      <c r="N289" t="s">
+    <row r="287" spans="10:15">
+      <c r="O287" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="290" spans="14:14">
-      <c r="N290" t="s">
+    <row r="288" spans="10:15">
+      <c r="O288" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="291" spans="14:14">
-      <c r="N291" t="s">
+    <row r="289" spans="15:15">
+      <c r="O289" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="292" spans="14:14">
-      <c r="N292" t="s">
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="293" spans="14:14">
-      <c r="N293" t="s">
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="294" spans="14:14">
-      <c r="N294" t="s">
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
         <v>601</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000044/metadata_template_ERC000044.xlsx
+++ b/templates/ERC000044/metadata_template_ERC000044.xlsx
@@ -20,13 +20,13 @@
     <definedName name="clinicalsetting">'cv_sample'!$I$1:$I$2</definedName>
     <definedName name="countryoftravel">'cv_sample'!$J$1:$J$273</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Q$1:$Q$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
     <definedName name="travelrelation">'cv_sample'!$H$1:$H$3</definedName>
   </definedNames>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="625">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1759,7 +1765,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1771,10 +1777,19 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
   </si>
   <si>
     <t>North Sea</t>
@@ -2421,10 +2436,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2465,10 +2480,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2512,7 +2527,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2529,7 +2544,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2546,7 +2561,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2563,7 +2578,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2580,7 +2595,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2597,7 +2612,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2614,7 +2629,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2631,7 +2646,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2648,7 +2663,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2662,7 +2677,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2676,7 +2691,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2690,7 +2705,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2704,7 +2719,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2718,7 +2733,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2732,7 +2747,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2746,7 +2761,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2760,7 +2775,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2770,8 +2785,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2782,7 +2800,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2793,7 +2811,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2804,7 +2822,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2815,7 +2833,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2826,7 +2844,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2837,7 +2855,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2848,7 +2866,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2859,7 +2877,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2870,7 +2888,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2881,7 +2899,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2892,7 +2910,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2903,7 +2921,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2914,7 +2932,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2922,7 +2940,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2930,7 +2948,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2938,7 +2956,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2946,7 +2964,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2954,7 +2972,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2962,7 +2980,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2970,7 +2988,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2978,7 +2996,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2986,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2994,236 +3012,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3245,27 +3268,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3285,122 +3308,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3424,138 +3447,138 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -3582,1716 +3605,1716 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:Q289"/>
+  <dimension ref="H1:Q294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:17">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="8:17">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q2" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="8:17">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q3" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="8:17">
       <c r="J4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="8:17">
       <c r="J5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="8:17">
       <c r="J6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="8:17">
       <c r="J7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="8:17">
       <c r="J8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="8:17">
       <c r="J9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="8:17">
       <c r="J10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="8:17">
       <c r="J11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="8:17">
       <c r="J12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="8:17">
       <c r="J13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="8:17">
       <c r="J14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="8:17">
       <c r="J15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O15" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="8:17">
       <c r="J16" t="s">
+        <v>302</v>
+      </c>
+      <c r="O16" t="s">
         <v>300</v>
-      </c>
-      <c r="O16" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="17" spans="10:15">
       <c r="J17" t="s">
+        <v>303</v>
+      </c>
+      <c r="O17" t="s">
         <v>301</v>
-      </c>
-      <c r="O17" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="18" spans="10:15">
       <c r="J18" t="s">
+        <v>304</v>
+      </c>
+      <c r="O18" t="s">
         <v>302</v>
-      </c>
-      <c r="O18" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="19" spans="10:15">
       <c r="J19" t="s">
+        <v>305</v>
+      </c>
+      <c r="O19" t="s">
         <v>303</v>
-      </c>
-      <c r="O19" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="20" spans="10:15">
       <c r="J20" t="s">
+        <v>306</v>
+      </c>
+      <c r="O20" t="s">
         <v>304</v>
-      </c>
-      <c r="O20" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="21" spans="10:15">
       <c r="J21" t="s">
+        <v>307</v>
+      </c>
+      <c r="O21" t="s">
         <v>305</v>
-      </c>
-      <c r="O21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="22" spans="10:15">
       <c r="J22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O22" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="10:15">
       <c r="J23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="10:15">
       <c r="J24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="10:15">
       <c r="J25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="10:15">
       <c r="J26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O26" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="10:15">
       <c r="J27" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="10:15">
       <c r="J28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="10:15">
       <c r="J29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="10:15">
       <c r="J30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O30" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="10:15">
       <c r="J31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="10:15">
       <c r="J32" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O32" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="10:15">
       <c r="J33" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O33" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="34" spans="10:15">
       <c r="J34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="10:15">
       <c r="J35" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="10:15">
       <c r="J36" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="10:15">
       <c r="J37" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="10:15">
       <c r="J38" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="10:15">
       <c r="J39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="10:15">
       <c r="J40" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="10:15">
       <c r="J41" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="10:15">
       <c r="J42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O42" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="10:15">
       <c r="J43" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="10:15">
       <c r="J44" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O44" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="10:15">
       <c r="J45" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="10:15">
       <c r="J46" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="10:15">
       <c r="J47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="10:15">
       <c r="J48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O48" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="10:15">
       <c r="J49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O49" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="10:15">
       <c r="J50" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="10:15">
       <c r="J51" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O51" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="10:15">
       <c r="J52" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O52" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="10:15">
       <c r="J53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O53" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="10:15">
       <c r="J54" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O54" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="10:15">
       <c r="J55" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O55" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="10:15">
       <c r="J56" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O56" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="10:15">
       <c r="J57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O57" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="10:15">
       <c r="J58" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O58" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="10:15">
       <c r="J59" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O59" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="10:15">
       <c r="J60" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O60" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="10:15">
       <c r="J61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="10:15">
       <c r="J62" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O62" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="10:15">
       <c r="J63" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O63" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" spans="10:15">
       <c r="J64" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O64" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="10:15">
       <c r="J65" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O65" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="66" spans="10:15">
       <c r="J66" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O66" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="10:15">
       <c r="J67" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O67" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="10:15">
       <c r="J68" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O68" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="10:15">
       <c r="J69" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="10:15">
       <c r="J70" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="10:15">
       <c r="J71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O71" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="10:15">
       <c r="J72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O72" t="s">
-        <v>574</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="10:15">
       <c r="J73" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O73" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" spans="10:15">
       <c r="J74" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="75" spans="10:15">
       <c r="J75" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O75" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="10:15">
       <c r="J76" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O76" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="10:15">
       <c r="J77" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O77" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="10:15">
       <c r="J78" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O78" t="s">
-        <v>357</v>
+        <v>576</v>
       </c>
     </row>
     <row r="79" spans="10:15">
       <c r="J79" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O79" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="10:15">
       <c r="J80" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O80" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="10:15">
       <c r="J81" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O81" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" spans="10:15">
       <c r="J82" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O82" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="10:15">
       <c r="J83" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O83" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="10:15">
       <c r="J84" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O84" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="10:15">
       <c r="J85" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O85" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="10:15">
       <c r="J86" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O86" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="10:15">
       <c r="J87" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O87" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="10:15">
       <c r="J88" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O88" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="10:15">
       <c r="J89" t="s">
+        <v>375</v>
+      </c>
+      <c r="O89" t="s">
         <v>373</v>
-      </c>
-      <c r="O89" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="90" spans="10:15">
       <c r="J90" t="s">
+        <v>376</v>
+      </c>
+      <c r="O90" t="s">
         <v>374</v>
-      </c>
-      <c r="O90" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="91" spans="10:15">
       <c r="J91" t="s">
+        <v>377</v>
+      </c>
+      <c r="O91" t="s">
         <v>375</v>
-      </c>
-      <c r="O91" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="92" spans="10:15">
       <c r="J92" t="s">
+        <v>378</v>
+      </c>
+      <c r="O92" t="s">
         <v>376</v>
-      </c>
-      <c r="O92" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="93" spans="10:15">
       <c r="J93" t="s">
+        <v>379</v>
+      </c>
+      <c r="O93" t="s">
         <v>377</v>
-      </c>
-      <c r="O93" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="94" spans="10:15">
       <c r="J94" t="s">
+        <v>380</v>
+      </c>
+      <c r="O94" t="s">
         <v>378</v>
-      </c>
-      <c r="O94" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="95" spans="10:15">
       <c r="J95" t="s">
+        <v>381</v>
+      </c>
+      <c r="O95" t="s">
         <v>379</v>
-      </c>
-      <c r="O95" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="96" spans="10:15">
       <c r="J96" t="s">
+        <v>382</v>
+      </c>
+      <c r="O96" t="s">
         <v>380</v>
-      </c>
-      <c r="O96" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="97" spans="10:15">
       <c r="J97" t="s">
+        <v>383</v>
+      </c>
+      <c r="O97" t="s">
         <v>381</v>
-      </c>
-      <c r="O97" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="98" spans="10:15">
       <c r="J98" t="s">
+        <v>384</v>
+      </c>
+      <c r="O98" t="s">
         <v>382</v>
-      </c>
-      <c r="O98" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="99" spans="10:15">
       <c r="J99" t="s">
+        <v>385</v>
+      </c>
+      <c r="O99" t="s">
         <v>383</v>
-      </c>
-      <c r="O99" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="100" spans="10:15">
       <c r="J100" t="s">
+        <v>386</v>
+      </c>
+      <c r="O100" t="s">
         <v>384</v>
-      </c>
-      <c r="O100" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="101" spans="10:15">
       <c r="J101" t="s">
+        <v>387</v>
+      </c>
+      <c r="O101" t="s">
         <v>385</v>
-      </c>
-      <c r="O101" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="102" spans="10:15">
       <c r="J102" t="s">
+        <v>388</v>
+      </c>
+      <c r="O102" t="s">
         <v>386</v>
-      </c>
-      <c r="O102" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="103" spans="10:15">
       <c r="J103" t="s">
+        <v>389</v>
+      </c>
+      <c r="O103" t="s">
         <v>387</v>
-      </c>
-      <c r="O103" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="104" spans="10:15">
       <c r="J104" t="s">
+        <v>390</v>
+      </c>
+      <c r="O104" t="s">
         <v>388</v>
-      </c>
-      <c r="O104" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="105" spans="10:15">
       <c r="J105" t="s">
+        <v>391</v>
+      </c>
+      <c r="O105" t="s">
         <v>389</v>
-      </c>
-      <c r="O105" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="106" spans="10:15">
       <c r="J106" t="s">
+        <v>392</v>
+      </c>
+      <c r="O106" t="s">
         <v>390</v>
-      </c>
-      <c r="O106" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="107" spans="10:15">
       <c r="J107" t="s">
+        <v>393</v>
+      </c>
+      <c r="O107" t="s">
         <v>391</v>
-      </c>
-      <c r="O107" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="108" spans="10:15">
       <c r="J108" t="s">
+        <v>394</v>
+      </c>
+      <c r="O108" t="s">
         <v>392</v>
-      </c>
-      <c r="O108" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="109" spans="10:15">
       <c r="J109" t="s">
+        <v>395</v>
+      </c>
+      <c r="O109" t="s">
         <v>393</v>
-      </c>
-      <c r="O109" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="110" spans="10:15">
       <c r="J110" t="s">
+        <v>396</v>
+      </c>
+      <c r="O110" t="s">
         <v>394</v>
-      </c>
-      <c r="O110" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="111" spans="10:15">
       <c r="J111" t="s">
+        <v>397</v>
+      </c>
+      <c r="O111" t="s">
         <v>395</v>
-      </c>
-      <c r="O111" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="112" spans="10:15">
       <c r="J112" t="s">
+        <v>398</v>
+      </c>
+      <c r="O112" t="s">
         <v>396</v>
-      </c>
-      <c r="O112" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="113" spans="10:15">
       <c r="J113" t="s">
+        <v>399</v>
+      </c>
+      <c r="O113" t="s">
         <v>397</v>
-      </c>
-      <c r="O113" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="114" spans="10:15">
       <c r="J114" t="s">
+        <v>400</v>
+      </c>
+      <c r="O114" t="s">
         <v>398</v>
-      </c>
-      <c r="O114" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="115" spans="10:15">
       <c r="J115" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O115" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="116" spans="10:15">
       <c r="J116" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O116" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="10:15">
       <c r="J117" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O117" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="10:15">
       <c r="J118" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O118" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="10:15">
       <c r="J119" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O119" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="10:15">
       <c r="J120" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O120" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="10:15">
       <c r="J121" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O121" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="10:15">
       <c r="J122" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O122" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="10:15">
       <c r="J123" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O123" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="10:15">
       <c r="J124" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O124" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="10:15">
       <c r="J125" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O125" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="10:15">
       <c r="J126" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O126" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="127" spans="10:15">
       <c r="J127" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O127" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128" spans="10:15">
       <c r="J128" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O128" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" spans="10:15">
       <c r="J129" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O129" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="130" spans="10:15">
       <c r="J130" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O130" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131" spans="10:15">
       <c r="J131" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O131" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="10:15">
       <c r="J132" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O132" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="133" spans="10:15">
       <c r="J133" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O133" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="134" spans="10:15">
       <c r="J134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O134" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="10:15">
       <c r="J135" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O135" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="10:15">
       <c r="J136" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O136" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="10:15">
       <c r="J137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O137" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="10:15">
       <c r="J138" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O138" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="10:15">
       <c r="J139" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O139" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="10:15">
       <c r="J140" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O140" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="141" spans="10:15">
       <c r="J141" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O141" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="142" spans="10:15">
       <c r="J142" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O142" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="10:15">
       <c r="J143" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O143" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="10:15">
       <c r="J144" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O144" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="10:15">
       <c r="J145" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O145" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="146" spans="10:15">
       <c r="J146" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O146" t="s">
-        <v>427</v>
+        <v>580</v>
       </c>
     </row>
     <row r="147" spans="10:15">
       <c r="J147" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O147" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="148" spans="10:15">
       <c r="J148" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O148" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="149" spans="10:15">
       <c r="J149" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O149" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="150" spans="10:15">
       <c r="J150" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O150" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="151" spans="10:15">
       <c r="J151" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O151" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="152" spans="10:15">
       <c r="J152" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O152" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="10:15">
       <c r="J153" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O153" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="10:15">
       <c r="J154" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O154" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="155" spans="10:15">
       <c r="J155" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O155" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="156" spans="10:15">
       <c r="J156" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O156" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="157" spans="10:15">
       <c r="J157" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O157" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="158" spans="10:15">
       <c r="J158" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O158" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="159" spans="10:15">
       <c r="J159" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O159" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="160" spans="10:15">
       <c r="J160" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O160" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="161" spans="10:15">
       <c r="J161" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O161" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="162" spans="10:15">
       <c r="J162" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O162" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="10:15">
       <c r="J163" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O163" t="s">
-        <v>443</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="10:15">
       <c r="J164" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O164" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="10:15">
       <c r="J165" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O165" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="10:15">
       <c r="J166" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O166" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="167" spans="10:15">
       <c r="J167" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O167" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="10:15">
       <c r="J168" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="169" spans="10:15">
       <c r="J169" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="10:15">
       <c r="J170" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O170" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="171" spans="10:15">
       <c r="J171" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O171" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="172" spans="10:15">
       <c r="J172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O172" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="173" spans="10:15">
       <c r="J173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O173" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="174" spans="10:15">
       <c r="J174" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O174" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="10:15">
       <c r="J175" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O175" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="176" spans="10:15">
       <c r="J176" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O176" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="177" spans="10:15">
       <c r="J177" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O177" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="10:15">
       <c r="J178" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O178" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="10:15">
       <c r="J179" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O179" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="180" spans="10:15">
       <c r="J180" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O180" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="10:15">
       <c r="J181" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O181" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="10:15">
       <c r="J182" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O182" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="10:15">
       <c r="J183" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O183" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="184" spans="10:15">
       <c r="J184" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O184" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="185" spans="10:15">
       <c r="J185" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O185" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="10:15">
       <c r="J186" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O186" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="187" spans="10:15">
       <c r="J187" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O187" t="s">
-        <v>466</v>
+        <v>585</v>
       </c>
     </row>
     <row r="188" spans="10:15">
       <c r="J188" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O188" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="189" spans="10:15">
       <c r="J189" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O189" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="190" spans="10:15">
       <c r="J190" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O190" t="s">
-        <v>581</v>
+        <v>470</v>
       </c>
     </row>
     <row r="191" spans="10:15">
       <c r="J191" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O191" t="s">
-        <v>469</v>
+        <v>586</v>
       </c>
     </row>
     <row r="192" spans="10:15">
       <c r="J192" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O192" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="193" spans="10:15">
       <c r="J193" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O193" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194" spans="10:15">
       <c r="J194" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O194" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="195" spans="10:15">
       <c r="J195" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O195" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="196" spans="10:15">
       <c r="J196" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O196" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="197" spans="10:15">
       <c r="J197" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O197" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="198" spans="10:15">
       <c r="J198" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O198" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="199" spans="10:15">
       <c r="J199" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O199" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="200" spans="10:15">
       <c r="J200" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O200" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="201" spans="10:15">
       <c r="J201" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O201" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="202" spans="10:15">
       <c r="J202" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O202" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203" spans="10:15">
       <c r="J203" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O203" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="204" spans="10:15">
       <c r="J204" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O204" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="10:15">
       <c r="J205" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="10:15">
       <c r="J206" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="10:15">
       <c r="J207" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O207" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="208" spans="10:15">
       <c r="J208" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O208" t="s">
-        <v>582</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="10:15">
       <c r="J209" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O209" t="s">
-        <v>486</v>
+        <v>587</v>
       </c>
     </row>
     <row r="210" spans="10:15">
       <c r="J210" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O210" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211" spans="10:15">
       <c r="J211" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O211" t="s">
         <v>489</v>
@@ -5299,7 +5322,7 @@
     </row>
     <row r="212" spans="10:15">
       <c r="J212" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O212" t="s">
         <v>490</v>
@@ -5307,7 +5330,7 @@
     </row>
     <row r="213" spans="10:15">
       <c r="J213" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O213" t="s">
         <v>491</v>
@@ -5315,23 +5338,23 @@
     </row>
     <row r="214" spans="10:15">
       <c r="J214" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O214" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="215" spans="10:15">
       <c r="J215" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O215" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="216" spans="10:15">
       <c r="J216" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O216" t="s">
         <v>495</v>
@@ -5339,7 +5362,7 @@
     </row>
     <row r="217" spans="10:15">
       <c r="J217" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O217" t="s">
         <v>496</v>
@@ -5347,7 +5370,7 @@
     </row>
     <row r="218" spans="10:15">
       <c r="J218" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O218" t="s">
         <v>497</v>
@@ -5355,7 +5378,7 @@
     </row>
     <row r="219" spans="10:15">
       <c r="J219" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O219" t="s">
         <v>498</v>
@@ -5363,55 +5386,55 @@
     </row>
     <row r="220" spans="10:15">
       <c r="J220" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O220" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="221" spans="10:15">
       <c r="J221" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O221" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="222" spans="10:15">
       <c r="J222" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O222" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="10:15">
       <c r="J223" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O223" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="10:15">
       <c r="J224" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O224" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="225" spans="10:15">
       <c r="J225" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O225" t="s">
-        <v>583</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="10:15">
       <c r="J226" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O226" t="s">
         <v>505</v>
@@ -5419,7 +5442,7 @@
     </row>
     <row r="227" spans="10:15">
       <c r="J227" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O227" t="s">
         <v>506</v>
@@ -5427,410 +5450,410 @@
     </row>
     <row r="228" spans="10:15">
       <c r="J228" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O228" t="s">
-        <v>507</v>
+        <v>588</v>
       </c>
     </row>
     <row r="229" spans="10:15">
       <c r="J229" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O229" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="230" spans="10:15">
       <c r="J230" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O230" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="231" spans="10:15">
       <c r="J231" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O231" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="232" spans="10:15">
       <c r="J232" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O232" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="233" spans="10:15">
       <c r="J233" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O233" t="s">
-        <v>584</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="10:15">
       <c r="J234" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O234" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="10:15">
       <c r="J235" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="236" spans="10:15">
       <c r="J236" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O236" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="237" spans="10:15">
       <c r="J237" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O237" t="s">
-        <v>517</v>
+        <v>589</v>
       </c>
     </row>
     <row r="238" spans="10:15">
       <c r="J238" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O238" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="239" spans="10:15">
       <c r="J239" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O239" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="240" spans="10:15">
       <c r="J240" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O240" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="241" spans="10:15">
       <c r="J241" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O241" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="242" spans="10:15">
       <c r="J242" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O242" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="243" spans="10:15">
       <c r="J243" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O243" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="244" spans="10:15">
       <c r="J244" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O244" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="245" spans="10:15">
       <c r="J245" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O245" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="10:15">
       <c r="J246" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O246" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="247" spans="10:15">
       <c r="J247" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O247" t="s">
-        <v>585</v>
+        <v>525</v>
       </c>
     </row>
     <row r="248" spans="10:15">
       <c r="J248" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O248" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="249" spans="10:15">
       <c r="J249" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O249" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250" spans="10:15">
       <c r="J250" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O250" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="251" spans="10:15">
       <c r="J251" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O251" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
     </row>
     <row r="252" spans="10:15">
       <c r="J252" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O252" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="253" spans="10:15">
       <c r="J253" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O253" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="254" spans="10:15">
       <c r="J254" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O254" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="255" spans="10:15">
       <c r="J255" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O255" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="256" spans="10:15">
       <c r="J256" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O256" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="257" spans="10:15">
       <c r="J257" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O257" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="258" spans="10:15">
       <c r="J258" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O258" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="259" spans="10:15">
       <c r="J259" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O259" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="260" spans="10:15">
       <c r="J260" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O260" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="261" spans="10:15">
       <c r="J261" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O261" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262" spans="10:15">
       <c r="J262" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O262" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="263" spans="10:15">
       <c r="J263" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O263" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="10:15">
       <c r="J264" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="O264" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" spans="10:15">
       <c r="J265" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O265" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="266" spans="10:15">
       <c r="J266" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O266" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="267" spans="10:15">
       <c r="J267" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O267" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="268" spans="10:15">
       <c r="J268" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O268" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="269" spans="10:15">
       <c r="J269" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O269" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="270" spans="10:15">
       <c r="J270" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O270" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="271" spans="10:15">
       <c r="J271" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O271" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="272" spans="10:15">
       <c r="J272" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O272" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="273" spans="10:15">
       <c r="J273" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O273" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="274" spans="10:15">
       <c r="O274" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="275" spans="10:15">
       <c r="O275" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="276" spans="10:15">
       <c r="O276" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="277" spans="10:15">
       <c r="O277" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
     </row>
     <row r="278" spans="10:15">
       <c r="O278" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
     </row>
     <row r="279" spans="10:15">
       <c r="O279" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
     </row>
     <row r="280" spans="10:15">
       <c r="O280" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="281" spans="10:15">
       <c r="O281" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
     </row>
     <row r="282" spans="10:15">
@@ -5871,6 +5894,31 @@
     <row r="289" spans="15:15">
       <c r="O289" t="s">
         <v>598</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000044/metadata_template_ERC000044.xlsx
+++ b/templates/ERC000044/metadata_template_ERC000044.xlsx
@@ -22,7 +22,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Q$1:$Q$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="626">
   <si>
     <t>alias</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2439,7 +2442,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2483,7 +2486,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3247,6 +3250,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3268,27 +3276,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3308,122 +3316,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3447,138 +3455,138 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -3610,2315 +3618,2315 @@
   <sheetData>
     <row r="1" spans="8:17">
       <c r="H1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" spans="8:17">
       <c r="H2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="8:17">
       <c r="H3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="8:17">
       <c r="J4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="8:17">
       <c r="J5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="8:17">
       <c r="J6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="8:17">
       <c r="J7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="8:17">
       <c r="J8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="8:17">
       <c r="J9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="8:17">
       <c r="J10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="8:17">
       <c r="J11" t="s">
+        <v>298</v>
+      </c>
+      <c r="O11" t="s">
         <v>297</v>
-      </c>
-      <c r="O11" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="12" spans="8:17">
       <c r="J12" t="s">
+        <v>299</v>
+      </c>
+      <c r="O12" t="s">
         <v>298</v>
-      </c>
-      <c r="O12" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="13" spans="8:17">
       <c r="J13" t="s">
+        <v>300</v>
+      </c>
+      <c r="O13" t="s">
         <v>299</v>
-      </c>
-      <c r="O13" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="14" spans="8:17">
       <c r="J14" t="s">
+        <v>301</v>
+      </c>
+      <c r="O14" t="s">
         <v>300</v>
-      </c>
-      <c r="O14" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="15" spans="8:17">
       <c r="J15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="8:17">
       <c r="J16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="10:15">
       <c r="J17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="10:15">
       <c r="J18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="10:15">
       <c r="J19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="10:15">
       <c r="J20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="10:15">
       <c r="J21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="10:15">
       <c r="J22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O22" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="23" spans="10:15">
       <c r="J23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="10:15">
       <c r="J24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="10:15">
       <c r="J25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="10:15">
       <c r="J26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="10:15">
       <c r="J27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="10:15">
       <c r="J28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O28" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="10:15">
       <c r="J29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="10:15">
       <c r="J30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="10:15">
       <c r="J31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O31" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" spans="10:15">
       <c r="J32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="10:15">
       <c r="J33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O33" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="34" spans="10:15">
       <c r="J34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="10:15">
       <c r="J35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="10:15">
       <c r="J36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O36" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="10:15">
       <c r="J37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O37" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="10:15">
       <c r="J38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" spans="10:15">
       <c r="J39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O39" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="10:15">
       <c r="J40" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O40" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="10:15">
       <c r="J41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O41" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" spans="10:15">
       <c r="J42" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O42" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="10:15">
       <c r="J43" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="10:15">
       <c r="J44" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O44" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" spans="10:15">
       <c r="J45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O45" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="10:15">
       <c r="J46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O46" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="10:15">
       <c r="J47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O47" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="10:15">
       <c r="J48" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O48" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="10:15">
       <c r="J49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="50" spans="10:15">
       <c r="J50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O50" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="10:15">
       <c r="J51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O51" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="10:15">
       <c r="J52" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O52" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="10:15">
       <c r="J53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O53" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="10:15">
       <c r="J54" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O54" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55" spans="10:15">
       <c r="J55" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O55" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="10:15">
       <c r="J56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O56" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="10:15">
       <c r="J57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O57" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="10:15">
       <c r="J58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O58" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="10:15">
       <c r="J59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O59" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="60" spans="10:15">
       <c r="J60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O60" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="61" spans="10:15">
       <c r="J61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O61" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62" spans="10:15">
       <c r="J62" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O62" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="10:15">
       <c r="J63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O63" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="64" spans="10:15">
       <c r="J64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O64" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="65" spans="10:15">
       <c r="J65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O65" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" spans="10:15">
       <c r="J66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="10:15">
       <c r="J67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O67" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="10:15">
       <c r="J68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="10:15">
       <c r="J69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="10:15">
       <c r="J70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O70" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" spans="10:15">
       <c r="J71" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="72" spans="10:15">
       <c r="J72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="10:15">
       <c r="J73" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O73" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="74" spans="10:15">
       <c r="J74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O74" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="10:15">
       <c r="J75" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O75" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="10:15">
       <c r="J76" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77" spans="10:15">
       <c r="J77" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O77" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="78" spans="10:15">
       <c r="J78" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O78" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="79" spans="10:15">
       <c r="J79" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O79" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="80" spans="10:15">
       <c r="J80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O80" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="81" spans="10:15">
       <c r="J81" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O81" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="82" spans="10:15">
       <c r="J82" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O82" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="10:15">
       <c r="J83" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O83" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="10:15">
       <c r="J84" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O84" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" spans="10:15">
       <c r="J85" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O85" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="10:15">
       <c r="J86" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O86" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="87" spans="10:15">
       <c r="J87" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O87" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="10:15">
       <c r="J88" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O88" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="89" spans="10:15">
       <c r="J89" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O89" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="90" spans="10:15">
       <c r="J90" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O90" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="91" spans="10:15">
       <c r="J91" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O91" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="10:15">
       <c r="J92" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O92" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" spans="10:15">
       <c r="J93" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O93" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="10:15">
       <c r="J94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O94" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="95" spans="10:15">
       <c r="J95" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O95" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="10:15">
       <c r="J96" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O96" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97" spans="10:15">
       <c r="J97" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O97" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="10:15">
       <c r="J98" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O98" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="99" spans="10:15">
       <c r="J99" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O99" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="100" spans="10:15">
       <c r="J100" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O100" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="101" spans="10:15">
       <c r="J101" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="102" spans="10:15">
       <c r="J102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O102" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="10:15">
       <c r="J103" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O103" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="10:15">
       <c r="J104" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O104" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="105" spans="10:15">
       <c r="J105" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O105" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="106" spans="10:15">
       <c r="J106" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O106" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="107" spans="10:15">
       <c r="J107" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O107" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="10:15">
       <c r="J108" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O108" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="109" spans="10:15">
       <c r="J109" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O109" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="110" spans="10:15">
       <c r="J110" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O110" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111" spans="10:15">
       <c r="J111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="112" spans="10:15">
       <c r="J112" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O112" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="113" spans="10:15">
       <c r="J113" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O113" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114" spans="10:15">
       <c r="J114" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O114" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="10:15">
       <c r="J115" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O115" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="116" spans="10:15">
       <c r="J116" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O116" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="10:15">
       <c r="J117" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O117" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="10:15">
       <c r="J118" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O118" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="119" spans="10:15">
       <c r="J119" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O119" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="120" spans="10:15">
       <c r="J120" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O120" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="121" spans="10:15">
       <c r="J121" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O121" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="122" spans="10:15">
       <c r="J122" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O122" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="123" spans="10:15">
       <c r="J123" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O123" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="124" spans="10:15">
       <c r="J124" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O124" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="125" spans="10:15">
       <c r="J125" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O125" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="126" spans="10:15">
       <c r="J126" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O126" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="127" spans="10:15">
       <c r="J127" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O127" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="128" spans="10:15">
       <c r="J128" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O128" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="129" spans="10:15">
       <c r="J129" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O129" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="130" spans="10:15">
       <c r="J130" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O130" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="131" spans="10:15">
       <c r="J131" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O131" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="132" spans="10:15">
       <c r="J132" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O132" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="133" spans="10:15">
       <c r="J133" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O133" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="134" spans="10:15">
       <c r="J134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O134" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="135" spans="10:15">
       <c r="J135" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O135" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="136" spans="10:15">
       <c r="J136" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O136" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="10:15">
       <c r="J137" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O137" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="138" spans="10:15">
       <c r="J138" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O138" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="139" spans="10:15">
       <c r="J139" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O139" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="140" spans="10:15">
       <c r="J140" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O140" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141" spans="10:15">
       <c r="J141" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O141" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="142" spans="10:15">
       <c r="J142" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O142" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="143" spans="10:15">
       <c r="J143" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O143" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="144" spans="10:15">
       <c r="J144" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O144" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="145" spans="10:15">
       <c r="J145" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O145" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="146" spans="10:15">
       <c r="J146" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O146" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="147" spans="10:15">
       <c r="J147" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O147" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="10:15">
       <c r="J148" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O148" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="149" spans="10:15">
       <c r="J149" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O149" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="150" spans="10:15">
       <c r="J150" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O150" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="151" spans="10:15">
       <c r="J151" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O151" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="152" spans="10:15">
       <c r="J152" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O152" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="153" spans="10:15">
       <c r="J153" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O153" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="154" spans="10:15">
       <c r="J154" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O154" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="155" spans="10:15">
       <c r="J155" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O155" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="156" spans="10:15">
       <c r="J156" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O156" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="157" spans="10:15">
       <c r="J157" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O157" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="158" spans="10:15">
       <c r="J158" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O158" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="159" spans="10:15">
       <c r="J159" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O159" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="160" spans="10:15">
       <c r="J160" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O160" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="161" spans="10:15">
       <c r="J161" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O161" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="10:15">
       <c r="J162" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O162" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" spans="10:15">
       <c r="J163" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O163" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="164" spans="10:15">
       <c r="J164" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O164" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="165" spans="10:15">
       <c r="J165" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O165" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="166" spans="10:15">
       <c r="J166" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O166" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="167" spans="10:15">
       <c r="J167" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O167" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="168" spans="10:15">
       <c r="J168" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O168" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="169" spans="10:15">
       <c r="J169" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O169" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="170" spans="10:15">
       <c r="J170" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O170" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="171" spans="10:15">
       <c r="J171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O171" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="172" spans="10:15">
       <c r="J172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O172" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="173" spans="10:15">
       <c r="J173" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O173" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="174" spans="10:15">
       <c r="J174" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O174" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="175" spans="10:15">
       <c r="J175" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O175" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="176" spans="10:15">
       <c r="J176" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O176" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="177" spans="10:15">
       <c r="J177" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O177" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="178" spans="10:15">
       <c r="J178" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O178" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="179" spans="10:15">
       <c r="J179" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O179" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="180" spans="10:15">
       <c r="J180" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O180" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="181" spans="10:15">
       <c r="J181" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O181" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="182" spans="10:15">
       <c r="J182" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O182" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="183" spans="10:15">
       <c r="J183" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O183" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="184" spans="10:15">
       <c r="J184" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O184" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="185" spans="10:15">
       <c r="J185" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O185" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="186" spans="10:15">
       <c r="J186" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O186" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="187" spans="10:15">
       <c r="J187" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O187" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="188" spans="10:15">
       <c r="J188" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O188" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="189" spans="10:15">
       <c r="J189" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O189" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="190" spans="10:15">
       <c r="J190" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O190" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="191" spans="10:15">
       <c r="J191" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O191" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="192" spans="10:15">
       <c r="J192" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O192" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="193" spans="10:15">
       <c r="J193" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O193" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="194" spans="10:15">
       <c r="J194" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O194" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="195" spans="10:15">
       <c r="J195" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O195" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="196" spans="10:15">
       <c r="J196" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O196" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="10:15">
       <c r="J197" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O197" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="198" spans="10:15">
       <c r="J198" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O198" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="199" spans="10:15">
       <c r="J199" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O199" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="200" spans="10:15">
       <c r="J200" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O200" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" spans="10:15">
       <c r="J201" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O201" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="202" spans="10:15">
       <c r="J202" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O202" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="203" spans="10:15">
       <c r="J203" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O203" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="10:15">
       <c r="J204" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="10:15">
       <c r="J205" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="10:15">
       <c r="J206" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O206" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="207" spans="10:15">
       <c r="J207" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O207" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="208" spans="10:15">
       <c r="J208" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O208" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="209" spans="10:15">
       <c r="J209" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O209" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="210" spans="10:15">
       <c r="J210" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O210" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="10:15">
       <c r="J211" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O211" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="212" spans="10:15">
       <c r="J212" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O212" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="213" spans="10:15">
       <c r="J213" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O213" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="214" spans="10:15">
       <c r="J214" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O214" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="215" spans="10:15">
       <c r="J215" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O215" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="216" spans="10:15">
       <c r="J216" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O216" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="217" spans="10:15">
       <c r="J217" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O217" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="218" spans="10:15">
       <c r="J218" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O218" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="219" spans="10:15">
       <c r="J219" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O219" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="220" spans="10:15">
       <c r="J220" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O220" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="221" spans="10:15">
       <c r="J221" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O221" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="222" spans="10:15">
       <c r="J222" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O222" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="223" spans="10:15">
       <c r="J223" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O223" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="224" spans="10:15">
       <c r="J224" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O224" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="225" spans="10:15">
       <c r="J225" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O225" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="226" spans="10:15">
       <c r="J226" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O226" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="227" spans="10:15">
       <c r="J227" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O227" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="228" spans="10:15">
       <c r="J228" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O228" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="229" spans="10:15">
       <c r="J229" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O229" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="230" spans="10:15">
       <c r="J230" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O230" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="231" spans="10:15">
       <c r="J231" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O231" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="232" spans="10:15">
       <c r="J232" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O232" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="233" spans="10:15">
       <c r="J233" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O233" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="234" spans="10:15">
       <c r="J234" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O234" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="235" spans="10:15">
       <c r="J235" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O235" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="236" spans="10:15">
       <c r="J236" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O236" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="237" spans="10:15">
       <c r="J237" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O237" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="238" spans="10:15">
       <c r="J238" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O238" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="239" spans="10:15">
       <c r="J239" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O239" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="240" spans="10:15">
       <c r="J240" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O240" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="241" spans="10:15">
       <c r="J241" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O241" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" spans="10:15">
       <c r="J242" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O242" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="10:15">
       <c r="J243" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O243" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="244" spans="10:15">
       <c r="J244" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O244" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="245" spans="10:15">
       <c r="J245" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O245" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="246" spans="10:15">
       <c r="J246" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O246" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="247" spans="10:15">
       <c r="J247" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O247" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="248" spans="10:15">
       <c r="J248" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O248" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="249" spans="10:15">
       <c r="J249" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O249" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="250" spans="10:15">
       <c r="J250" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O250" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="251" spans="10:15">
       <c r="J251" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O251" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="252" spans="10:15">
       <c r="J252" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O252" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="253" spans="10:15">
       <c r="J253" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O253" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="254" spans="10:15">
       <c r="J254" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O254" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="255" spans="10:15">
       <c r="J255" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O255" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="256" spans="10:15">
       <c r="J256" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O256" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="257" spans="10:15">
       <c r="J257" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O257" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="258" spans="10:15">
       <c r="J258" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O258" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="259" spans="10:15">
       <c r="J259" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O259" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="260" spans="10:15">
       <c r="J260" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O260" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="261" spans="10:15">
       <c r="J261" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O261" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="262" spans="10:15">
       <c r="J262" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O262" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="263" spans="10:15">
       <c r="J263" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O263" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="264" spans="10:15">
       <c r="J264" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O264" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="265" spans="10:15">
       <c r="J265" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O265" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="266" spans="10:15">
       <c r="J266" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O266" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="267" spans="10:15">
       <c r="J267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O267" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="268" spans="10:15">
       <c r="J268" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O268" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="269" spans="10:15">
       <c r="J269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O269" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="270" spans="10:15">
       <c r="J270" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O270" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="271" spans="10:15">
       <c r="J271" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O271" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="272" spans="10:15">
       <c r="J272" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O272" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="273" spans="10:15">
       <c r="J273" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O273" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="274" spans="10:15">
       <c r="O274" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="275" spans="10:15">
       <c r="O275" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="276" spans="10:15">
       <c r="O276" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="277" spans="10:15">
       <c r="O277" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="278" spans="10:15">
       <c r="O278" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="279" spans="10:15">
       <c r="O279" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="280" spans="10:15">
       <c r="O280" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="281" spans="10:15">
       <c r="O281" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="282" spans="10:15">
       <c r="O282" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="283" spans="10:15">
       <c r="O283" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="284" spans="10:15">
       <c r="O284" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="285" spans="10:15">
       <c r="O285" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="286" spans="10:15">
       <c r="O286" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="287" spans="10:15">
       <c r="O287" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="288" spans="10:15">
       <c r="O288" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="290" spans="15:15">
       <c r="O290" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="291" spans="15:15">
       <c r="O291" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="292" spans="15:15">
       <c r="O292" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="293" spans="15:15">
       <c r="O293" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="294" spans="15:15">
       <c r="O294" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
